--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="157">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -486,6 +486,15 @@
   </si>
   <si>
     <t>ДЛЯ ДЕТЕЙ</t>
+  </si>
+  <si>
+    <t>ГЛАВНЫЕ ЗАПРОСЫ</t>
+  </si>
+  <si>
+    <t>MEGAINDEX</t>
+  </si>
+  <si>
+    <t>MAJENTO</t>
   </si>
 </sst>
 </file>
@@ -561,137 +570,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -701,7 +585,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -719,49 +603,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1068,44 +934,50 @@
     <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="M1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1117,7 +989,7 @@
       <c r="C2" s="3">
         <v>4054</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="9"/>
       <c r="E2" s="1" t="s">
         <v>68</v>
       </c>
@@ -1127,7 +999,7 @@
       <c r="G2" s="6">
         <v>1080</v>
       </c>
-      <c r="H2" s="9"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="1" t="s">
         <v>114</v>
       </c>
@@ -1138,9 +1010,15 @@
         <v>944</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="M2" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="14">
+        <v>610</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1152,7 +1030,7 @@
       <c r="C3" s="2">
         <v>1740</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="9"/>
       <c r="E3" s="1" t="s">
         <v>70</v>
       </c>
@@ -1162,7 +1040,7 @@
       <c r="G3" s="6">
         <v>676</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="8"/>
       <c r="I3" s="1" t="s">
         <v>116</v>
       </c>
@@ -1173,6 +1051,15 @@
         <v>58</v>
       </c>
       <c r="L3" s="5"/>
+      <c r="M3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="N3" s="11">
+        <v>122</v>
+      </c>
+      <c r="O3" s="14">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -1184,7 +1071,7 @@
       <c r="C4" s="6">
         <v>19</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="9"/>
       <c r="E4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1194,7 +1081,7 @@
       <c r="G4" s="6">
         <v>173</v>
       </c>
-      <c r="H4" s="9"/>
+      <c r="H4" s="8"/>
       <c r="I4" s="1" t="s">
         <v>117</v>
       </c>
@@ -1205,6 +1092,15 @@
         <v>48</v>
       </c>
       <c r="L4" s="5"/>
+      <c r="M4" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="N4" s="11">
+        <v>113</v>
+      </c>
+      <c r="O4" s="14">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -1216,7 +1112,7 @@
       <c r="C5" s="6">
         <v>1049</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="1" t="s">
         <v>72</v>
       </c>
@@ -1226,7 +1122,7 @@
       <c r="G5" s="6">
         <v>160</v>
       </c>
-      <c r="H5" s="9"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="1" t="s">
         <v>118</v>
       </c>
@@ -1237,6 +1133,15 @@
         <v>29</v>
       </c>
       <c r="L5" s="5"/>
+      <c r="M5" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N5" s="11">
+        <v>103</v>
+      </c>
+      <c r="O5" s="14">
+        <v>89</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1248,7 +1153,7 @@
       <c r="C6" s="6">
         <v>376</v>
       </c>
-      <c r="D6" s="10"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="1" t="s">
         <v>74</v>
       </c>
@@ -1258,7 +1163,7 @@
       <c r="G6" s="6">
         <v>292</v>
       </c>
-      <c r="H6" s="9"/>
+      <c r="H6" s="8"/>
       <c r="I6" s="1" t="s">
         <v>119</v>
       </c>
@@ -1269,6 +1174,15 @@
         <v>8</v>
       </c>
       <c r="L6" s="5"/>
+      <c r="M6" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="N6" s="11">
+        <v>83</v>
+      </c>
+      <c r="O6" s="14">
+        <v>49</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -1280,7 +1194,7 @@
       <c r="C7" s="6">
         <v>1352</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="1" t="s">
         <v>76</v>
       </c>
@@ -1290,7 +1204,7 @@
       <c r="G7" s="6">
         <v>407</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="8"/>
       <c r="I7" s="1" t="s">
         <v>120</v>
       </c>
@@ -1301,6 +1215,15 @@
         <v>24</v>
       </c>
       <c r="L7" s="5"/>
+      <c r="M7" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="N7" s="2">
+        <v>81</v>
+      </c>
+      <c r="O7" s="13">
+        <v>39</v>
+      </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -1312,7 +1235,7 @@
       <c r="C8" s="6">
         <v>1103</v>
       </c>
-      <c r="D8" s="10"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="1" t="s">
         <v>78</v>
       </c>
@@ -1322,7 +1245,7 @@
       <c r="G8" s="6">
         <v>23</v>
       </c>
-      <c r="H8" s="9"/>
+      <c r="H8" s="8"/>
       <c r="I8" s="1" t="s">
         <v>121</v>
       </c>
@@ -1333,6 +1256,15 @@
         <v>2</v>
       </c>
       <c r="L8" s="5"/>
+      <c r="M8" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="11">
+        <v>60</v>
+      </c>
+      <c r="O8" s="12">
+        <v>38</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -1344,7 +1276,7 @@
       <c r="C9" s="6">
         <v>536</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="1" t="s">
         <v>80</v>
       </c>
@@ -1354,7 +1286,7 @@
       <c r="G9" s="6">
         <v>404</v>
       </c>
-      <c r="H9" s="9"/>
+      <c r="H9" s="8"/>
       <c r="I9" s="1" t="s">
         <v>122</v>
       </c>
@@ -1365,6 +1297,15 @@
         <v>9</v>
       </c>
       <c r="L9" s="5"/>
+      <c r="M9" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="N9" s="11">
+        <v>50</v>
+      </c>
+      <c r="O9" s="13">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1376,7 +1317,7 @@
       <c r="C10" s="6">
         <v>540</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="9"/>
       <c r="E10" s="1" t="s">
         <v>82</v>
       </c>
@@ -1386,7 +1327,7 @@
       <c r="G10" s="6">
         <v>159</v>
       </c>
-      <c r="H10" s="9"/>
+      <c r="H10" s="8"/>
       <c r="I10" s="1" t="s">
         <v>123</v>
       </c>
@@ -1397,6 +1338,15 @@
         <v>19</v>
       </c>
       <c r="L10" s="5"/>
+      <c r="M10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="N10" s="2">
+        <v>47</v>
+      </c>
+      <c r="O10" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1408,7 +1358,7 @@
       <c r="C11" s="6">
         <v>10</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="9"/>
       <c r="E11" s="1" t="s">
         <v>84</v>
       </c>
@@ -1418,7 +1368,7 @@
       <c r="G11" s="6">
         <v>133</v>
       </c>
-      <c r="H11" s="9"/>
+      <c r="H11" s="8"/>
       <c r="I11" s="1" t="s">
         <v>124</v>
       </c>
@@ -1429,6 +1379,15 @@
         <v>21</v>
       </c>
       <c r="L11" s="5"/>
+      <c r="M11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="N11" s="2">
+        <v>35</v>
+      </c>
+      <c r="O11" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -1440,7 +1399,7 @@
       <c r="C12" s="6">
         <v>741</v>
       </c>
-      <c r="D12" s="10"/>
+      <c r="D12" s="9"/>
       <c r="E12" s="1" t="s">
         <v>86</v>
       </c>
@@ -1450,7 +1409,7 @@
       <c r="G12" s="6">
         <v>4</v>
       </c>
-      <c r="H12" s="9"/>
+      <c r="H12" s="8"/>
       <c r="I12" s="1" t="s">
         <v>125</v>
       </c>
@@ -1461,6 +1420,15 @@
         <v>12</v>
       </c>
       <c r="L12" s="5"/>
+      <c r="M12" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="N12" s="2">
+        <v>31</v>
+      </c>
+      <c r="O12" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1472,7 +1440,7 @@
       <c r="C13" s="6">
         <v>591</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="9"/>
       <c r="E13" s="1" t="s">
         <v>88</v>
       </c>
@@ -1482,7 +1450,7 @@
       <c r="G13" s="6">
         <v>359</v>
       </c>
-      <c r="H13" s="9"/>
+      <c r="H13" s="8"/>
       <c r="I13" s="1" t="s">
         <v>126</v>
       </c>
@@ -1493,6 +1461,15 @@
         <v>12</v>
       </c>
       <c r="L13" s="5"/>
+      <c r="M13" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N13" s="2">
+        <v>21</v>
+      </c>
+      <c r="O13" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -1504,7 +1481,7 @@
       <c r="C14" s="6">
         <v>40</v>
       </c>
-      <c r="D14" s="10"/>
+      <c r="D14" s="9"/>
       <c r="E14" s="1" t="s">
         <v>90</v>
       </c>
@@ -1514,7 +1491,7 @@
       <c r="G14" s="6">
         <v>26</v>
       </c>
-      <c r="H14" s="9"/>
+      <c r="H14" s="8"/>
       <c r="I14" s="1" t="s">
         <v>127</v>
       </c>
@@ -1525,6 +1502,15 @@
         <v>9</v>
       </c>
       <c r="L14" s="5"/>
+      <c r="M14" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="N14" s="2">
+        <v>15</v>
+      </c>
+      <c r="O14" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -1536,7 +1522,7 @@
       <c r="C15" s="6">
         <v>31</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="9"/>
       <c r="E15" s="1" t="s">
         <v>92</v>
       </c>
@@ -1546,7 +1532,7 @@
       <c r="G15" s="6">
         <v>55</v>
       </c>
-      <c r="H15" s="9"/>
+      <c r="H15" s="8"/>
       <c r="I15" s="1" t="s">
         <v>128</v>
       </c>
@@ -1557,6 +1543,15 @@
         <v>3</v>
       </c>
       <c r="L15" s="5"/>
+      <c r="M15" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="N15" s="2">
+        <v>14</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1568,7 +1563,7 @@
       <c r="C16" s="6">
         <v>2479</v>
       </c>
-      <c r="D16" s="10"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="1" t="s">
         <v>94</v>
       </c>
@@ -1578,7 +1573,7 @@
       <c r="G16" s="6">
         <v>77</v>
       </c>
-      <c r="H16" s="9"/>
+      <c r="H16" s="8"/>
       <c r="I16" s="1" t="s">
         <v>129</v>
       </c>
@@ -1590,7 +1585,7 @@
       </c>
       <c r="L16" s="5"/>
     </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1600,7 +1595,7 @@
       <c r="C17" s="6">
         <v>41</v>
       </c>
-      <c r="D17" s="10"/>
+      <c r="D17" s="9"/>
       <c r="E17" s="1" t="s">
         <v>96</v>
       </c>
@@ -1610,16 +1605,7 @@
       <c r="G17" s="6">
         <v>275</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>131</v>
-      </c>
+      <c r="H17" s="8"/>
       <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1632,7 +1618,7 @@
       <c r="C18" s="6">
         <v>98</v>
       </c>
-      <c r="D18" s="10"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="1" t="s">
         <v>98</v>
       </c>
@@ -1642,16 +1628,7 @@
       <c r="G18" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="K18" s="17">
-        <v>610</v>
-      </c>
+      <c r="H18" s="8"/>
       <c r="L18" s="5"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1664,7 +1641,7 @@
       <c r="C19" s="6">
         <v>173</v>
       </c>
-      <c r="D19" s="10"/>
+      <c r="D19" s="9"/>
       <c r="E19" s="1" t="s">
         <v>100</v>
       </c>
@@ -1674,16 +1651,7 @@
       <c r="G19" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="19">
-        <v>122</v>
-      </c>
-      <c r="K19" s="20">
-        <v>14</v>
-      </c>
+      <c r="H19" s="8"/>
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1696,7 +1664,7 @@
       <c r="C20" s="6">
         <v>31</v>
       </c>
-      <c r="D20" s="10"/>
+      <c r="D20" s="9"/>
       <c r="E20" s="1" t="s">
         <v>102</v>
       </c>
@@ -1706,16 +1674,7 @@
       <c r="G20" s="6">
         <v>6</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="J20" s="19">
-        <v>113</v>
-      </c>
-      <c r="K20" s="20">
-        <v>3</v>
-      </c>
+      <c r="H20" s="8"/>
       <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1728,7 +1687,7 @@
       <c r="C21" s="6">
         <v>582</v>
       </c>
-      <c r="D21" s="10"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="1" t="s">
         <v>104</v>
       </c>
@@ -1738,19 +1697,10 @@
       <c r="G21" s="6">
         <v>91</v>
       </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="J21" s="19">
-        <v>103</v>
-      </c>
-      <c r="K21" s="20">
-        <v>89</v>
-      </c>
+      <c r="H21" s="8"/>
       <c r="L21" s="5"/>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
@@ -1760,7 +1710,7 @@
       <c r="C22" s="6">
         <v>365</v>
       </c>
-      <c r="D22" s="10"/>
+      <c r="D22" s="9"/>
       <c r="E22" s="1" t="s">
         <v>106</v>
       </c>
@@ -1770,19 +1720,10 @@
       <c r="G22" s="6">
         <v>3</v>
       </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J22" s="22">
-        <v>83</v>
-      </c>
-      <c r="K22" s="23">
-        <v>49</v>
-      </c>
+      <c r="H22" s="8"/>
       <c r="L22" s="5"/>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
@@ -1792,7 +1733,7 @@
       <c r="C23" s="6">
         <v>6</v>
       </c>
-      <c r="D23" s="10"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="1" t="s">
         <v>108</v>
       </c>
@@ -1802,19 +1743,10 @@
       <c r="G23" s="6">
         <v>46</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="2">
-        <v>81</v>
-      </c>
-      <c r="K23" s="1">
-        <v>39</v>
-      </c>
+      <c r="H23" s="8"/>
       <c r="L23" s="5"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
@@ -1824,7 +1756,7 @@
       <c r="C24" s="6">
         <v>109</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="1" t="s">
         <v>109</v>
       </c>
@@ -1834,16 +1766,7 @@
       <c r="G24" s="6">
         <v>110</v>
       </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="13">
-        <v>60</v>
-      </c>
-      <c r="K24" s="14">
-        <v>38</v>
-      </c>
+      <c r="H24" s="8"/>
       <c r="L24" s="5"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1856,7 +1779,7 @@
       <c r="C25" s="6">
         <v>93</v>
       </c>
-      <c r="D25" s="10"/>
+      <c r="D25" s="9"/>
       <c r="E25" s="1" t="s">
         <v>110</v>
       </c>
@@ -1866,16 +1789,7 @@
       <c r="G25" s="6">
         <v>24</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J25" s="2">
-        <v>50</v>
-      </c>
-      <c r="K25" s="1">
-        <v>28</v>
-      </c>
+      <c r="H25" s="8"/>
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1888,7 +1802,7 @@
       <c r="C26" s="6">
         <v>16</v>
       </c>
-      <c r="D26" s="10"/>
+      <c r="D26" s="9"/>
       <c r="E26" s="1" t="s">
         <v>111</v>
       </c>
@@ -1898,16 +1812,7 @@
       <c r="G26" s="6">
         <v>13</v>
       </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="J26" s="2">
-        <v>47</v>
-      </c>
-      <c r="K26" s="1">
-        <v>4</v>
-      </c>
+      <c r="H26" s="8"/>
       <c r="L26" s="5"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1920,20 +1825,11 @@
       <c r="C27" s="6">
         <v>23</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="9"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J27" s="2">
-        <v>35</v>
-      </c>
-      <c r="K27" s="1">
-        <v>11</v>
-      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="8"/>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1946,20 +1842,11 @@
       <c r="C28" s="6">
         <v>3467</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J28" s="2">
-        <v>31</v>
-      </c>
-      <c r="K28" s="1">
-        <v>12</v>
-      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="8"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1971,20 +1858,11 @@
       <c r="C29" s="6">
         <v>12</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J29" s="2">
-        <v>21</v>
-      </c>
-      <c r="K29" s="1">
-        <v>18</v>
-      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="8"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1996,20 +1874,11 @@
       <c r="C30" s="6">
         <v>290</v>
       </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J30" s="2">
-        <v>15</v>
-      </c>
-      <c r="K30" s="1">
-        <v>3</v>
-      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="8"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -2021,20 +1890,11 @@
       <c r="C31" s="6">
         <v>29</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J31" s="2">
-        <v>14</v>
-      </c>
-      <c r="K31" s="1">
-        <v>3</v>
-      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="8"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2046,16 +1906,16 @@
       <c r="C32" s="6">
         <v>269</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
@@ -2065,16 +1925,16 @@
       <c r="C33" s="6">
         <v>4</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
@@ -2084,80 +1944,93 @@
       <c r="C34" s="6">
         <v>6</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="F36" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="G36" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F36" s="8" t="s">
+      <c r="H36" s="8"/>
+      <c r="I36" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="K36" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="H36" s="9"/>
-      <c r="I36" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M36" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="6">
+        <v>19</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="6">
+      <c r="G37" s="6">
         <v>376</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="6">
-        <v>19</v>
-      </c>
-      <c r="H37" s="9"/>
+      <c r="H37" s="8"/>
       <c r="I37" s="1" t="s">
         <v>12</v>
       </c>
@@ -2167,28 +2040,37 @@
       <c r="K37" s="6">
         <v>1103</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M37" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="N37" s="15">
+        <v>0.61</v>
+      </c>
+      <c r="O37" s="15">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6">
+        <v>1049</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="6">
+      <c r="G38" s="6">
         <v>676</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="6">
-        <v>1049</v>
-      </c>
-      <c r="H38" s="9"/>
+      <c r="H38" s="8"/>
       <c r="I38" s="1" t="s">
         <v>20</v>
       </c>
@@ -2198,28 +2080,37 @@
       <c r="K38" s="6">
         <v>741</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M38" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="N38" s="15">
+        <v>0.6</v>
+      </c>
+      <c r="O38" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="6">
+        <v>676</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="6">
+      <c r="G39" s="6">
         <v>41</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G39" s="6">
-        <v>676</v>
-      </c>
-      <c r="H39" s="9"/>
+      <c r="H39" s="8"/>
       <c r="I39" s="1" t="s">
         <v>76</v>
       </c>
@@ -2229,28 +2120,37 @@
       <c r="K39" s="6">
         <v>407</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M39" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="N39" s="15">
+        <v>0.59</v>
+      </c>
+      <c r="O39" s="17">
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" s="6">
+        <v>536</v>
+      </c>
+      <c r="D40" s="8"/>
+      <c r="E40" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="6">
+      <c r="G40" s="6">
         <v>16</v>
       </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="6">
-        <v>536</v>
-      </c>
-      <c r="H40" s="9"/>
+      <c r="H40" s="8"/>
       <c r="I40" s="1" t="s">
         <v>46</v>
       </c>
@@ -2260,28 +2160,37 @@
       <c r="K40" s="6">
         <v>93</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M40" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="N40" s="15">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O40" s="15">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="6">
+        <v>31</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C41" s="6">
+      <c r="G41" s="6">
         <v>12</v>
       </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G41" s="6">
-        <v>31</v>
-      </c>
-      <c r="H41" s="9"/>
+      <c r="H41" s="8"/>
       <c r="I41" s="1" t="s">
         <v>51</v>
       </c>
@@ -2291,59 +2200,77 @@
       <c r="K41" s="6">
         <v>23</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M41" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="N41" s="15">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O41" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>41</v>
+      </c>
+      <c r="D42" s="8"/>
+      <c r="E42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="6">
+      <c r="G42" s="6">
         <v>404</v>
       </c>
-      <c r="D42" s="9"/>
-      <c r="E42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G42" s="6">
-        <v>41</v>
-      </c>
-      <c r="H42" s="9"/>
-      <c r="I42" s="8" t="s">
+      <c r="H42" s="8"/>
+      <c r="I42" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J42" s="8" t="s">
+      <c r="J42" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K42" s="8" t="s">
+      <c r="K42" s="7" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="M42" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N42" s="15">
+        <v>0.51</v>
+      </c>
+      <c r="O42" s="15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="6">
+        <v>16</v>
+      </c>
+      <c r="D43" s="8"/>
+      <c r="E43" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C43" s="6">
+      <c r="G43" s="6">
         <v>4</v>
       </c>
-      <c r="D43" s="9"/>
-      <c r="E43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G43" s="6">
-        <v>16</v>
-      </c>
-      <c r="H43" s="9"/>
+      <c r="H43" s="8"/>
       <c r="I43" s="1" t="s">
         <v>16</v>
       </c>
@@ -2353,28 +2280,29 @@
       <c r="K43" s="6">
         <v>540</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="O43" s="16"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="6">
+        <v>12</v>
+      </c>
+      <c r="D44" s="8"/>
+      <c r="E44" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="6">
+      <c r="G44" s="6">
         <v>6</v>
       </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G44" s="6">
-        <v>12</v>
-      </c>
-      <c r="H44" s="9"/>
+      <c r="H44" s="8"/>
       <c r="I44" s="1" t="s">
         <v>22</v>
       </c>
@@ -2385,27 +2313,27 @@
         <v>591</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="6">
+        <v>23</v>
+      </c>
+      <c r="D45" s="8"/>
+      <c r="E45" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C45" s="6">
+      <c r="G45" s="6">
         <v>55</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G45" s="6">
-        <v>23</v>
-      </c>
-      <c r="H45" s="9"/>
+      <c r="H45" s="8"/>
       <c r="I45" s="1" t="s">
         <v>74</v>
       </c>
@@ -2416,27 +2344,27 @@
         <v>292</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="6">
+        <v>404</v>
+      </c>
+      <c r="D46" s="8"/>
+      <c r="E46" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="6">
+      <c r="G46" s="6">
         <v>77</v>
       </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G46" s="6">
-        <v>404</v>
-      </c>
-      <c r="H46" s="9"/>
+      <c r="H46" s="8"/>
       <c r="I46" s="1" t="s">
         <v>96</v>
       </c>
@@ -2447,58 +2375,58 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="6">
+        <v>4</v>
+      </c>
+      <c r="D47" s="8"/>
+      <c r="E47" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B47" s="2">
+      <c r="F47" s="2">
         <v>984</v>
       </c>
-      <c r="C47" s="6">
+      <c r="G47" s="6">
         <v>46</v>
       </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G47" s="6">
-        <v>4</v>
-      </c>
-      <c r="H47" s="9"/>
-      <c r="I47" s="8" t="s">
+      <c r="H47" s="8"/>
+      <c r="I47" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J47" s="8" t="s">
+      <c r="J47" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="K47" s="8" t="s">
+      <c r="K47" s="7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="6">
+        <v>6</v>
+      </c>
+      <c r="D48" s="8"/>
+      <c r="E48" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B48" s="2">
+      <c r="F48" s="2">
         <v>113</v>
       </c>
-      <c r="C48" s="1">
+      <c r="G48" s="1">
         <v>3</v>
       </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G48" s="6">
-        <v>6</v>
-      </c>
-      <c r="H48" s="9"/>
+      <c r="H48" s="8"/>
       <c r="I48" s="1" t="s">
         <v>57</v>
       </c>
@@ -2510,26 +2438,26 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="6">
+        <v>55</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="2">
+      <c r="F49" s="2">
         <v>103</v>
       </c>
-      <c r="C49" s="1">
+      <c r="G49" s="1">
         <v>89</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="6">
-        <v>55</v>
-      </c>
-      <c r="H49" s="9"/>
+      <c r="H49" s="8"/>
       <c r="I49" s="1" t="s">
         <v>84</v>
       </c>
@@ -2541,175 +2469,166 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B50" s="2">
+        <v>122</v>
+      </c>
+      <c r="C50" s="1">
+        <v>14</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B50" s="1">
+      <c r="F50" s="1">
         <v>89</v>
       </c>
-      <c r="C50" s="1">
+      <c r="G50" s="1">
         <v>48</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="F50" s="2">
-        <v>122</v>
-      </c>
-      <c r="G50" s="1">
-        <v>14</v>
-      </c>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="2">
+        <v>113</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="8"/>
+      <c r="E51" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B51" s="2">
+      <c r="F51" s="2">
         <v>83</v>
       </c>
-      <c r="C51" s="1">
+      <c r="G51" s="1">
         <v>49</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="2">
-        <v>113</v>
-      </c>
-      <c r="G51" s="1">
-        <v>3</v>
-      </c>
-      <c r="H51" s="9"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="6" t="s">
+      <c r="A52" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F52" s="2">
+      <c r="B52" s="2">
         <v>103</v>
       </c>
-      <c r="G52" s="1">
+      <c r="C52" s="1">
         <v>89</v>
       </c>
-      <c r="H52" s="9"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
+      <c r="D52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="6" t="s">
+      <c r="A53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F53" s="2">
+      <c r="B53" s="2">
         <v>60</v>
       </c>
-      <c r="G53" s="1">
+      <c r="C53" s="1">
         <v>38</v>
       </c>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
+      <c r="D53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="9"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="6" t="s">
+      <c r="A54" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F54" s="2">
+      <c r="B54" s="2">
         <v>50</v>
       </c>
-      <c r="G54" s="1">
+      <c r="C54" s="1">
         <v>28</v>
       </c>
-      <c r="H54" s="9"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
+      <c r="D54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E55" s="6" t="s">
+      <c r="A55" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F55" s="2">
+      <c r="B55" s="2">
         <v>47</v>
       </c>
-      <c r="G55" s="1">
+      <c r="C55" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E56" s="1" t="s">
+      <c r="A56" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F56" s="1">
+      <c r="B56" s="1">
         <v>45</v>
       </c>
-      <c r="G56" s="1">
+      <c r="C56" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E57" s="1" t="s">
+      <c r="A57" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F57" s="1">
+      <c r="B57" s="1">
         <v>28</v>
       </c>
-      <c r="G57" s="1">
+      <c r="C57" s="1">
         <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E58" s="1" t="s">
+      <c r="A58" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F58" s="1">
+      <c r="B58" s="1">
         <v>26</v>
       </c>
-      <c r="G58" s="1">
+      <c r="C58" s="1">
         <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E59" s="6" t="s">
+      <c r="A59" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F59" s="2">
+      <c r="B59" s="2">
         <v>21</v>
       </c>
-      <c r="G59" s="1">
+      <c r="C59" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E60" s="1" t="s">
+      <c r="A60" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F60" s="1">
+      <c r="B60" s="1">
         <v>16</v>
       </c>
-      <c r="G60" s="1">
+      <c r="C60" s="1">
         <v>3</v>
       </c>
     </row>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="157">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -921,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
@@ -935,8 +935,10 @@
     <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" customWidth="1"/>
     <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1915,7 +1917,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
@@ -1934,7 +1936,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
@@ -1953,7 +1955,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
@@ -1969,8 +1971,10 @@
       <c r="M35" s="10"/>
       <c r="N35" s="10"/>
       <c r="O35" s="10"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>150</v>
       </c>
@@ -2004,13 +2008,19 @@
         <v>154</v>
       </c>
       <c r="N36" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="P36" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="O36" s="7" t="s">
+      <c r="Q36" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>4</v>
       </c>
@@ -2043,14 +2053,20 @@
       <c r="M37" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="N37" s="15">
+      <c r="N37" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="O37" s="14">
+        <v>610</v>
+      </c>
+      <c r="P37" s="15">
         <v>0.61</v>
       </c>
-      <c r="O37" s="15">
+      <c r="Q37" s="15">
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -2083,14 +2099,20 @@
       <c r="M38" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38" s="11">
+        <v>113</v>
+      </c>
+      <c r="O38" s="14">
+        <v>3</v>
+      </c>
+      <c r="P38" s="15">
         <v>0.6</v>
       </c>
-      <c r="O38" s="15">
+      <c r="Q38" s="15">
         <v>0.75</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>70</v>
       </c>
@@ -2123,14 +2145,20 @@
       <c r="M39" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="N39" s="15">
+      <c r="N39" s="11">
+        <v>122</v>
+      </c>
+      <c r="O39" s="14">
+        <v>14</v>
+      </c>
+      <c r="P39" s="15">
         <v>0.59</v>
       </c>
-      <c r="O39" s="17">
+      <c r="Q39" s="17">
         <v>0.77500000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>14</v>
       </c>
@@ -2163,14 +2191,20 @@
       <c r="M40" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="N40" s="15">
+      <c r="N40" s="11">
+        <v>83</v>
+      </c>
+      <c r="O40" s="14">
+        <v>49</v>
+      </c>
+      <c r="P40" s="15">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O40" s="15">
+      <c r="Q40" s="15">
         <v>0.75</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>26</v>
       </c>
@@ -2203,14 +2237,20 @@
       <c r="M41" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="N41" s="15">
+      <c r="N41" s="11">
+        <v>60</v>
+      </c>
+      <c r="O41" s="12">
+        <v>38</v>
+      </c>
+      <c r="P41" s="15">
         <v>0.56999999999999995</v>
       </c>
-      <c r="O41" s="15">
+      <c r="Q41" s="15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>30</v>
       </c>
@@ -2243,14 +2283,20 @@
       <c r="M42" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="N42" s="15">
+      <c r="N42" s="11">
+        <v>103</v>
+      </c>
+      <c r="O42" s="14">
+        <v>89</v>
+      </c>
+      <c r="P42" s="15">
         <v>0.51</v>
       </c>
-      <c r="O42" s="15">
+      <c r="Q42" s="15">
         <v>0.7</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -2282,7 +2328,7 @@
       </c>
       <c r="O43" s="16"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>55</v>
       </c>
@@ -2313,7 +2359,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>78</v>
       </c>
@@ -2344,7 +2390,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>80</v>
       </c>
@@ -2375,7 +2421,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
@@ -2406,7 +2452,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>65</v>
       </c>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,10 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24750" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24750" windowHeight="12330" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Запросы" sheetId="1" r:id="rId1"/>
+    <sheet name="Категории запросов" sheetId="2" r:id="rId2"/>
+    <sheet name="Title и Description" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="164">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -488,13 +490,34 @@
     <t>ДЛЯ ДЕТЕЙ</t>
   </si>
   <si>
-    <t>ГЛАВНЫЕ ЗАПРОСЫ</t>
-  </si>
-  <si>
-    <t>MEGAINDEX</t>
-  </si>
-  <si>
-    <t>MAJENTO</t>
+    <t>СТРАНИЦА</t>
+  </si>
+  <si>
+    <t>Главная</t>
+  </si>
+  <si>
+    <t>Обувь</t>
+  </si>
+  <si>
+    <t>Одежда</t>
+  </si>
+  <si>
+    <t>abibas официальный сайт abibas интернет магазин abibas купить бесплатно</t>
+  </si>
+  <si>
+    <t>тут есть abibas можно купить abibas или посмотреть интернет магазин abibas заходите на официальный сайт abibas короче</t>
+  </si>
+  <si>
+    <t>abibas официальный сайт лучшая спортивная обувь among us obama abibas купить</t>
+  </si>
+  <si>
+    <t>это магазина abibas официальный сайт можно купить abibas посмотреть на него здесь лучшая спортивная обувь и вполне хорошая детская обувь</t>
+  </si>
+  <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
   </si>
 </sst>
 </file>
@@ -570,12 +593,147 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -585,7 +743,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -608,7 +766,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -629,6 +786,33 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -921,27 +1105,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:AG34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="13" max="13" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" customWidth="1"/>
     <col min="15" max="15" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="50" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.42578125" customWidth="1"/>
+    <col min="21" max="21" width="50" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="42" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" customWidth="1"/>
+    <col min="27" max="27" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>48</v>
       </c>
@@ -971,17 +1171,13 @@
       <c r="K1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="7"/>
+      <c r="AE1" s="7"/>
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="7"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1012,17 +1208,13 @@
         <v>944</v>
       </c>
       <c r="L2" s="5"/>
-      <c r="M2" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="O2" s="14">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="10"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1053,17 +1245,13 @@
         <v>58</v>
       </c>
       <c r="L3" s="5"/>
-      <c r="M3" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="N3" s="11">
-        <v>122</v>
-      </c>
-      <c r="O3" s="14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="14"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1094,17 +1282,13 @@
         <v>48</v>
       </c>
       <c r="L4" s="5"/>
-      <c r="M4" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="N4" s="11">
-        <v>113</v>
-      </c>
-      <c r="O4" s="14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="13"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="16"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1135,17 +1319,13 @@
         <v>29</v>
       </c>
       <c r="L5" s="5"/>
-      <c r="M5" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="N5" s="11">
-        <v>103</v>
-      </c>
-      <c r="O5" s="14">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1176,17 +1356,13 @@
         <v>8</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="N6" s="11">
-        <v>83</v>
-      </c>
-      <c r="O6" s="14">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1217,17 +1393,13 @@
         <v>24</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="N7" s="2">
-        <v>81</v>
-      </c>
-      <c r="O7" s="13">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1258,17 +1430,9 @@
         <v>2</v>
       </c>
       <c r="L8" s="5"/>
-      <c r="M8" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="N8" s="11">
-        <v>60</v>
-      </c>
-      <c r="O8" s="12">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="AE8" s="15"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1299,17 +1463,8 @@
         <v>9</v>
       </c>
       <c r="L9" s="5"/>
-      <c r="M9" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="N9" s="11">
-        <v>50</v>
-      </c>
-      <c r="O9" s="13">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1340,17 +1495,8 @@
         <v>19</v>
       </c>
       <c r="L10" s="5"/>
-      <c r="M10" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="N10" s="2">
-        <v>47</v>
-      </c>
-      <c r="O10" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1381,17 +1527,8 @@
         <v>21</v>
       </c>
       <c r="L11" s="5"/>
-      <c r="M11" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2">
-        <v>35</v>
-      </c>
-      <c r="O11" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1422,17 +1559,8 @@
         <v>12</v>
       </c>
       <c r="L12" s="5"/>
-      <c r="M12" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="N12" s="2">
-        <v>31</v>
-      </c>
-      <c r="O12" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1463,17 +1591,8 @@
         <v>12</v>
       </c>
       <c r="L13" s="5"/>
-      <c r="M13" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="N13" s="2">
-        <v>21</v>
-      </c>
-      <c r="O13" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1504,17 +1623,8 @@
         <v>9</v>
       </c>
       <c r="L14" s="5"/>
-      <c r="M14" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="N14" s="2">
-        <v>15</v>
-      </c>
-      <c r="O14" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
@@ -1545,17 +1655,8 @@
         <v>3</v>
       </c>
       <c r="L15" s="5"/>
-      <c r="M15" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="N15" s="2">
-        <v>14</v>
-      </c>
-      <c r="O15" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -1608,6 +1709,15 @@
         <v>275</v>
       </c>
       <c r="H17" s="8"/>
+      <c r="I17" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1631,6 +1741,15 @@
         <v>112</v>
       </c>
       <c r="H18" s="8"/>
+      <c r="I18" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="13">
+        <v>610</v>
+      </c>
       <c r="L18" s="5"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1654,6 +1773,15 @@
         <v>113</v>
       </c>
       <c r="H19" s="8"/>
+      <c r="I19" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="10">
+        <v>122</v>
+      </c>
+      <c r="K19" s="13">
+        <v>14</v>
+      </c>
       <c r="L19" s="5"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1677,6 +1805,15 @@
         <v>6</v>
       </c>
       <c r="H20" s="8"/>
+      <c r="I20" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="10">
+        <v>113</v>
+      </c>
+      <c r="K20" s="13">
+        <v>3</v>
+      </c>
       <c r="L20" s="5"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1700,6 +1837,15 @@
         <v>91</v>
       </c>
       <c r="H21" s="8"/>
+      <c r="I21" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="J21" s="10">
+        <v>103</v>
+      </c>
+      <c r="K21" s="13">
+        <v>89</v>
+      </c>
       <c r="L21" s="5"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1723,6 +1869,15 @@
         <v>3</v>
       </c>
       <c r="H22" s="8"/>
+      <c r="I22" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="10">
+        <v>83</v>
+      </c>
+      <c r="K22" s="13">
+        <v>49</v>
+      </c>
       <c r="L22" s="5"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1746,6 +1901,15 @@
         <v>46</v>
       </c>
       <c r="H23" s="8"/>
+      <c r="I23" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="J23" s="2">
+        <v>81</v>
+      </c>
+      <c r="K23" s="12">
+        <v>39</v>
+      </c>
       <c r="L23" s="5"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1769,6 +1933,15 @@
         <v>110</v>
       </c>
       <c r="H24" s="8"/>
+      <c r="I24" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="J24" s="10">
+        <v>60</v>
+      </c>
+      <c r="K24" s="11">
+        <v>38</v>
+      </c>
       <c r="L24" s="5"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1792,6 +1965,15 @@
         <v>24</v>
       </c>
       <c r="H25" s="8"/>
+      <c r="I25" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="10">
+        <v>50</v>
+      </c>
+      <c r="K25" s="12">
+        <v>28</v>
+      </c>
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1815,6 +1997,15 @@
         <v>13</v>
       </c>
       <c r="H26" s="8"/>
+      <c r="I26" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="J26" s="2">
+        <v>47</v>
+      </c>
+      <c r="K26" s="1">
+        <v>4</v>
+      </c>
       <c r="L26" s="5"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1832,6 +2023,15 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="8"/>
+      <c r="I27" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J27" s="2">
+        <v>35</v>
+      </c>
+      <c r="K27" s="1">
+        <v>11</v>
+      </c>
       <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1849,6 +2049,15 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="8"/>
+      <c r="I28" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="J28" s="2">
+        <v>31</v>
+      </c>
+      <c r="K28" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -1865,6 +2074,15 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="8"/>
+      <c r="I29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J29" s="2">
+        <v>21</v>
+      </c>
+      <c r="K29" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1881,6 +2099,15 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="8"/>
+      <c r="I30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J30" s="2">
+        <v>15</v>
+      </c>
+      <c r="K30" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1897,6 +2124,15 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="8"/>
+      <c r="I31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J31" s="2">
+        <v>14</v>
+      </c>
+      <c r="K31" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -1913,11 +2149,8 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>63</v>
       </c>
@@ -1936,7 +2169,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>65</v>
       </c>
@@ -1955,731 +2188,685 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="N36" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="O36" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="P36" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q36" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="6">
-        <v>19</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G37" s="6">
-        <v>376</v>
-      </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K37" s="6">
-        <v>1103</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="N37" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="O37" s="14">
-        <v>610</v>
-      </c>
-      <c r="P37" s="15">
-        <v>0.61</v>
-      </c>
-      <c r="Q37" s="15">
-        <v>0.56999999999999995</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="6">
-        <v>1049</v>
-      </c>
-      <c r="D38" s="8"/>
-      <c r="E38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G38" s="6">
-        <v>676</v>
-      </c>
-      <c r="H38" s="8"/>
-      <c r="I38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="6">
-        <v>741</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="N38" s="11">
-        <v>113</v>
-      </c>
-      <c r="O38" s="14">
-        <v>3</v>
-      </c>
-      <c r="P38" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="Q38" s="15">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="6">
-        <v>676</v>
-      </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G39" s="6">
-        <v>41</v>
-      </c>
-      <c r="H39" s="8"/>
-      <c r="I39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="6">
-        <v>407</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="N39" s="11">
-        <v>122</v>
-      </c>
-      <c r="O39" s="14">
-        <v>14</v>
-      </c>
-      <c r="P39" s="15">
-        <v>0.59</v>
-      </c>
-      <c r="Q39" s="17">
-        <v>0.77500000000000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="6">
-        <v>536</v>
-      </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G40" s="6">
-        <v>16</v>
-      </c>
-      <c r="H40" s="8"/>
-      <c r="I40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K40" s="6">
-        <v>93</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="N40" s="11">
-        <v>83</v>
-      </c>
-      <c r="O40" s="14">
-        <v>49</v>
-      </c>
-      <c r="P40" s="15">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="Q40" s="15">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C41" s="6">
-        <v>31</v>
-      </c>
-      <c r="D41" s="8"/>
-      <c r="E41" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" s="6">
-        <v>12</v>
-      </c>
-      <c r="H41" s="8"/>
-      <c r="I41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K41" s="6">
-        <v>23</v>
-      </c>
-      <c r="M41" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="N41" s="11">
-        <v>60</v>
-      </c>
-      <c r="O41" s="12">
-        <v>38</v>
-      </c>
-      <c r="P41" s="15">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="Q41" s="15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="6">
-        <v>41</v>
-      </c>
-      <c r="D42" s="8"/>
-      <c r="E42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G42" s="6">
-        <v>404</v>
-      </c>
-      <c r="H42" s="8"/>
-      <c r="I42" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="J42" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="N42" s="11">
-        <v>103</v>
-      </c>
-      <c r="O42" s="14">
-        <v>89</v>
-      </c>
-      <c r="P42" s="15">
-        <v>0.51</v>
-      </c>
-      <c r="Q42" s="15">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="6">
-        <v>16</v>
-      </c>
-      <c r="D43" s="8"/>
-      <c r="E43" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G43" s="6">
-        <v>4</v>
-      </c>
-      <c r="H43" s="8"/>
-      <c r="I43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" s="6">
-        <v>540</v>
-      </c>
-      <c r="O43" s="16"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="6">
-        <v>12</v>
-      </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G44" s="6">
-        <v>6</v>
-      </c>
-      <c r="H44" s="8"/>
-      <c r="I44" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K44" s="6">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" s="6">
-        <v>23</v>
-      </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G45" s="6">
-        <v>55</v>
-      </c>
-      <c r="H45" s="8"/>
-      <c r="I45" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="K45" s="6">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="6">
-        <v>404</v>
-      </c>
-      <c r="D46" s="8"/>
-      <c r="E46" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G46" s="6">
-        <v>77</v>
-      </c>
-      <c r="H46" s="8"/>
-      <c r="I46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K46" s="6">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="6">
-        <v>4</v>
-      </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F47" s="2">
-        <v>984</v>
-      </c>
-      <c r="G47" s="6">
-        <v>46</v>
-      </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="6">
-        <v>6</v>
-      </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F48" s="2">
-        <v>113</v>
-      </c>
-      <c r="G48" s="1">
-        <v>3</v>
-      </c>
-      <c r="H48" s="8"/>
-      <c r="I48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K48" s="6">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C49" s="6">
-        <v>55</v>
-      </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F49" s="2">
-        <v>103</v>
-      </c>
-      <c r="G49" s="1">
-        <v>89</v>
-      </c>
-      <c r="H49" s="8"/>
-      <c r="I49" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K49" s="6">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B50" s="2">
-        <v>122</v>
-      </c>
-      <c r="C50" s="1">
-        <v>14</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F50" s="1">
-        <v>89</v>
-      </c>
-      <c r="G50" s="1">
-        <v>48</v>
-      </c>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B51" s="2">
-        <v>113</v>
-      </c>
-      <c r="C51" s="1">
-        <v>3</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="F51" s="2">
-        <v>83</v>
-      </c>
-      <c r="G51" s="1">
-        <v>49</v>
-      </c>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" s="2">
-        <v>103</v>
-      </c>
-      <c r="C52" s="1">
-        <v>89</v>
-      </c>
-      <c r="D52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B53" s="2">
-        <v>60</v>
-      </c>
-      <c r="C53" s="1">
-        <v>38</v>
-      </c>
-      <c r="D53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="2">
-        <v>50</v>
-      </c>
-      <c r="C54" s="1">
-        <v>28</v>
-      </c>
-      <c r="D54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="2">
-        <v>47</v>
-      </c>
-      <c r="C55" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B56" s="1">
-        <v>45</v>
-      </c>
-      <c r="C56" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B57" s="1">
-        <v>28</v>
-      </c>
-      <c r="C57" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B58" s="1">
-        <v>26</v>
-      </c>
-      <c r="C58" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B59" s="2">
-        <v>21</v>
-      </c>
-      <c r="C59" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B60" s="1">
-        <v>16</v>
-      </c>
-      <c r="C60" s="1">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="47" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="8"/>
+      <c r="E1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6">
+        <v>19</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="6">
+        <v>376</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="6">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1049</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="6">
+        <v>676</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="6">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="6">
+        <v>676</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="6">
+        <v>41</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="6">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6">
+        <v>536</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="6">
+        <v>16</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="6">
+        <v>31</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="6">
+        <v>12</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="6">
+        <v>41</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="6">
+        <v>404</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="6">
+        <v>16</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="6">
+        <v>4</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="6">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="6">
+        <v>12</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="6">
+        <v>6</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="6">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="6">
+        <v>23</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="6">
+        <v>55</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="6">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="6">
+        <v>404</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="6">
+        <v>77</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" s="6">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F12" s="2">
+        <v>984</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="6">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="2">
+        <v>113</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="6">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="6">
+        <v>55</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="2">
+        <v>103</v>
+      </c>
+      <c r="G14" s="1">
+        <v>89</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="6">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15" s="2">
+        <v>122</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8"/>
+      <c r="E15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F15" s="1">
+        <v>89</v>
+      </c>
+      <c r="G15" s="1">
+        <v>48</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="2">
+        <v>113</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8"/>
+      <c r="E16" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="2">
+        <v>83</v>
+      </c>
+      <c r="G16" s="1">
+        <v>49</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="2">
+        <v>103</v>
+      </c>
+      <c r="C17" s="1">
+        <v>89</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="2">
+        <v>60</v>
+      </c>
+      <c r="C18" s="1">
+        <v>38</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B19" s="2">
+        <v>50</v>
+      </c>
+      <c r="C19" s="1">
+        <v>28</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="2">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="1">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="1">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="1">
+        <v>26</v>
+      </c>
+      <c r="C23" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="2">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="1">
+        <v>16</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" customWidth="1"/>
+    <col min="3" max="3" width="34.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="25"/>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\оптимизация\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClassUser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24750" windowHeight="12330" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
     <sheet name="Категории запросов" sheetId="2" r:id="rId2"/>
     <sheet name="Title и Description" sheetId="3" r:id="rId3"/>
+    <sheet name="Ссылки" sheetId="5" r:id="rId4"/>
+    <sheet name="Конкуренты" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="198">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -518,13 +520,118 @@
   </si>
   <si>
     <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>РЕЛЕВАНТНОСТЬ</t>
+  </si>
+  <si>
+    <t>НАШ САЙТ</t>
+  </si>
+  <si>
+    <t>ЗАПРОСЫ</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 1</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io</t>
+  </si>
+  <si>
+    <t>https://www.kant.ru/</t>
+  </si>
+  <si>
+    <t>https://georgekazanba.github.io/</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 2</t>
+  </si>
+  <si>
+    <t>https://spb.rendez-vous.ru/</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 3</t>
+  </si>
+  <si>
+    <t>https://www.planeta-sport.ru/</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 4</t>
+  </si>
+  <si>
+    <t>https://www.traektoria.ru/</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 5</t>
+  </si>
+  <si>
+    <t>https://piter.sportse.ru/</t>
+  </si>
+  <si>
+    <t>АНКОР</t>
+  </si>
+  <si>
+    <t>ЧАСТОТА АНКОРА</t>
+  </si>
+  <si>
+    <t>АДРЕС</t>
+  </si>
+  <si>
+    <t>ГЛАВНАЯ</t>
+  </si>
+  <si>
+    <t>ГJIАBHAR</t>
+  </si>
+  <si>
+    <t>ОБУВЬ</t>
+  </si>
+  <si>
+    <t>ОДЕЖДА И КОСТЮМЫ</t>
+  </si>
+  <si>
+    <t>ПP04ЕЕ</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index1.html</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index3.html</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index2.html</t>
+  </si>
+  <si>
+    <t>здесь</t>
+  </si>
+  <si>
+    <t>СПОРТИВНАЯ ОБУВЬ</t>
+  </si>
+  <si>
+    <t>СПОРТИВНАЯ ОДЕЖДА</t>
+  </si>
+  <si>
+    <t>эту</t>
+  </si>
+  <si>
+    <t>ГЛАВНАЯ СТРАНИЦА</t>
+  </si>
+  <si>
+    <t>ОДЕЖДА</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/#</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,8 +681,23 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,8 +714,13 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -736,14 +863,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -814,11 +958,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="6">
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Нейтральный" xfId="3" builtinId="28"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Плохой" xfId="5" builtinId="27"/>
+    <cellStyle name="Процентный" xfId="4" builtinId="5"/>
     <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2869,4 +3051,712 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C16" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="10" max="10" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="12" max="12" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="16.28515625" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:14" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="M2" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="N2" s="33" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="36">
+        <v>0.49</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3" s="36">
+        <v>0.49</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="J3" s="36">
+        <v>0.59</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="L3" s="36">
+        <v>0.49</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="N3" s="36">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36">
+        <v>0.27</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="36">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="35"/>
+      <c r="J4" s="36">
+        <v>0.18</v>
+      </c>
+      <c r="K4" s="35"/>
+      <c r="L4" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="M4" s="35"/>
+      <c r="N4" s="36">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36">
+        <v>0.43</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36">
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="36">
+        <v>0.21</v>
+      </c>
+      <c r="K5" s="35"/>
+      <c r="L5" s="36">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M5" s="35"/>
+      <c r="N5" s="36">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36">
+        <v>0.46</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36">
+        <v>0.63</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="36">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="36">
+        <v>0.49</v>
+      </c>
+      <c r="M6" s="35"/>
+      <c r="N6" s="36">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36">
+        <v>0.61</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36">
+        <v>0</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36">
+        <v>0</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="36">
+        <v>0</v>
+      </c>
+      <c r="K7" s="35"/>
+      <c r="L7" s="36">
+        <v>0</v>
+      </c>
+      <c r="M7" s="35"/>
+      <c r="N7" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="36">
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36">
+        <v>0.18</v>
+      </c>
+      <c r="I8" s="35"/>
+      <c r="J8" s="36">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="35"/>
+      <c r="N8" s="36">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36">
+        <v>0.51</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36">
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36">
+        <v>0.18</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="36">
+        <v>0.12</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="L9" s="36">
+        <v>0.22</v>
+      </c>
+      <c r="M9" s="35"/>
+      <c r="N9" s="36">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="37" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="36">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36">
+        <v>0</v>
+      </c>
+      <c r="I10" s="35"/>
+      <c r="J10" s="36">
+        <v>0</v>
+      </c>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36">
+        <v>0</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="36">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="36">
+        <v>0</v>
+      </c>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36">
+        <v>0</v>
+      </c>
+      <c r="I11" s="35"/>
+      <c r="J11" s="36">
+        <v>0</v>
+      </c>
+      <c r="K11" s="35"/>
+      <c r="L11" s="36">
+        <v>0</v>
+      </c>
+      <c r="M11" s="35"/>
+      <c r="N11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="36">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="36">
+        <v>0.19</v>
+      </c>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36">
+        <v>0.18</v>
+      </c>
+      <c r="I12" s="35"/>
+      <c r="J12" s="36">
+        <v>0.12</v>
+      </c>
+      <c r="K12" s="35"/>
+      <c r="L12" s="36">
+        <v>0.23</v>
+      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="36">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C3:C12"/>
+    <mergeCell ref="E3:E12"/>
+    <mergeCell ref="G3:G12"/>
+    <mergeCell ref="I3:I12"/>
+    <mergeCell ref="K3:K12"/>
+    <mergeCell ref="M3:M12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="G3" r:id="rId3"/>
+    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink ref="K3" r:id="rId5"/>
+    <hyperlink ref="M3" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+</worksheet>
 </file>
--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,14 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
     <sheet name="Категории запросов" sheetId="2" r:id="rId2"/>
-    <sheet name="Title и Description" sheetId="3" r:id="rId3"/>
-    <sheet name="Ссылки" sheetId="5" r:id="rId4"/>
-    <sheet name="Конкуренты" sheetId="4" r:id="rId5"/>
+    <sheet name="Релевантность" sheetId="6" r:id="rId3"/>
+    <sheet name="Title и Description (сниппеты)" sheetId="7" r:id="rId4"/>
+    <sheet name="Ссылки" sheetId="5" r:id="rId5"/>
+    <sheet name="Конкуренты" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="202">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -507,15 +508,9 @@
     <t>abibas официальный сайт abibas интернет магазин abibas купить бесплатно</t>
   </si>
   <si>
-    <t>тут есть abibas можно купить abibas или посмотреть интернет магазин abibas заходите на официальный сайт abibas короче</t>
-  </si>
-  <si>
     <t>abibas официальный сайт лучшая спортивная обувь among us obama abibas купить</t>
   </si>
   <si>
-    <t>это магазина abibas официальный сайт можно купить abibas посмотреть на него здесь лучшая спортивная обувь и вполне хорошая детская обувь</t>
-  </si>
-  <si>
     <t>TITLE</t>
   </si>
   <si>
@@ -622,6 +617,24 @@
   </si>
   <si>
     <t>georgekazanba.github.io/index.html</t>
+  </si>
+  <si>
+    <t>MEGAINDEX</t>
+  </si>
+  <si>
+    <t>MAJENTO</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas. В нашем интернет магазине вы можете купить нашу продукцию: от детской обуви до спортивных костюмов.</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с нашей обувью для всех полов, возрастов и сфер жизни.</t>
+  </si>
+  <si>
+    <t>abibas интернет магазин спортивной одежды abibas купить спортивная одежда</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с моделями нашей одежды и спортивными костюмами.</t>
   </si>
 </sst>
 </file>
@@ -629,9 +642,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -696,8 +709,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -719,8 +740,19 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -878,16 +910,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -946,18 +995,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -967,39 +1010,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="8">
+    <cellStyle name="40% — акцент2" xfId="7" builtinId="35"/>
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Нейтральный" xfId="3" builtinId="28"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Плохой" xfId="5" builtinId="27"/>
+    <cellStyle name="Примечание" xfId="6" builtinId="10"/>
     <cellStyle name="Процентный" xfId="4" builtinId="5"/>
     <cellStyle name="Хороший" xfId="1" builtinId="26"/>
   </cellStyles>
@@ -2999,61 +3092,301 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C5"/>
+  <dimension ref="B1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" customWidth="1"/>
-    <col min="3" max="3" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="37"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="K2" s="37"/>
+      <c r="L2" s="38"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="E3" s="42"/>
+      <c r="F3" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="I3" s="42"/>
+      <c r="J3" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="L3" s="41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="44">
+        <v>0.61</v>
+      </c>
+      <c r="D4" s="45">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="44">
+        <v>0.43</v>
+      </c>
+      <c r="H4" s="45">
+        <v>0.80800000000000005</v>
+      </c>
+      <c r="J4" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="44">
+        <v>0.59</v>
+      </c>
+      <c r="L4" s="45">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="44">
+        <v>0.59</v>
+      </c>
+      <c r="D5" s="45">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="44">
+        <v>0.42</v>
+      </c>
+      <c r="H5" s="45">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="K5" s="44">
+        <v>0.52</v>
+      </c>
+      <c r="L5" s="45">
+        <v>0.82299999999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="46" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="44">
+        <v>0.51</v>
+      </c>
+      <c r="D6" s="45">
+        <v>0.7</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="44">
+        <v>0.43</v>
+      </c>
+      <c r="H6" s="45">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="45">
+        <v>0.79800000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="44">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="D7" s="45">
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
+      <c r="J7" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="K7" s="44">
+        <v>0.39</v>
+      </c>
+      <c r="L7" s="45">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="44">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D8" s="45">
+        <v>0.7</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="K8" s="48"/>
+      <c r="L8" s="49"/>
+    </row>
+    <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="44">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D9" s="45">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
+    </row>
+    <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="B10:D10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:E6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.140625" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" customWidth="1"/>
+    <col min="5" max="5" width="46.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="2:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="B4" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="26"/>
+    </row>
+    <row r="5" spans="2:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" s="26"/>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3064,29 +3397,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" s="15">
         <v>1</v>
@@ -3094,32 +3427,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C4" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>185</v>
+      <c r="A5" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C5" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>186</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>188</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -3127,10 +3460,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C7" s="15">
         <v>1</v>
@@ -3138,50 +3471,50 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C8" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
-        <v>191</v>
+      <c r="A9" s="26" t="s">
+        <v>189</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C9" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>192</v>
+      <c r="A10" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C10" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C12" s="15">
         <v>1</v>
@@ -3189,32 +3522,32 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C13" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>185</v>
+      <c r="A14" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C14" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>186</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>188</v>
       </c>
       <c r="C15" s="15">
         <v>1</v>
@@ -3222,10 +3555,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -3233,50 +3566,50 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>194</v>
+      <c r="A18" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>192</v>
+      <c r="A19" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C19" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
+      <c r="A20" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C21" s="15">
         <v>1</v>
@@ -3284,32 +3617,32 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C22" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>185</v>
+      <c r="A23" s="26" t="s">
+        <v>183</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C23" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>186</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>188</v>
       </c>
       <c r="C24" s="15">
         <v>1</v>
@@ -3317,10 +3650,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C25" s="15">
         <v>1</v>
@@ -3328,32 +3661,32 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C26" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
-        <v>194</v>
+      <c r="A27" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C27" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
-        <v>191</v>
+      <c r="A28" s="26" t="s">
+        <v>189</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C28" s="15">
         <v>1</v>
@@ -3370,12 +3703,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="B1:N13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
@@ -3396,357 +3729,357 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" s="32" t="s">
+      <c r="B2" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" s="33" t="s">
+      <c r="F2" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="N2" s="30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="E3" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="L2" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="M2" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="N2" s="33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="34" t="s">
+      <c r="F3" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="J3" s="32">
+        <v>0.59</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="L3" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="N3" s="32">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="35"/>
+      <c r="D4" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="35"/>
+      <c r="F4" s="32">
+        <v>0.27</v>
+      </c>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="35"/>
+      <c r="J4" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="K4" s="35"/>
+      <c r="L4" s="32">
+        <v>0.3</v>
+      </c>
+      <c r="M4" s="35"/>
+      <c r="N4" s="32">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="32">
+        <v>0.43</v>
+      </c>
+      <c r="E5" s="35"/>
+      <c r="F5" s="32">
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="32">
+        <v>0.21</v>
+      </c>
+      <c r="K5" s="35"/>
+      <c r="L5" s="32">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M5" s="35"/>
+      <c r="N5" s="32">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="32">
+        <v>0.46</v>
+      </c>
+      <c r="E6" s="35"/>
+      <c r="F6" s="32">
+        <v>0.63</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="32">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="35"/>
+      <c r="L6" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="M6" s="35"/>
+      <c r="N6" s="32">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="32">
+        <v>0.61</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="32">
         <v>0</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="D3" s="36">
-        <v>0.49</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="F3" s="36">
-        <v>0.49</v>
-      </c>
-      <c r="G3" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="36">
+      <c r="G7" s="35"/>
+      <c r="H7" s="32">
+        <v>0</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="32">
+        <v>0</v>
+      </c>
+      <c r="K7" s="35"/>
+      <c r="L7" s="32">
+        <v>0</v>
+      </c>
+      <c r="M7" s="35"/>
+      <c r="N7" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="32">
+        <v>0.59</v>
+      </c>
+      <c r="E8" s="35"/>
+      <c r="F8" s="32">
         <v>0.01</v>
       </c>
-      <c r="I3" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="J3" s="36">
-        <v>0.59</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="L3" s="36">
-        <v>0.49</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="N3" s="36">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="34" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="36">
-        <v>0.27</v>
-      </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="36">
+      <c r="G8" s="35"/>
+      <c r="H8" s="32">
         <v>0.18</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="36">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36">
-        <v>0.43</v>
-      </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36">
+      <c r="I8" s="35"/>
+      <c r="J8" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="35"/>
+      <c r="L8" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="35"/>
+      <c r="N8" s="32">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="32">
+        <v>0.51</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="32">
         <v>0.19</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36">
-        <v>0.15</v>
-      </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36">
-        <v>0.21</v>
-      </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="36">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36">
-        <v>0.46</v>
-      </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="36">
-        <v>0.63</v>
-      </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="36">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36">
-        <v>0.64</v>
-      </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36">
-        <v>0.49</v>
-      </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="36">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="36">
-        <v>0.61</v>
-      </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36">
+      <c r="G9" s="35"/>
+      <c r="H9" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="K9" s="35"/>
+      <c r="L9" s="32">
+        <v>0.22</v>
+      </c>
+      <c r="M9" s="35"/>
+      <c r="N9" s="32">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="32">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E10" s="35"/>
+      <c r="F10" s="32">
         <v>0</v>
       </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="36">
+      <c r="G10" s="35"/>
+      <c r="H10" s="32">
         <v>0</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36">
+      <c r="I10" s="35"/>
+      <c r="J10" s="32">
         <v>0</v>
       </c>
-      <c r="K7" s="35"/>
-      <c r="L7" s="36">
+      <c r="K10" s="35"/>
+      <c r="L10" s="32">
         <v>0</v>
       </c>
-      <c r="M7" s="35"/>
-      <c r="N7" s="36">
+      <c r="M10" s="35"/>
+      <c r="N10" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="36">
-        <v>0.59</v>
-      </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="36">
-        <v>0.01</v>
-      </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36">
+    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="32">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E11" s="35"/>
+      <c r="F11" s="32">
+        <v>0</v>
+      </c>
+      <c r="G11" s="35"/>
+      <c r="H11" s="32">
+        <v>0</v>
+      </c>
+      <c r="I11" s="35"/>
+      <c r="J11" s="32">
+        <v>0</v>
+      </c>
+      <c r="K11" s="35"/>
+      <c r="L11" s="32">
+        <v>0</v>
+      </c>
+      <c r="M11" s="35"/>
+      <c r="N11" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="35"/>
+      <c r="D12" s="32">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E12" s="35"/>
+      <c r="F12" s="32">
+        <v>0.19</v>
+      </c>
+      <c r="G12" s="35"/>
+      <c r="H12" s="32">
         <v>0.18</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36">
-        <v>0.01</v>
-      </c>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36">
-        <v>0.2</v>
-      </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="36">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="36">
-        <v>0.51</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="36">
-        <v>0.19</v>
-      </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="36">
-        <v>0.18</v>
-      </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36">
+      <c r="I12" s="35"/>
+      <c r="J12" s="32">
         <v>0.12</v>
       </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="36">
-        <v>0.22</v>
-      </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="36">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="36">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36">
-        <v>0</v>
-      </c>
-      <c r="G10" s="35"/>
-      <c r="H10" s="36">
-        <v>0</v>
-      </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36">
-        <v>0</v>
-      </c>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36">
-        <v>0</v>
-      </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="36">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="36">
-        <v>0</v>
-      </c>
-      <c r="G11" s="35"/>
-      <c r="H11" s="36">
-        <v>0</v>
-      </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36">
-        <v>0</v>
-      </c>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36">
-        <v>0</v>
-      </c>
-      <c r="M11" s="35"/>
-      <c r="N11" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="36">
-        <v>0.19</v>
-      </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="36">
-        <v>0.18</v>
-      </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="36">
-        <v>0.12</v>
-      </c>
       <c r="K12" s="35"/>
-      <c r="L12" s="36">
+      <c r="L12" s="32">
         <v>0.23</v>
       </c>
       <c r="M12" s="35"/>
-      <c r="N12" s="36">
+      <c r="N12" s="32">
         <v>0.18</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="M3:M12"/>
     <mergeCell ref="C3:C12"/>
     <mergeCell ref="E3:E12"/>
     <mergeCell ref="G3:G12"/>
     <mergeCell ref="I3:I12"/>
     <mergeCell ref="K3:K12"/>
-    <mergeCell ref="M3:M12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1"/>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClassUser\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\оптимизация\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Title и Description (сниппеты)" sheetId="7" r:id="rId4"/>
     <sheet name="Ссылки" sheetId="5" r:id="rId5"/>
     <sheet name="Конкуренты" sheetId="4" r:id="rId6"/>
+    <sheet name="Уникальность" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="204">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -520,9 +521,6 @@
     <t>РЕЛЕВАНТНОСТЬ</t>
   </si>
   <si>
-    <t>НАШ САЙТ</t>
-  </si>
-  <si>
     <t>ЗАПРОСЫ</t>
   </si>
   <si>
@@ -635,6 +633,15 @@
   </si>
   <si>
     <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с моделями нашей одежды и спортивными костюмами.</t>
+  </si>
+  <si>
+    <t>https://georgekazanba.github.io/index2.html</t>
+  </si>
+  <si>
+    <t>https://www.planeta-sport.ru/catalog/wear/</t>
+  </si>
+  <si>
+    <t>https://www.kant.ru/catalog/clothes/</t>
   </si>
 </sst>
 </file>
@@ -752,7 +759,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -925,6 +932,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top style="double">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="double">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -936,7 +980,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1031,59 +1075,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1115,6 +1192,87 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>2301</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="209550"/>
+          <a:ext cx="7934325" cy="4555251"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>10813</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7924800" y="190500"/>
+          <a:ext cx="7934325" cy="4582813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3109,210 +3267,210 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="G2" s="37"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="K2" s="37"/>
-      <c r="L2" s="38"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="40" t="s">
+      <c r="B3" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="G3" s="40" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="H3" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="H3" s="41" t="s">
-        <v>197</v>
-      </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="K3" s="40" t="s">
+      <c r="I3" s="38"/>
+      <c r="J3" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="K3" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="L3" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="L3" s="41" t="s">
-        <v>197</v>
-      </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="40">
         <v>0.61</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="41">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="40">
         <v>0.43</v>
       </c>
-      <c r="H4" s="45">
+      <c r="H4" s="41">
         <v>0.80800000000000005</v>
       </c>
-      <c r="J4" s="43" t="s">
+      <c r="J4" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="40">
         <v>0.59</v>
       </c>
-      <c r="L4" s="45">
+      <c r="L4" s="41">
         <v>0.82</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="39" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="44">
+      <c r="C5" s="40">
         <v>0.59</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="41">
         <v>0.77500000000000002</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="40">
         <v>0.42</v>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="41">
         <v>0.79500000000000004</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="40">
         <v>0.52</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="41">
         <v>0.82299999999999995</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="40">
         <v>0.51</v>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="41">
         <v>0.7</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="40">
         <v>0.43</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="41">
         <v>0.81499999999999995</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="44">
+      <c r="K6" s="40">
         <v>0.5</v>
       </c>
-      <c r="L6" s="45">
+      <c r="L6" s="41">
         <v>0.79800000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="40">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="41">
         <v>0.75</v>
       </c>
-      <c r="F7" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
-      <c r="J7" s="43" t="s">
+      <c r="F7" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="G7" s="49"/>
+      <c r="H7" s="50"/>
+      <c r="J7" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="K7" s="44">
+      <c r="K7" s="40">
         <v>0.39</v>
       </c>
-      <c r="L7" s="45">
+      <c r="L7" s="41">
         <v>0.84</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="40">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D8" s="45">
+      <c r="D8" s="41">
         <v>0.7</v>
       </c>
-      <c r="J8" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="49"/>
+      <c r="J8" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="44">
+      <c r="C9" s="40">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="41">
         <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="B10" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="50"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="J8:L8"/>
-    <mergeCell ref="B10:D10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3350,8 +3508,8 @@
       <c r="C3" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>198</v>
+      <c r="D3" s="43" t="s">
+        <v>197</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -3362,8 +3520,8 @@
       <c r="C4" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="D4" s="50" t="s">
-        <v>199</v>
+      <c r="D4" s="43" t="s">
+        <v>198</v>
       </c>
       <c r="E4" s="26"/>
     </row>
@@ -3372,10 +3530,10 @@
         <v>157</v>
       </c>
       <c r="C5" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="44" t="s">
         <v>200</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>201</v>
       </c>
       <c r="E5" s="26"/>
     </row>
@@ -3398,28 +3556,28 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
+        <v>179</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C3" s="15">
         <v>1</v>
@@ -3427,10 +3585,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C4" s="15">
         <v>1</v>
@@ -3438,10 +3596,10 @@
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C5" s="15">
         <v>1</v>
@@ -3449,10 +3607,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -3460,10 +3618,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C7" s="15">
         <v>1</v>
@@ -3471,10 +3629,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C8" s="15">
         <v>1</v>
@@ -3482,10 +3640,10 @@
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C9" s="15">
         <v>1</v>
@@ -3493,10 +3651,10 @@
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C10" s="15">
         <v>1</v>
@@ -3504,17 +3662,17 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
+        <v>181</v>
+      </c>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C12" s="15">
         <v>1</v>
@@ -3522,10 +3680,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C13" s="15">
         <v>1</v>
@@ -3533,10 +3691,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C14" s="15">
         <v>1</v>
@@ -3544,10 +3702,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="15">
         <v>1</v>
@@ -3555,10 +3713,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -3566,10 +3724,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
@@ -3577,10 +3735,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18" s="15">
         <v>1</v>
@@ -3588,10 +3746,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="15">
         <v>1</v>
@@ -3599,17 +3757,17 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
+        <v>192</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" s="15">
         <v>1</v>
@@ -3617,10 +3775,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C22" s="15">
         <v>1</v>
@@ -3628,10 +3786,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C23" s="15">
         <v>1</v>
@@ -3639,10 +3797,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C24" s="15">
         <v>1</v>
@@ -3650,10 +3808,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C25" s="15">
         <v>1</v>
@@ -3661,10 +3819,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C26" s="15">
         <v>1</v>
@@ -3672,10 +3830,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C27" s="15">
         <v>1</v>
@@ -3683,10 +3841,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C28" s="15">
         <v>1</v>
@@ -3708,388 +3866,642 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:N13"/>
+  <dimension ref="B1:P24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="16.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="16.28515625" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="10" max="10" width="16.28515625" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="14" max="14" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="16.28515625" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="D2" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="F2" s="30" t="s">
+      <c r="E2" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" s="29" t="s">
         <v>162</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O2" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="35" t="s">
-        <v>168</v>
+      <c r="C3" s="52" t="s">
+        <v>167</v>
       </c>
       <c r="D3" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>167</v>
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>201</v>
       </c>
       <c r="F3" s="32">
         <v>0.49</v>
       </c>
-      <c r="G3" s="35" t="s">
-        <v>170</v>
+      <c r="G3" s="52" t="s">
+        <v>166</v>
       </c>
       <c r="H3" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="J3" s="32">
         <v>0.01</v>
       </c>
-      <c r="I3" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="J3" s="32">
+      <c r="K3" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="L3" s="32">
         <v>0.59</v>
       </c>
-      <c r="K3" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="L3" s="32">
+      <c r="M3" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="N3" s="32">
         <v>0.49</v>
       </c>
-      <c r="M3" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="N3" s="32">
+      <c r="O3" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="P3" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="35"/>
+      <c r="C4" s="52"/>
       <c r="D4" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="35"/>
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="54"/>
       <c r="F4" s="32">
+        <v>0.62</v>
+      </c>
+      <c r="G4" s="52"/>
+      <c r="H4" s="32">
         <v>0.27</v>
       </c>
-      <c r="G4" s="35"/>
-      <c r="H4" s="32">
+      <c r="I4" s="52"/>
+      <c r="J4" s="32">
         <v>0.15</v>
       </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="32">
+      <c r="K4" s="52"/>
+      <c r="L4" s="32">
         <v>0.18</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="32">
+      <c r="M4" s="52"/>
+      <c r="N4" s="32">
         <v>0.3</v>
       </c>
-      <c r="M4" s="35"/>
-      <c r="N4" s="32">
+      <c r="O4" s="52"/>
+      <c r="P4" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="35"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="32">
-        <v>0.43</v>
-      </c>
-      <c r="E5" s="35"/>
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="54"/>
       <c r="F5" s="32">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="52"/>
+      <c r="H5" s="32">
         <v>0.19</v>
       </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="32">
+      <c r="I5" s="52"/>
+      <c r="J5" s="32">
         <v>0.15</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="32">
+      <c r="K5" s="52"/>
+      <c r="L5" s="32">
         <v>0.21</v>
       </c>
-      <c r="K5" s="35"/>
-      <c r="L5" s="32">
+      <c r="M5" s="52"/>
+      <c r="N5" s="32">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="32">
+      <c r="O5" s="52"/>
+      <c r="P5" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="35"/>
+      <c r="C6" s="52"/>
       <c r="D6" s="32">
-        <v>0.46</v>
-      </c>
-      <c r="E6" s="35"/>
+        <v>0.16</v>
+      </c>
+      <c r="E6" s="54"/>
       <c r="F6" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="G6" s="52"/>
+      <c r="H6" s="32">
         <v>0.63</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="32">
+      <c r="I6" s="52"/>
+      <c r="J6" s="32">
         <v>0.5</v>
       </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="32">
+      <c r="K6" s="52"/>
+      <c r="L6" s="32">
         <v>0.64</v>
       </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="32">
+      <c r="M6" s="52"/>
+      <c r="N6" s="32">
         <v>0.49</v>
       </c>
-      <c r="M6" s="35"/>
-      <c r="N6" s="32">
+      <c r="O6" s="52"/>
+      <c r="P6" s="32">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="35"/>
+      <c r="C7" s="52"/>
       <c r="D7" s="32">
-        <v>0.61</v>
-      </c>
-      <c r="E7" s="35"/>
+        <v>0.63</v>
+      </c>
+      <c r="E7" s="54"/>
       <c r="F7" s="32">
-        <v>0</v>
-      </c>
-      <c r="G7" s="35"/>
+        <v>0.71</v>
+      </c>
+      <c r="G7" s="52"/>
       <c r="H7" s="32">
         <v>0</v>
       </c>
-      <c r="I7" s="35"/>
+      <c r="I7" s="52"/>
       <c r="J7" s="32">
         <v>0</v>
       </c>
-      <c r="K7" s="35"/>
+      <c r="K7" s="52"/>
       <c r="L7" s="32">
         <v>0</v>
       </c>
-      <c r="M7" s="35"/>
+      <c r="M7" s="52"/>
       <c r="N7" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O7" s="52"/>
+      <c r="P7" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="52"/>
       <c r="D8" s="32">
-        <v>0.59</v>
-      </c>
-      <c r="E8" s="35"/>
+        <v>0.61</v>
+      </c>
+      <c r="E8" s="54"/>
       <c r="F8" s="32">
+        <v>0.65</v>
+      </c>
+      <c r="G8" s="52"/>
+      <c r="H8" s="32">
         <v>0.01</v>
       </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="32">
+      <c r="I8" s="52"/>
+      <c r="J8" s="32">
         <v>0.18</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="32">
+      <c r="K8" s="52"/>
+      <c r="L8" s="32">
         <v>0.01</v>
       </c>
-      <c r="K8" s="35"/>
-      <c r="L8" s="32">
+      <c r="M8" s="52"/>
+      <c r="N8" s="32">
         <v>0.2</v>
       </c>
-      <c r="M8" s="35"/>
-      <c r="N8" s="32">
+      <c r="O8" s="52"/>
+      <c r="P8" s="32">
         <v>0.17</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="32">
-        <v>0.51</v>
-      </c>
-      <c r="E9" s="35"/>
+        <v>0.52</v>
+      </c>
+      <c r="E9" s="54"/>
       <c r="F9" s="32">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" s="32">
         <v>0.19</v>
       </c>
-      <c r="G9" s="35"/>
-      <c r="H9" s="32">
+      <c r="I9" s="52"/>
+      <c r="J9" s="32">
         <v>0.18</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="32">
+      <c r="K9" s="52"/>
+      <c r="L9" s="32">
         <v>0.12</v>
       </c>
-      <c r="K9" s="35"/>
-      <c r="L9" s="32">
+      <c r="M9" s="52"/>
+      <c r="N9" s="32">
         <v>0.22</v>
       </c>
-      <c r="M9" s="35"/>
-      <c r="N9" s="32">
+      <c r="O9" s="52"/>
+      <c r="P9" s="32">
         <v>0.18</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="52"/>
       <c r="D10" s="32">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E10" s="35"/>
+        <v>0.51</v>
+      </c>
+      <c r="E10" s="54"/>
       <c r="F10" s="32">
-        <v>0</v>
-      </c>
-      <c r="G10" s="35"/>
+        <v>0.65</v>
+      </c>
+      <c r="G10" s="52"/>
       <c r="H10" s="32">
         <v>0</v>
       </c>
-      <c r="I10" s="35"/>
+      <c r="I10" s="52"/>
       <c r="J10" s="32">
         <v>0</v>
       </c>
-      <c r="K10" s="35"/>
+      <c r="K10" s="52"/>
       <c r="L10" s="32">
         <v>0</v>
       </c>
-      <c r="M10" s="35"/>
+      <c r="M10" s="52"/>
       <c r="N10" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O10" s="52"/>
+      <c r="P10" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="52"/>
       <c r="D11" s="32">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E11" s="35"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E11" s="54"/>
       <c r="F11" s="32">
-        <v>0</v>
-      </c>
-      <c r="G11" s="35"/>
+        <v>0.21</v>
+      </c>
+      <c r="G11" s="52"/>
       <c r="H11" s="32">
         <v>0</v>
       </c>
-      <c r="I11" s="35"/>
+      <c r="I11" s="52"/>
       <c r="J11" s="32">
         <v>0</v>
       </c>
-      <c r="K11" s="35"/>
+      <c r="K11" s="52"/>
       <c r="L11" s="32">
         <v>0</v>
       </c>
-      <c r="M11" s="35"/>
+      <c r="M11" s="52"/>
       <c r="N11" s="32">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O11" s="52"/>
+      <c r="P11" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="35"/>
+      <c r="C12" s="52"/>
       <c r="D12" s="32">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="E12" s="35"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E12" s="55"/>
       <c r="F12" s="32">
+        <v>0.42</v>
+      </c>
+      <c r="G12" s="52"/>
+      <c r="H12" s="32">
         <v>0.19</v>
       </c>
-      <c r="G12" s="35"/>
-      <c r="H12" s="32">
+      <c r="I12" s="52"/>
+      <c r="J12" s="32">
         <v>0.18</v>
       </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="32">
+      <c r="K12" s="52"/>
+      <c r="L12" s="32">
         <v>0.12</v>
       </c>
-      <c r="K12" s="35"/>
-      <c r="L12" s="32">
+      <c r="M12" s="52"/>
+      <c r="N12" s="32">
         <v>0.23</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="32">
+      <c r="O12" s="52"/>
+      <c r="P12" s="32">
         <v>0.18</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="33"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="32"/>
+    </row>
+    <row r="14" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="H14" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="K14" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="L14" s="61">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="58"/>
+      <c r="H15" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="58"/>
+      <c r="L15" s="32">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="G16" s="58"/>
+      <c r="H16" s="32">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K16" s="58"/>
+      <c r="L16" s="32">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="58"/>
+      <c r="H17" s="32">
+        <v>0.19</v>
+      </c>
+      <c r="K17" s="58"/>
+      <c r="L17" s="32">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" s="58"/>
+      <c r="H18" s="32">
+        <v>0</v>
+      </c>
+      <c r="K18" s="58"/>
+      <c r="L18" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="58"/>
+      <c r="H19" s="32">
+        <v>0</v>
+      </c>
+      <c r="K19" s="58"/>
+      <c r="L19" s="32">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="58"/>
+      <c r="H20" s="32">
+        <v>0</v>
+      </c>
+      <c r="K20" s="58"/>
+      <c r="L20" s="32">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G21" s="58"/>
+      <c r="H21" s="32">
+        <v>0.02</v>
+      </c>
+      <c r="K21" s="58"/>
+      <c r="L21" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="58"/>
+      <c r="H22" s="32">
+        <v>0</v>
+      </c>
+      <c r="K22" s="58"/>
+      <c r="L22" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" s="58"/>
+      <c r="H23" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="K23" s="58"/>
+      <c r="L23" s="32">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="M3:M12"/>
+  <mergeCells count="9">
+    <mergeCell ref="K14:K23"/>
+    <mergeCell ref="G14:G23"/>
+    <mergeCell ref="O3:O12"/>
     <mergeCell ref="C3:C12"/>
-    <mergeCell ref="E3:E12"/>
     <mergeCell ref="G3:G12"/>
     <mergeCell ref="I3:I12"/>
     <mergeCell ref="K3:K12"/>
+    <mergeCell ref="M3:M12"/>
+    <mergeCell ref="E3:E12"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId1"/>
     <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="G3" r:id="rId3"/>
-    <hyperlink ref="I3" r:id="rId4"/>
-    <hyperlink ref="K3" r:id="rId5"/>
-    <hyperlink ref="M3" r:id="rId6"/>
+    <hyperlink ref="I3" r:id="rId3"/>
+    <hyperlink ref="K3" r:id="rId4"/>
+    <hyperlink ref="M3" r:id="rId5"/>
+    <hyperlink ref="O3" r:id="rId6"/>
+    <hyperlink ref="E3" r:id="rId7"/>
+    <hyperlink ref="K14" r:id="rId8"/>
+    <hyperlink ref="G14" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56" t="s">
+        <v>181</v>
+      </c>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="N1:Z1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\оптимизация\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ClassUser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="205">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -642,6 +642,9 @@
   </si>
   <si>
     <t>https://www.kant.ru/catalog/clothes/</t>
+  </si>
+  <si>
+    <t>УНИКАЛЬНЫЕ ССЫЛКИ</t>
   </si>
 </sst>
 </file>
@@ -1108,6 +1111,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1117,18 +1135,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
@@ -1144,23 +1162,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1198,34 +1201,33 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>2301</xdr:rowOff>
+      <xdr:colOff>16329</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1"/>
+        <xdr:cNvPr id="4" name="Рисунок 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect t="-1" r="65280" b="68243"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="209550"/>
-          <a:ext cx="7934325" cy="4555251"/>
+          <a:off x="3686175" y="200025"/>
+          <a:ext cx="4254954" cy="2247900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1236,20 +1238,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>10813</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>56883</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3"/>
+        <xdr:cNvPr id="3" name="Рисунок 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1262,8 +1264,46 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7924800" y="190500"/>
-          <a:ext cx="7934325" cy="4582813"/>
+          <a:off x="0" y="209550"/>
+          <a:ext cx="3705225" cy="2133333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>168260</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7924799" y="200025"/>
+          <a:ext cx="3657601" cy="2063735"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3267,23 +3307,23 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="45" t="s">
+      <c r="J2" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="52"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="35" t="s">
@@ -3413,11 +3453,11 @@
       <c r="D7" s="41">
         <v>0.75</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="49"/>
       <c r="J7" s="39" t="s">
         <v>0</v>
       </c>
@@ -3438,11 +3478,11 @@
       <c r="D8" s="41">
         <v>0.7</v>
       </c>
-      <c r="J8" s="48" t="s">
+      <c r="J8" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="50"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="49"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39" t="s">
@@ -3456,11 +3496,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="49"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3569,8 +3609,8 @@
       <c r="A2" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -3664,8 +3704,8 @@
       <c r="A11" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
@@ -3759,8 +3799,8 @@
       <c r="A20" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
@@ -3866,29 +3906,27 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B1:P24"/>
+  <dimension ref="B1:N25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.7109375" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="8" max="8" width="16.28515625" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="10" max="10" width="16.28515625" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1" outlineLevel="1"/>
     <col min="14" max="14" width="16.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="13.140625" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="16.28515625" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="28" t="s">
         <v>163</v>
       </c>
@@ -3898,392 +3936,344 @@
       <c r="D2" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" s="29" t="s">
+      <c r="E2" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L2" s="30" t="s">
         <v>162</v>
       </c>
       <c r="M2" s="30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="57" t="s">
         <v>167</v>
       </c>
       <c r="D3" s="32">
         <v>0.22</v>
       </c>
-      <c r="E3" s="53" t="s">
-        <v>201</v>
+      <c r="E3" s="57" t="s">
+        <v>166</v>
       </c>
       <c r="F3" s="32">
         <v>0.49</v>
       </c>
-      <c r="G3" s="52" t="s">
-        <v>166</v>
+      <c r="G3" s="57" t="s">
+        <v>169</v>
       </c>
       <c r="H3" s="32">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="J3" s="32">
+        <v>0.59</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="32">
         <v>0.49</v>
       </c>
-      <c r="I3" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="J3" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="K3" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="L3" s="32">
-        <v>0.59</v>
-      </c>
-      <c r="M3" s="52" t="s">
-        <v>173</v>
+      <c r="M3" s="57" t="s">
+        <v>175</v>
       </c>
       <c r="N3" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="O3" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="P3" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="52"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="32">
         <v>0.25</v>
       </c>
-      <c r="E4" s="54"/>
+      <c r="E4" s="57"/>
       <c r="F4" s="32">
-        <v>0.62</v>
-      </c>
-      <c r="G4" s="52"/>
+        <v>0.27</v>
+      </c>
+      <c r="G4" s="57"/>
       <c r="H4" s="32">
-        <v>0.27</v>
-      </c>
-      <c r="I4" s="52"/>
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="57"/>
       <c r="J4" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="K4" s="52"/>
+        <v>0.18</v>
+      </c>
+      <c r="K4" s="57"/>
       <c r="L4" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="M4" s="52"/>
+        <v>0.3</v>
+      </c>
+      <c r="M4" s="57"/>
       <c r="N4" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="O4" s="52"/>
-      <c r="P4" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="52"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="32">
         <v>0.09</v>
       </c>
-      <c r="E5" s="54"/>
+      <c r="E5" s="57"/>
       <c r="F5" s="32">
-        <v>0.04</v>
-      </c>
-      <c r="G5" s="52"/>
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="57"/>
       <c r="H5" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="I5" s="52"/>
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="57"/>
       <c r="J5" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="K5" s="52"/>
+        <v>0.21</v>
+      </c>
+      <c r="K5" s="57"/>
       <c r="L5" s="32">
-        <v>0.21</v>
-      </c>
-      <c r="M5" s="52"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M5" s="57"/>
       <c r="N5" s="32">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="O5" s="52"/>
-      <c r="P5" s="32">
         <v>0.26</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="52"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="32">
         <v>0.16</v>
       </c>
-      <c r="E6" s="54"/>
+      <c r="E6" s="57"/>
       <c r="F6" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="G6" s="52"/>
+        <v>0.63</v>
+      </c>
+      <c r="G6" s="57"/>
       <c r="H6" s="32">
-        <v>0.63</v>
-      </c>
-      <c r="I6" s="52"/>
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="57"/>
       <c r="J6" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="52"/>
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="57"/>
       <c r="L6" s="32">
-        <v>0.64</v>
-      </c>
-      <c r="M6" s="52"/>
+        <v>0.49</v>
+      </c>
+      <c r="M6" s="57"/>
       <c r="N6" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="O6" s="52"/>
-      <c r="P6" s="32">
         <v>0.2</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="52"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="32">
         <v>0.63</v>
       </c>
-      <c r="E7" s="54"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="32">
-        <v>0.71</v>
-      </c>
-      <c r="G7" s="52"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="57"/>
       <c r="H7" s="32">
         <v>0</v>
       </c>
-      <c r="I7" s="52"/>
+      <c r="I7" s="57"/>
       <c r="J7" s="32">
         <v>0</v>
       </c>
-      <c r="K7" s="52"/>
+      <c r="K7" s="57"/>
       <c r="L7" s="32">
         <v>0</v>
       </c>
-      <c r="M7" s="52"/>
+      <c r="M7" s="57"/>
       <c r="N7" s="32">
         <v>0</v>
       </c>
-      <c r="O7" s="52"/>
-      <c r="P7" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="52"/>
+      <c r="C8" s="57"/>
       <c r="D8" s="32">
         <v>0.61</v>
       </c>
-      <c r="E8" s="54"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="32">
-        <v>0.65</v>
-      </c>
-      <c r="G8" s="52"/>
+        <v>0.01</v>
+      </c>
+      <c r="G8" s="57"/>
       <c r="H8" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="I8" s="57"/>
+      <c r="J8" s="32">
         <v>0.01</v>
       </c>
-      <c r="I8" s="52"/>
-      <c r="J8" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="K8" s="52"/>
+      <c r="K8" s="57"/>
       <c r="L8" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="M8" s="52"/>
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="57"/>
       <c r="N8" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="O8" s="52"/>
-      <c r="P8" s="32">
         <v>0.17</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="52"/>
+      <c r="C9" s="57"/>
       <c r="D9" s="32">
         <v>0.52</v>
       </c>
-      <c r="E9" s="54"/>
+      <c r="E9" s="57"/>
       <c r="F9" s="32">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G9" s="52"/>
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="57"/>
       <c r="H9" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="I9" s="52"/>
+        <v>0.18</v>
+      </c>
+      <c r="I9" s="57"/>
       <c r="J9" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="K9" s="57"/>
+      <c r="L9" s="32">
+        <v>0.22</v>
+      </c>
+      <c r="M9" s="57"/>
+      <c r="N9" s="32">
         <v>0.18</v>
       </c>
-      <c r="K9" s="52"/>
-      <c r="L9" s="32">
-        <v>0.12</v>
-      </c>
-      <c r="M9" s="52"/>
-      <c r="N9" s="32">
-        <v>0.22</v>
-      </c>
-      <c r="O9" s="52"/>
-      <c r="P9" s="32">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="52"/>
+      <c r="C10" s="57"/>
       <c r="D10" s="32">
         <v>0.51</v>
       </c>
-      <c r="E10" s="54"/>
+      <c r="E10" s="57"/>
       <c r="F10" s="32">
-        <v>0.65</v>
-      </c>
-      <c r="G10" s="52"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="57"/>
       <c r="H10" s="32">
         <v>0</v>
       </c>
-      <c r="I10" s="52"/>
+      <c r="I10" s="57"/>
       <c r="J10" s="32">
         <v>0</v>
       </c>
-      <c r="K10" s="52"/>
+      <c r="K10" s="57"/>
       <c r="L10" s="32">
         <v>0</v>
       </c>
-      <c r="M10" s="52"/>
+      <c r="M10" s="57"/>
       <c r="N10" s="32">
         <v>0</v>
       </c>
-      <c r="O10" s="52"/>
-      <c r="P10" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="52"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="32">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E11" s="54"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="32">
-        <v>0.21</v>
-      </c>
-      <c r="G11" s="52"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="57"/>
       <c r="H11" s="32">
         <v>0</v>
       </c>
-      <c r="I11" s="52"/>
+      <c r="I11" s="57"/>
       <c r="J11" s="32">
         <v>0</v>
       </c>
-      <c r="K11" s="52"/>
+      <c r="K11" s="57"/>
       <c r="L11" s="32">
         <v>0</v>
       </c>
-      <c r="M11" s="52"/>
+      <c r="M11" s="57"/>
       <c r="N11" s="32">
         <v>0</v>
       </c>
-      <c r="O11" s="52"/>
-      <c r="P11" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="52"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E12" s="55"/>
+      <c r="E12" s="57"/>
       <c r="F12" s="32">
-        <v>0.42</v>
-      </c>
-      <c r="G12" s="52"/>
+        <v>0.19</v>
+      </c>
+      <c r="G12" s="57"/>
       <c r="H12" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="I12" s="52"/>
+        <v>0.18</v>
+      </c>
+      <c r="I12" s="57"/>
       <c r="J12" s="32">
+        <v>0.12</v>
+      </c>
+      <c r="K12" s="57"/>
+      <c r="L12" s="32">
+        <v>0.23</v>
+      </c>
+      <c r="M12" s="57"/>
+      <c r="N12" s="32">
         <v>0.18</v>
       </c>
-      <c r="K12" s="52"/>
-      <c r="L12" s="32">
-        <v>0.12</v>
-      </c>
-      <c r="M12" s="52"/>
-      <c r="N12" s="32">
-        <v>0.23</v>
-      </c>
-      <c r="O12" s="52"/>
-      <c r="P12" s="32">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="33"/>
       <c r="C13" s="34"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="62"/>
+      <c r="E13" s="34"/>
       <c r="F13" s="32"/>
       <c r="G13" s="34"/>
       <c r="H13" s="32"/>
@@ -4293,166 +4283,235 @@
       <c r="L13" s="32"/>
       <c r="M13" s="34"/>
       <c r="N13" s="32"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="32"/>
-    </row>
-    <row r="14" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="59" t="s">
+    </row>
+    <row r="14" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="G14" s="57" t="s">
+      <c r="C14" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="32">
+        <v>0.49</v>
+      </c>
+      <c r="E14" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="H14" s="32">
+      <c r="F14" s="32">
         <v>0.49</v>
       </c>
-      <c r="K14" s="60" t="s">
+      <c r="I14" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="L14" s="61">
+      <c r="J14" s="46">
         <v>0.59</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="58"/>
-      <c r="H15" s="32">
+      <c r="C15" s="59"/>
+      <c r="D15" s="32">
+        <v>0.62</v>
+      </c>
+      <c r="E15" s="55"/>
+      <c r="F15" s="32">
         <v>0.2</v>
       </c>
-      <c r="K15" s="58"/>
-      <c r="L15" s="32">
+      <c r="I15" s="55"/>
+      <c r="J15" s="32">
         <v>0.18</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="58"/>
-      <c r="H16" s="32">
+      <c r="C16" s="59"/>
+      <c r="D16" s="32">
+        <v>0.04</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="32">
         <v>0.14000000000000001</v>
       </c>
-      <c r="K16" s="58"/>
-      <c r="L16" s="32">
+      <c r="I16" s="55"/>
+      <c r="J16" s="32">
         <v>0.21</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="32">
+      <c r="C17" s="59"/>
+      <c r="D17" s="32">
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="32">
         <v>0.19</v>
       </c>
-      <c r="K17" s="58"/>
-      <c r="L17" s="32">
+      <c r="I17" s="55"/>
+      <c r="J17" s="32">
         <v>0.64</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="58"/>
-      <c r="H18" s="32">
+      <c r="C18" s="59"/>
+      <c r="D18" s="32">
+        <v>0.71</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="32">
         <v>0</v>
       </c>
-      <c r="K18" s="58"/>
-      <c r="L18" s="32">
+      <c r="I18" s="55"/>
+      <c r="J18" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="58"/>
-      <c r="H19" s="32">
+      <c r="C19" s="59"/>
+      <c r="D19" s="32">
+        <v>0.65</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="32">
         <v>0</v>
       </c>
-      <c r="K19" s="58"/>
-      <c r="L19" s="32">
+      <c r="I19" s="55"/>
+      <c r="J19" s="32">
         <v>0.01</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="G20" s="58"/>
-      <c r="H20" s="32">
+      <c r="C20" s="59"/>
+      <c r="D20" s="32">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="32">
         <v>0</v>
       </c>
-      <c r="K20" s="58"/>
-      <c r="L20" s="32">
+      <c r="I20" s="55"/>
+      <c r="J20" s="32">
         <v>0.12</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="58"/>
-      <c r="H21" s="32">
+      <c r="C21" s="59"/>
+      <c r="D21" s="32">
+        <v>0.65</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="32">
         <v>0.02</v>
       </c>
-      <c r="K21" s="58"/>
-      <c r="L21" s="32">
+      <c r="I21" s="55"/>
+      <c r="J21" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="G22" s="58"/>
-      <c r="H22" s="32">
+      <c r="C22" s="59"/>
+      <c r="D22" s="32">
+        <v>0.21</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="32">
         <v>0</v>
       </c>
-      <c r="K22" s="58"/>
-      <c r="L22" s="32">
+      <c r="I22" s="55"/>
+      <c r="J22" s="32">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="58"/>
-      <c r="H23" s="32">
+      <c r="C23" s="60"/>
+      <c r="D23" s="32">
+        <v>0.42</v>
+      </c>
+      <c r="E23" s="55"/>
+      <c r="F23" s="32">
         <v>0.01</v>
       </c>
-      <c r="K23" s="58"/>
-      <c r="L23" s="32">
+      <c r="I23" s="55"/>
+      <c r="J23" s="32">
         <v>0.12</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="62" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="15">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15">
+        <v>7823</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15">
+        <v>144</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15">
+        <v>1555</v>
+      </c>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15">
+        <v>2984</v>
+      </c>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15">
+        <v>9</v>
+      </c>
+      <c r="N25" s="15"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="K14:K23"/>
-    <mergeCell ref="G14:G23"/>
-    <mergeCell ref="O3:O12"/>
+    <mergeCell ref="I14:I23"/>
+    <mergeCell ref="E14:E23"/>
+    <mergeCell ref="M3:M12"/>
     <mergeCell ref="C3:C12"/>
+    <mergeCell ref="E3:E12"/>
     <mergeCell ref="G3:G12"/>
     <mergeCell ref="I3:I12"/>
     <mergeCell ref="K3:K12"/>
-    <mergeCell ref="M3:M12"/>
-    <mergeCell ref="E3:E12"/>
+    <mergeCell ref="C14:C23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId1"/>
     <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="I3" r:id="rId3"/>
-    <hyperlink ref="K3" r:id="rId4"/>
-    <hyperlink ref="M3" r:id="rId5"/>
-    <hyperlink ref="O3" r:id="rId6"/>
-    <hyperlink ref="E3" r:id="rId7"/>
-    <hyperlink ref="K14" r:id="rId8"/>
-    <hyperlink ref="G14" r:id="rId9"/>
+    <hyperlink ref="G3" r:id="rId3"/>
+    <hyperlink ref="I3" r:id="rId4"/>
+    <hyperlink ref="K3" r:id="rId5"/>
+    <hyperlink ref="M3" r:id="rId6"/>
+    <hyperlink ref="C14" r:id="rId7"/>
+    <hyperlink ref="I14" r:id="rId8"/>
+    <hyperlink ref="E14" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
@@ -4461,45 +4520,41 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="N1:Z1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -17,8 +17,9 @@
     <sheet name="Релевантность" sheetId="6" r:id="rId3"/>
     <sheet name="Title и Description (сниппеты)" sheetId="7" r:id="rId4"/>
     <sheet name="Ссылки" sheetId="5" r:id="rId5"/>
-    <sheet name="Конкуренты" sheetId="4" r:id="rId6"/>
-    <sheet name="Уникальность" sheetId="8" r:id="rId7"/>
+    <sheet name="Уникальность" sheetId="8" r:id="rId6"/>
+    <sheet name="Конкуренты" sheetId="4" r:id="rId7"/>
+    <sheet name="Интерактив" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="212">
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -645,6 +646,27 @@
   </si>
   <si>
     <t>УНИКАЛЬНЫЕ ССЫЛКИ</t>
+  </si>
+  <si>
+    <t>САЙТ</t>
+  </si>
+  <si>
+    <t>ИНТЕРАКТИВ</t>
+  </si>
+  <si>
+    <t>консультант, личный кабинет, корзина и желаемое, ссылки на соц. сети, отзывы, рассылка по почте</t>
+  </si>
+  <si>
+    <t>консультант, рассылка по почте, личный кабинет, корзина</t>
+  </si>
+  <si>
+    <t>личный кабинет, корзина</t>
+  </si>
+  <si>
+    <t>личный кабинет, корзина, консультант</t>
+  </si>
+  <si>
+    <t>рассылка по почте</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1005,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1117,6 +1139,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1162,7 +1187,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3307,23 +3341,23 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="53"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="50" t="s">
+      <c r="J2" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="K2" s="51"/>
-      <c r="L2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="53"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="35" t="s">
@@ -3453,11 +3487,11 @@
       <c r="D7" s="41">
         <v>0.75</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="50"/>
       <c r="J7" s="39" t="s">
         <v>0</v>
       </c>
@@ -3478,11 +3512,11 @@
       <c r="D8" s="41">
         <v>0.7</v>
       </c>
-      <c r="J8" s="47" t="s">
+      <c r="J8" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="50"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="39" t="s">
@@ -3496,11 +3530,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="50"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3609,8 +3643,8 @@
       <c r="A2" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -3704,8 +3738,8 @@
       <c r="A11" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
@@ -3799,8 +3833,8 @@
       <c r="A20" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
@@ -3902,6 +3936,49 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62" t="s">
+        <v>192</v>
+      </c>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -3971,37 +4048,37 @@
       <c r="B3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="58" t="s">
         <v>167</v>
       </c>
       <c r="D3" s="32">
         <v>0.22</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="58" t="s">
         <v>166</v>
       </c>
       <c r="F3" s="32">
         <v>0.49</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="58" t="s">
         <v>169</v>
       </c>
       <c r="H3" s="32">
         <v>0.01</v>
       </c>
-      <c r="I3" s="57" t="s">
+      <c r="I3" s="58" t="s">
         <v>171</v>
       </c>
       <c r="J3" s="32">
         <v>0.59</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="58" t="s">
         <v>173</v>
       </c>
       <c r="L3" s="32">
         <v>0.49</v>
       </c>
-      <c r="M3" s="57" t="s">
+      <c r="M3" s="58" t="s">
         <v>175</v>
       </c>
       <c r="N3" s="32">
@@ -4012,27 +4089,27 @@
       <c r="B4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="57"/>
+      <c r="C4" s="58"/>
       <c r="D4" s="32">
         <v>0.25</v>
       </c>
-      <c r="E4" s="57"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="32">
         <v>0.27</v>
       </c>
-      <c r="G4" s="57"/>
+      <c r="G4" s="58"/>
       <c r="H4" s="32">
         <v>0.15</v>
       </c>
-      <c r="I4" s="57"/>
+      <c r="I4" s="58"/>
       <c r="J4" s="32">
         <v>0.18</v>
       </c>
-      <c r="K4" s="57"/>
+      <c r="K4" s="58"/>
       <c r="L4" s="32">
         <v>0.3</v>
       </c>
-      <c r="M4" s="57"/>
+      <c r="M4" s="58"/>
       <c r="N4" s="32">
         <v>0.26</v>
       </c>
@@ -4041,27 +4118,27 @@
       <c r="B5" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="57"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="32">
         <v>0.09</v>
       </c>
-      <c r="E5" s="57"/>
+      <c r="E5" s="58"/>
       <c r="F5" s="32">
         <v>0.19</v>
       </c>
-      <c r="G5" s="57"/>
+      <c r="G5" s="58"/>
       <c r="H5" s="32">
         <v>0.15</v>
       </c>
-      <c r="I5" s="57"/>
+      <c r="I5" s="58"/>
       <c r="J5" s="32">
         <v>0.21</v>
       </c>
-      <c r="K5" s="57"/>
+      <c r="K5" s="58"/>
       <c r="L5" s="32">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="57"/>
+      <c r="M5" s="58"/>
       <c r="N5" s="32">
         <v>0.26</v>
       </c>
@@ -4070,27 +4147,27 @@
       <c r="B6" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="57"/>
+      <c r="C6" s="58"/>
       <c r="D6" s="32">
         <v>0.16</v>
       </c>
-      <c r="E6" s="57"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="32">
         <v>0.63</v>
       </c>
-      <c r="G6" s="57"/>
+      <c r="G6" s="58"/>
       <c r="H6" s="32">
         <v>0.5</v>
       </c>
-      <c r="I6" s="57"/>
+      <c r="I6" s="58"/>
       <c r="J6" s="32">
         <v>0.64</v>
       </c>
-      <c r="K6" s="57"/>
+      <c r="K6" s="58"/>
       <c r="L6" s="32">
         <v>0.49</v>
       </c>
-      <c r="M6" s="57"/>
+      <c r="M6" s="58"/>
       <c r="N6" s="32">
         <v>0.2</v>
       </c>
@@ -4099,27 +4176,27 @@
       <c r="B7" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="58"/>
       <c r="D7" s="32">
         <v>0.63</v>
       </c>
-      <c r="E7" s="57"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="32">
         <v>0</v>
       </c>
-      <c r="G7" s="57"/>
+      <c r="G7" s="58"/>
       <c r="H7" s="32">
         <v>0</v>
       </c>
-      <c r="I7" s="57"/>
+      <c r="I7" s="58"/>
       <c r="J7" s="32">
         <v>0</v>
       </c>
-      <c r="K7" s="57"/>
+      <c r="K7" s="58"/>
       <c r="L7" s="32">
         <v>0</v>
       </c>
-      <c r="M7" s="57"/>
+      <c r="M7" s="58"/>
       <c r="N7" s="32">
         <v>0</v>
       </c>
@@ -4128,27 +4205,27 @@
       <c r="B8" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="57"/>
+      <c r="C8" s="58"/>
       <c r="D8" s="32">
         <v>0.61</v>
       </c>
-      <c r="E8" s="57"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="32">
         <v>0.01</v>
       </c>
-      <c r="G8" s="57"/>
+      <c r="G8" s="58"/>
       <c r="H8" s="32">
         <v>0.18</v>
       </c>
-      <c r="I8" s="57"/>
+      <c r="I8" s="58"/>
       <c r="J8" s="32">
         <v>0.01</v>
       </c>
-      <c r="K8" s="57"/>
+      <c r="K8" s="58"/>
       <c r="L8" s="32">
         <v>0.2</v>
       </c>
-      <c r="M8" s="57"/>
+      <c r="M8" s="58"/>
       <c r="N8" s="32">
         <v>0.17</v>
       </c>
@@ -4157,27 +4234,27 @@
       <c r="B9" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="57"/>
+      <c r="C9" s="58"/>
       <c r="D9" s="32">
         <v>0.52</v>
       </c>
-      <c r="E9" s="57"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="32">
         <v>0.19</v>
       </c>
-      <c r="G9" s="57"/>
+      <c r="G9" s="58"/>
       <c r="H9" s="32">
         <v>0.18</v>
       </c>
-      <c r="I9" s="57"/>
+      <c r="I9" s="58"/>
       <c r="J9" s="32">
         <v>0.12</v>
       </c>
-      <c r="K9" s="57"/>
+      <c r="K9" s="58"/>
       <c r="L9" s="32">
         <v>0.22</v>
       </c>
-      <c r="M9" s="57"/>
+      <c r="M9" s="58"/>
       <c r="N9" s="32">
         <v>0.18</v>
       </c>
@@ -4186,27 +4263,27 @@
       <c r="B10" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C10" s="57"/>
+      <c r="C10" s="58"/>
       <c r="D10" s="32">
         <v>0.51</v>
       </c>
-      <c r="E10" s="57"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="32">
         <v>0</v>
       </c>
-      <c r="G10" s="57"/>
+      <c r="G10" s="58"/>
       <c r="H10" s="32">
         <v>0</v>
       </c>
-      <c r="I10" s="57"/>
+      <c r="I10" s="58"/>
       <c r="J10" s="32">
         <v>0</v>
       </c>
-      <c r="K10" s="57"/>
+      <c r="K10" s="58"/>
       <c r="L10" s="32">
         <v>0</v>
       </c>
-      <c r="M10" s="57"/>
+      <c r="M10" s="58"/>
       <c r="N10" s="32">
         <v>0</v>
       </c>
@@ -4215,27 +4292,27 @@
       <c r="B11" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C11" s="57"/>
+      <c r="C11" s="58"/>
       <c r="D11" s="32">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E11" s="57"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="32">
         <v>0</v>
       </c>
-      <c r="G11" s="57"/>
+      <c r="G11" s="58"/>
       <c r="H11" s="32">
         <v>0</v>
       </c>
-      <c r="I11" s="57"/>
+      <c r="I11" s="58"/>
       <c r="J11" s="32">
         <v>0</v>
       </c>
-      <c r="K11" s="57"/>
+      <c r="K11" s="58"/>
       <c r="L11" s="32">
         <v>0</v>
       </c>
-      <c r="M11" s="57"/>
+      <c r="M11" s="58"/>
       <c r="N11" s="32">
         <v>0</v>
       </c>
@@ -4244,27 +4321,27 @@
       <c r="B12" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="32">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E12" s="57"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="32">
         <v>0.19</v>
       </c>
-      <c r="G12" s="57"/>
+      <c r="G12" s="58"/>
       <c r="H12" s="32">
         <v>0.18</v>
       </c>
-      <c r="I12" s="57"/>
+      <c r="I12" s="58"/>
       <c r="J12" s="32">
         <v>0.12</v>
       </c>
-      <c r="K12" s="57"/>
+      <c r="K12" s="58"/>
       <c r="L12" s="32">
         <v>0.23</v>
       </c>
-      <c r="M12" s="57"/>
+      <c r="M12" s="58"/>
       <c r="N12" s="32">
         <v>0.18</v>
       </c>
@@ -4288,19 +4365,19 @@
       <c r="B14" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="59" t="s">
         <v>201</v>
       </c>
       <c r="D14" s="32">
         <v>0.49</v>
       </c>
-      <c r="E14" s="56" t="s">
+      <c r="E14" s="57" t="s">
         <v>203</v>
       </c>
       <c r="F14" s="32">
         <v>0.49</v>
       </c>
-      <c r="I14" s="54" t="s">
+      <c r="I14" s="55" t="s">
         <v>202</v>
       </c>
       <c r="J14" s="46">
@@ -4311,15 +4388,15 @@
       <c r="B15" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="59"/>
+      <c r="C15" s="60"/>
       <c r="D15" s="32">
         <v>0.62</v>
       </c>
-      <c r="E15" s="55"/>
+      <c r="E15" s="56"/>
       <c r="F15" s="32">
         <v>0.2</v>
       </c>
-      <c r="I15" s="55"/>
+      <c r="I15" s="56"/>
       <c r="J15" s="32">
         <v>0.18</v>
       </c>
@@ -4328,15 +4405,15 @@
       <c r="B16" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="60"/>
       <c r="D16" s="32">
         <v>0.04</v>
       </c>
-      <c r="E16" s="55"/>
+      <c r="E16" s="56"/>
       <c r="F16" s="32">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I16" s="55"/>
+      <c r="I16" s="56"/>
       <c r="J16" s="32">
         <v>0.21</v>
       </c>
@@ -4345,15 +4422,15 @@
       <c r="B17" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="59"/>
+      <c r="C17" s="60"/>
       <c r="D17" s="32">
         <v>0.18</v>
       </c>
-      <c r="E17" s="55"/>
+      <c r="E17" s="56"/>
       <c r="F17" s="32">
         <v>0.19</v>
       </c>
-      <c r="I17" s="55"/>
+      <c r="I17" s="56"/>
       <c r="J17" s="32">
         <v>0.64</v>
       </c>
@@ -4362,15 +4439,15 @@
       <c r="B18" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="59"/>
+      <c r="C18" s="60"/>
       <c r="D18" s="32">
         <v>0.71</v>
       </c>
-      <c r="E18" s="55"/>
+      <c r="E18" s="56"/>
       <c r="F18" s="32">
         <v>0</v>
       </c>
-      <c r="I18" s="55"/>
+      <c r="I18" s="56"/>
       <c r="J18" s="32">
         <v>0</v>
       </c>
@@ -4379,15 +4456,15 @@
       <c r="B19" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="59"/>
+      <c r="C19" s="60"/>
       <c r="D19" s="32">
         <v>0.65</v>
       </c>
-      <c r="E19" s="55"/>
+      <c r="E19" s="56"/>
       <c r="F19" s="32">
         <v>0</v>
       </c>
-      <c r="I19" s="55"/>
+      <c r="I19" s="56"/>
       <c r="J19" s="32">
         <v>0.01</v>
       </c>
@@ -4396,15 +4473,15 @@
       <c r="B20" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="59"/>
+      <c r="C20" s="60"/>
       <c r="D20" s="32">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E20" s="55"/>
+      <c r="E20" s="56"/>
       <c r="F20" s="32">
         <v>0</v>
       </c>
-      <c r="I20" s="55"/>
+      <c r="I20" s="56"/>
       <c r="J20" s="32">
         <v>0.12</v>
       </c>
@@ -4413,15 +4490,15 @@
       <c r="B21" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="32">
         <v>0.65</v>
       </c>
-      <c r="E21" s="55"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="32">
         <v>0.02</v>
       </c>
-      <c r="I21" s="55"/>
+      <c r="I21" s="56"/>
       <c r="J21" s="32">
         <v>0</v>
       </c>
@@ -4430,15 +4507,15 @@
       <c r="B22" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="59"/>
+      <c r="C22" s="60"/>
       <c r="D22" s="32">
         <v>0.21</v>
       </c>
-      <c r="E22" s="55"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="32">
         <v>0</v>
       </c>
-      <c r="I22" s="55"/>
+      <c r="I22" s="56"/>
       <c r="J22" s="32">
         <v>0</v>
       </c>
@@ -4447,22 +4524,22 @@
       <c r="B23" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="60"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="32">
         <v>0.42</v>
       </c>
-      <c r="E23" s="55"/>
+      <c r="E23" s="56"/>
       <c r="F23" s="32">
         <v>0.01</v>
       </c>
-      <c r="I23" s="55"/>
+      <c r="I23" s="56"/>
       <c r="J23" s="32">
         <v>0.12</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="62" t="s">
+      <c r="B25" s="47" t="s">
         <v>204</v>
       </c>
       <c r="C25" s="15">
@@ -4518,45 +4595,102 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61" t="s">
-        <v>192</v>
-      </c>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="66" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="65"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="66" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="65"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="65"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="65"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="65"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="65"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="65"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="N1:S1"/>
-  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="A5" r:id="rId4"/>
+    <hyperlink ref="A8" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="3" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,43 @@
     <sheet name="Уникальность" sheetId="8" r:id="rId6"/>
     <sheet name="Конкуренты" sheetId="4" r:id="rId7"/>
     <sheet name="Интерактив" sheetId="9" r:id="rId8"/>
+    <sheet name="Ссылки сайтов" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="219">
+  <si>
+    <t>ЗАПРОС «СПОРТИВНАЯ ОДЕЖДА»</t>
+  </si>
+  <si>
+    <t>ЧАСТОТНОСТЬ</t>
+  </si>
+  <si>
+    <t>"ЧАСТОТНОСТЬ"</t>
+  </si>
+  <si>
+    <t>ЗАПРОС «СПОРТИВНАЯ ОБУВЬ»</t>
+  </si>
+  <si>
+    <t>ЗАПРОСЫ «АБИБАС»</t>
+  </si>
   <si>
     <t>спортивная одежда</t>
   </si>
@@ -39,106 +64,274 @@
     <t>215 960</t>
   </si>
   <si>
+    <t>спортивная обувь</t>
+  </si>
+  <si>
+    <t>62 918</t>
+  </si>
+  <si>
+    <t>абибас</t>
+  </si>
+  <si>
+    <t>2 216</t>
+  </si>
+  <si>
     <t>магазин спортивной одежды</t>
   </si>
   <si>
     <t>45 557</t>
   </si>
   <si>
+    <t>магазин спортивной обуви</t>
+  </si>
+  <si>
+    <t>9 865</t>
+  </si>
+  <si>
+    <t>кроссовки абибас</t>
+  </si>
+  <si>
     <t>одежда спортивная интернет</t>
   </si>
   <si>
     <t>18 133</t>
   </si>
   <si>
+    <t>спортивная одежда +и обувь</t>
+  </si>
+  <si>
+    <t>5 546</t>
+  </si>
+  <si>
+    <t>абибас купить</t>
+  </si>
+  <si>
     <t>интернет магазин спортивной одежды</t>
   </si>
   <si>
     <t>16 981</t>
   </si>
   <si>
+    <t>купить спортивную обувь</t>
+  </si>
+  <si>
+    <t>5 000</t>
+  </si>
+  <si>
+    <t>абибас три полоски</t>
+  </si>
+  <si>
     <t>купить спортивную одежду</t>
   </si>
   <si>
     <t>12 953</t>
   </si>
   <si>
+    <t>женская спортивная обувь</t>
+  </si>
+  <si>
+    <t>4 787</t>
+  </si>
+  <si>
+    <t>адидас абибас</t>
+  </si>
+  <si>
     <t>бренды спортивной одежды</t>
   </si>
   <si>
     <t>11 424</t>
   </si>
   <si>
+    <t>мужская спортивная обувь</t>
+  </si>
+  <si>
+    <t>4 259</t>
+  </si>
+  <si>
+    <t>фирма абибас</t>
+  </si>
+  <si>
     <t>спортивная одежда +для мужчин</t>
   </si>
   <si>
     <t>9 982</t>
   </si>
   <si>
+    <t>обувь спортивная интернет</t>
+  </si>
+  <si>
+    <t>3 262</t>
+  </si>
+  <si>
+    <t>скачать абибас</t>
+  </si>
+  <si>
     <t>сайты спортивной одежды</t>
   </si>
   <si>
     <t>9 864</t>
   </si>
   <si>
+    <t>интернет магазин спортивной обуви</t>
+  </si>
+  <si>
+    <t>2 978</t>
+  </si>
+  <si>
+    <t>абибас фото</t>
+  </si>
+  <si>
     <t>женская спортивная одежда</t>
   </si>
   <si>
     <t>9 744</t>
   </si>
   <si>
+    <t>спортивная зимняя обувь</t>
+  </si>
+  <si>
+    <t>2 557</t>
+  </si>
+  <si>
+    <t>футболка абибас</t>
+  </si>
+  <si>
     <t>спортивная одежда официальный</t>
   </si>
   <si>
     <t>9 620</t>
   </si>
   <si>
+    <t>детская спортивная обувь</t>
+  </si>
+  <si>
+    <t>1 726</t>
+  </si>
+  <si>
+    <t>абибас мем</t>
+  </si>
+  <si>
     <t>мужская спортивная одежда</t>
   </si>
   <si>
     <t>9 616</t>
   </si>
   <si>
+    <t>носим спортивную обувь</t>
+  </si>
+  <si>
+    <t>1 639</t>
+  </si>
+  <si>
+    <t>костюм абибас</t>
+  </si>
+  <si>
     <t>спортивная одежда +для женщин</t>
   </si>
   <si>
     <t>9 530</t>
   </si>
   <si>
+    <t>спортивная обувь +для мужчин</t>
+  </si>
+  <si>
+    <t>1 569</t>
+  </si>
+  <si>
+    <t>штаны абибас</t>
+  </si>
+  <si>
     <t>спортивная одежда костюмы</t>
   </si>
   <si>
     <t>9 435</t>
   </si>
   <si>
+    <t>спортивная обувь москва</t>
+  </si>
+  <si>
+    <t>1 565</t>
+  </si>
+  <si>
+    <t>абибас 3 полоски</t>
+  </si>
+  <si>
     <t>спортивная одежда официальный сайт</t>
   </si>
   <si>
     <t>8 224</t>
   </si>
   <si>
+    <t>магазин спортивной одежды +и обуви</t>
+  </si>
+  <si>
+    <t>1 555</t>
+  </si>
+  <si>
+    <t>абибас видео</t>
+  </si>
+  <si>
     <t>форвард спортивная одежда</t>
   </si>
   <si>
     <t>7 740</t>
   </si>
   <si>
+    <t>дисконт спортивной обуви</t>
+  </si>
+  <si>
+    <t>1 370</t>
+  </si>
+  <si>
+    <t>логотип абибас</t>
+  </si>
+  <si>
     <t>каталог спортивной одежды</t>
   </si>
   <si>
     <t>7 683</t>
   </si>
   <si>
+    <t>спортивная обувь +для женщин</t>
+  </si>
+  <si>
+    <t>1 315</t>
+  </si>
+  <si>
+    <t>ЗАПРОСЫ «ABIBAS»</t>
+  </si>
+  <si>
     <t>спортивная одежда москва</t>
   </si>
   <si>
     <t>6 863</t>
   </si>
   <si>
-    <t>спортивная одежда +и обувь</t>
-  </si>
-  <si>
-    <t>5 546</t>
+    <t>бренды спортивной обуви</t>
+  </si>
+  <si>
+    <t>1 256</t>
+  </si>
+  <si>
+    <t>285 </t>
+  </si>
+  <si>
+    <t>abibas</t>
+  </si>
+  <si>
+    <t>1 588</t>
+  </si>
+  <si>
+    <t>виды спортивной обуви</t>
+  </si>
+  <si>
+    <t>1 201</t>
+  </si>
+  <si>
+    <t>359 </t>
+  </si>
+  <si>
+    <t>abibas интернет</t>
   </si>
   <si>
     <t>лучшая спортивная одежда</t>
@@ -147,37 +340,79 @@
     <t>5 484</t>
   </si>
   <si>
+    <t>спортивная обувь осень</t>
+  </si>
+  <si>
+    <t>1 111</t>
+  </si>
+  <si>
+    <t>магазин abibas</t>
+  </si>
+  <si>
     <t>фирмы спортивной одежды</t>
   </si>
   <si>
     <t>4 468</t>
   </si>
   <si>
+    <t>лучшая спортивная обувь</t>
+  </si>
+  <si>
+    <t>1 062</t>
+  </si>
+  <si>
+    <t>abibas интернет магазин</t>
+  </si>
+  <si>
     <t>спортивный стиль одежды</t>
   </si>
   <si>
     <t>4 419</t>
   </si>
   <si>
+    <t>+с какой обувью носить спортивные</t>
+  </si>
+  <si>
+    <t>1 057</t>
+  </si>
+  <si>
+    <t>abibas купить</t>
+  </si>
+  <si>
     <t>спортивная одежда большая</t>
   </si>
   <si>
     <t>4 361</t>
   </si>
   <si>
+    <t>спортивная обувь цены</t>
+  </si>
+  <si>
+    <t>кроссовки abibas</t>
+  </si>
+  <si>
     <t>лучшие бренды спортивной одежды</t>
   </si>
   <si>
     <t>4 088</t>
   </si>
   <si>
+    <t>сумка +для спортивной обуви</t>
+  </si>
+  <si>
+    <t>abibas официальный сайт</t>
+  </si>
+  <si>
     <t>спортивная одежда +для мужчин бренды</t>
   </si>
   <si>
     <t>4 075</t>
   </si>
   <si>
-    <t>ЗАПРОС «СПОРТИВНАЯ ОДЕЖДА»</t>
+    <t>обувь спортивная кроссовки</t>
+  </si>
+  <si>
+    <t>abibas шрифт</t>
   </si>
   <si>
     <t>каталог магазинов спортивной одежды</t>
@@ -186,36 +421,57 @@
     <t>4 052</t>
   </si>
   <si>
+    <t>спортивная обувь 2021</t>
+  </si>
+  <si>
+    <t>abibas скачать</t>
+  </si>
+  <si>
     <t>лучшая спортивная одежда +для мужчин</t>
   </si>
   <si>
     <t>3 824</t>
   </si>
   <si>
+    <t>abibas ru</t>
+  </si>
+  <si>
     <t>лучшие бренды спортивной одежды +для мужчин</t>
   </si>
   <si>
     <t>3 785</t>
   </si>
   <si>
+    <t>футболка abibas</t>
+  </si>
+  <si>
     <t>магазин одежды спортивные костюмы</t>
   </si>
   <si>
     <t>3 759</t>
   </si>
   <si>
+    <t>abibas шрифт скачать</t>
+  </si>
+  <si>
     <t>детская спортивная одежда</t>
   </si>
   <si>
     <t>3 115</t>
   </si>
   <si>
+    <t>костюм abibas</t>
+  </si>
+  <si>
     <t>размер спортивной одежды</t>
   </si>
   <si>
     <t>3 097</t>
   </si>
   <si>
+    <t>abibas одежда</t>
+  </si>
+  <si>
     <t>модная спортивная одежда</t>
   </si>
   <si>
@@ -234,258 +490,12 @@
     <t>2 923</t>
   </si>
   <si>
-    <t>ЗАПРОС «СПОРТИВНАЯ ОБУВЬ»</t>
-  </si>
-  <si>
-    <t>спортивная обувь</t>
-  </si>
-  <si>
-    <t>62 918</t>
-  </si>
-  <si>
-    <t>магазин спортивной обуви</t>
-  </si>
-  <si>
-    <t>9 865</t>
-  </si>
-  <si>
-    <t>купить спортивную обувь</t>
-  </si>
-  <si>
-    <t>5 000</t>
-  </si>
-  <si>
-    <t>женская спортивная обувь</t>
-  </si>
-  <si>
-    <t>4 787</t>
-  </si>
-  <si>
-    <t>мужская спортивная обувь</t>
-  </si>
-  <si>
-    <t>4 259</t>
-  </si>
-  <si>
-    <t>обувь спортивная интернет</t>
-  </si>
-  <si>
-    <t>3 262</t>
-  </si>
-  <si>
-    <t>интернет магазин спортивной обуви</t>
-  </si>
-  <si>
-    <t>2 978</t>
-  </si>
-  <si>
-    <t>спортивная зимняя обувь</t>
-  </si>
-  <si>
-    <t>2 557</t>
-  </si>
-  <si>
-    <t>детская спортивная обувь</t>
-  </si>
-  <si>
-    <t>1 726</t>
-  </si>
-  <si>
-    <t>носим спортивную обувь</t>
-  </si>
-  <si>
-    <t>1 639</t>
-  </si>
-  <si>
-    <t>спортивная обувь +для мужчин</t>
-  </si>
-  <si>
-    <t>1 569</t>
-  </si>
-  <si>
-    <t>спортивная обувь москва</t>
-  </si>
-  <si>
-    <t>1 565</t>
-  </si>
-  <si>
-    <t>магазин спортивной одежды +и обуви</t>
-  </si>
-  <si>
-    <t>1 555</t>
-  </si>
-  <si>
-    <t>дисконт спортивной обуви</t>
-  </si>
-  <si>
-    <t>1 370</t>
-  </si>
-  <si>
-    <t>спортивная обувь +для женщин</t>
-  </si>
-  <si>
-    <t>1 315</t>
-  </si>
-  <si>
-    <t>бренды спортивной обуви</t>
-  </si>
-  <si>
-    <t>1 256</t>
-  </si>
-  <si>
-    <t>виды спортивной обуви</t>
-  </si>
-  <si>
-    <t>1 201</t>
-  </si>
-  <si>
-    <t>спортивная обувь осень</t>
-  </si>
-  <si>
-    <t>1 111</t>
-  </si>
-  <si>
-    <t>лучшая спортивная обувь</t>
-  </si>
-  <si>
-    <t>1 062</t>
-  </si>
-  <si>
-    <t>+с какой обувью носить спортивные</t>
-  </si>
-  <si>
-    <t>1 057</t>
-  </si>
-  <si>
-    <t>спортивная обувь цены</t>
-  </si>
-  <si>
-    <t>сумка +для спортивной обуви</t>
-  </si>
-  <si>
-    <t>обувь спортивная кроссовки</t>
-  </si>
-  <si>
-    <t>спортивная обувь 2021</t>
-  </si>
-  <si>
-    <t>285 </t>
-  </si>
-  <si>
-    <t>359 </t>
-  </si>
-  <si>
-    <t>абибас</t>
-  </si>
-  <si>
-    <t>2 216</t>
-  </si>
-  <si>
-    <t>кроссовки абибас</t>
-  </si>
-  <si>
-    <t>абибас купить</t>
-  </si>
-  <si>
-    <t>абибас три полоски</t>
-  </si>
-  <si>
-    <t>адидас абибас</t>
-  </si>
-  <si>
-    <t>фирма абибас</t>
-  </si>
-  <si>
-    <t>скачать абибас</t>
-  </si>
-  <si>
-    <t>абибас фото</t>
-  </si>
-  <si>
-    <t>футболка абибас</t>
-  </si>
-  <si>
-    <t>абибас мем</t>
-  </si>
-  <si>
-    <t>костюм абибас</t>
-  </si>
-  <si>
-    <t>штаны абибас</t>
-  </si>
-  <si>
-    <t>абибас 3 полоски</t>
-  </si>
-  <si>
-    <t>абибас видео</t>
-  </si>
-  <si>
-    <t>логотип абибас</t>
-  </si>
-  <si>
-    <t>ЧАСТОТНОСТЬ</t>
-  </si>
-  <si>
-    <t>"ЧАСТОТНОСТЬ"</t>
-  </si>
-  <si>
-    <t>abibas</t>
-  </si>
-  <si>
-    <t>1 588</t>
-  </si>
-  <si>
-    <t>abibas интернет</t>
-  </si>
-  <si>
-    <t>магазин abibas</t>
-  </si>
-  <si>
-    <t>abibas интернет магазин</t>
-  </si>
-  <si>
-    <t>abibas купить</t>
-  </si>
-  <si>
-    <t>кроссовки abibas</t>
-  </si>
-  <si>
-    <t>abibas официальный сайт</t>
-  </si>
-  <si>
-    <t>abibas шрифт</t>
-  </si>
-  <si>
-    <t>abibas скачать</t>
-  </si>
-  <si>
-    <t>abibas ru</t>
-  </si>
-  <si>
-    <t>футболка abibas</t>
-  </si>
-  <si>
-    <t>abibas шрифт скачать</t>
-  </si>
-  <si>
-    <t>костюм abibas</t>
-  </si>
-  <si>
-    <t>abibas одежда</t>
-  </si>
-  <si>
-    <t>ЗАПРОСЫ «АБИБАС»</t>
-  </si>
-  <si>
-    <t>ЗАПРОСЫ «ABIBAS»</t>
+    <t>ИНТЕРНЕТ</t>
   </si>
   <si>
     <t>ПОКУПКА</t>
   </si>
   <si>
-    <t>ИНТЕРНЕТ</t>
-  </si>
-  <si>
     <t>ДЛЯ МУЖЧИН</t>
   </si>
   <si>
@@ -495,156 +505,156 @@
     <t>ДЛЯ ДЕТЕЙ</t>
   </si>
   <si>
+    <t>ГЛАВНАЯ СТРАНИЦА</t>
+  </si>
+  <si>
+    <t>ОБУВЬ</t>
+  </si>
+  <si>
+    <t>ОДЕЖДА</t>
+  </si>
+  <si>
+    <t>ЗАПРОСЫ</t>
+  </si>
+  <si>
+    <t>MEGAINDEX</t>
+  </si>
+  <si>
+    <t>MAJENTO</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index1.html</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index2.html</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io</t>
+  </si>
+  <si>
     <t>СТРАНИЦА</t>
   </si>
   <si>
+    <t>TITLE</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
     <t>Главная</t>
   </si>
   <si>
+    <t>abibas официальный сайт abibas интернет магазин abibas купить бесплатно</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas. В нашем интернет магазине вы можете купить нашу продукцию: от детской обуви до спортивных костюмов.</t>
+  </si>
+  <si>
     <t>Обувь</t>
   </si>
   <si>
+    <t>abibas официальный сайт лучшая спортивная обувь among us obama abibas купить</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с нашей обувью для всех полов, возрастов и сфер жизни.</t>
+  </si>
+  <si>
     <t>Одежда</t>
   </si>
   <si>
-    <t>abibas официальный сайт abibas интернет магазин abibas купить бесплатно</t>
-  </si>
-  <si>
-    <t>abibas официальный сайт лучшая спортивная обувь among us obama abibas купить</t>
-  </si>
-  <si>
-    <t>TITLE</t>
-  </si>
-  <si>
-    <t>DESCRIPTION</t>
+    <t>abibas интернет магазин спортивной одежды abibas купить спортивная одежда</t>
+  </si>
+  <si>
+    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с моделями нашей одежды и спортивными костюмами.</t>
+  </si>
+  <si>
+    <t>АНКОР</t>
+  </si>
+  <si>
+    <t>АДРЕС</t>
+  </si>
+  <si>
+    <t>ЧАСТОТА АНКОРА</t>
+  </si>
+  <si>
+    <t>ГЛАВНАЯ</t>
+  </si>
+  <si>
+    <t>ГJIАBHAR</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/#</t>
+  </si>
+  <si>
+    <t>ОДЕЖДА И КОСТЮМЫ</t>
+  </si>
+  <si>
+    <t>ПP04ЕЕ</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index3.html</t>
+  </si>
+  <si>
+    <t>здесь</t>
+  </si>
+  <si>
+    <t>СПОРТИВНАЯ ОБУВЬ</t>
+  </si>
+  <si>
+    <t>СПОРТИВНАЯ ОДЕЖДА</t>
+  </si>
+  <si>
+    <t>georgekazanba.github.io/index.html</t>
+  </si>
+  <si>
+    <t>эту</t>
   </si>
   <si>
     <t>РЕЛЕВАНТНОСТЬ</t>
   </si>
   <si>
-    <t>ЗАПРОСЫ</t>
-  </si>
-  <si>
     <t>КОНКУРЕНТ 1</t>
   </si>
   <si>
-    <t>georgekazanba.github.io</t>
+    <t>КОНКУРЕНТ 2</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 3</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 4</t>
+  </si>
+  <si>
+    <t>КОНКУРЕНТ 5</t>
+  </si>
+  <si>
+    <t>https://georgekazanba.github.io/</t>
   </si>
   <si>
     <t>https://www.kant.ru/</t>
   </si>
   <si>
-    <t>https://georgekazanba.github.io/</t>
-  </si>
-  <si>
-    <t>КОНКУРЕНТ 2</t>
-  </si>
-  <si>
     <t>https://spb.rendez-vous.ru/</t>
   </si>
   <si>
-    <t>КОНКУРЕНТ 3</t>
-  </si>
-  <si>
     <t>https://www.planeta-sport.ru/</t>
   </si>
   <si>
-    <t>КОНКУРЕНТ 4</t>
-  </si>
-  <si>
     <t>https://www.traektoria.ru/</t>
   </si>
   <si>
-    <t>КОНКУРЕНТ 5</t>
-  </si>
-  <si>
     <t>https://piter.sportse.ru/</t>
   </si>
   <si>
-    <t>АНКОР</t>
-  </si>
-  <si>
-    <t>ЧАСТОТА АНКОРА</t>
-  </si>
-  <si>
-    <t>АДРЕС</t>
-  </si>
-  <si>
-    <t>ГЛАВНАЯ</t>
-  </si>
-  <si>
-    <t>ГJIАBHAR</t>
-  </si>
-  <si>
-    <t>ОБУВЬ</t>
-  </si>
-  <si>
-    <t>ОДЕЖДА И КОСТЮМЫ</t>
-  </si>
-  <si>
-    <t>ПP04ЕЕ</t>
-  </si>
-  <si>
-    <t>georgekazanba.github.io/index1.html</t>
-  </si>
-  <si>
-    <t>georgekazanba.github.io/index3.html</t>
-  </si>
-  <si>
-    <t>georgekazanba.github.io/index2.html</t>
-  </si>
-  <si>
-    <t>здесь</t>
-  </si>
-  <si>
-    <t>СПОРТИВНАЯ ОБУВЬ</t>
-  </si>
-  <si>
-    <t>СПОРТИВНАЯ ОДЕЖДА</t>
-  </si>
-  <si>
-    <t>эту</t>
-  </si>
-  <si>
-    <t>ГЛАВНАЯ СТРАНИЦА</t>
-  </si>
-  <si>
-    <t>ОДЕЖДА</t>
-  </si>
-  <si>
-    <t>georgekazanba.github.io/#</t>
-  </si>
-  <si>
-    <t>georgekazanba.github.io/index.html</t>
-  </si>
-  <si>
-    <t>MEGAINDEX</t>
-  </si>
-  <si>
-    <t>MAJENTO</t>
-  </si>
-  <si>
-    <t>Добро пожаловать на официальный сайт Abibas. В нашем интернет магазине вы можете купить нашу продукцию: от детской обуви до спортивных костюмов.</t>
-  </si>
-  <si>
-    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с нашей обувью для всех полов, возрастов и сфер жизни.</t>
-  </si>
-  <si>
-    <t>abibas интернет магазин спортивной одежды abibas купить спортивная одежда</t>
-  </si>
-  <si>
-    <t>Добро пожаловать на официальный сайт Abibas, где вы можете ознакомиться с моделями нашей одежды и спортивными костюмами.</t>
-  </si>
-  <si>
     <t>https://georgekazanba.github.io/index2.html</t>
   </si>
   <si>
+    <t>https://www.kant.ru/catalog/clothes/</t>
+  </si>
+  <si>
     <t>https://www.planeta-sport.ru/catalog/wear/</t>
   </si>
   <si>
-    <t>https://www.kant.ru/catalog/clothes/</t>
-  </si>
-  <si>
     <t>УНИКАЛЬНЫЕ ССЫЛКИ</t>
   </si>
   <si>
@@ -654,12 +664,12 @@
     <t>ИНТЕРАКТИВ</t>
   </si>
   <si>
+    <t>консультант, рассылка по почте, личный кабинет, корзина</t>
+  </si>
+  <si>
     <t>консультант, личный кабинет, корзина и желаемое, ссылки на соц. сети, отзывы, рассылка по почте</t>
   </si>
   <si>
-    <t>консультант, рассылка по почте, личный кабинет, корзина</t>
-  </si>
-  <si>
     <t>личный кабинет, корзина</t>
   </si>
   <si>
@@ -667,6 +677,27 @@
   </si>
   <si>
     <t>рассылка по почте</t>
+  </si>
+  <si>
+    <t>kant.ru</t>
+  </si>
+  <si>
+    <t>% БЕЗАНКОРНЫХ</t>
+  </si>
+  <si>
+    <t>% ИКС &gt;500</t>
+  </si>
+  <si>
+    <t>traektoria.ru</t>
+  </si>
+  <si>
+    <t>planeta-sport.ru</t>
+  </si>
+  <si>
+    <t>spb.rendez-vous.ru</t>
+  </si>
+  <si>
+    <t>piter.sportse.ru</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1036,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1049,6 +1080,84 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,88 +1167,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="5" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1163,6 +1209,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
@@ -1184,19 +1233,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1248,7 +1286,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3"/>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1285,7 +1329,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2"/>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1323,7 +1373,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4"/>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1650,33 +1706,33 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="7" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
@@ -1686,30 +1742,30 @@
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3">
         <v>4054</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="G2" s="6">
         <v>1080</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="1" t="s">
-        <v>114</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1">
         <v>944</v>
@@ -1723,27 +1779,27 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2">
         <v>1740</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="G3" s="6">
         <v>676</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="1" t="s">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="J3" s="1">
         <v>116</v>
@@ -1760,27 +1816,27 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C4" s="6">
         <v>19</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G4" s="6">
         <v>173</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="1" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1">
         <v>89</v>
@@ -1797,27 +1853,27 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6">
         <v>1049</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G5" s="6">
         <v>160</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="1" t="s">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1">
         <v>61</v>
@@ -1834,27 +1890,27 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6">
         <v>376</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="1" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="G6" s="6">
         <v>292</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="1" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="J6" s="1">
         <v>52</v>
@@ -1871,27 +1927,27 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C7" s="6">
         <v>1352</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="1" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="G7" s="6">
         <v>407</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="1" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="J7" s="1">
         <v>48</v>
@@ -1908,27 +1964,27 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C8" s="6">
         <v>1103</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G8" s="6">
         <v>23</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="1" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="J8" s="1">
         <v>45</v>
@@ -1941,27 +1997,27 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C9" s="6">
         <v>536</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G9" s="6">
         <v>404</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="1" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="J9" s="1">
         <v>28</v>
@@ -1973,27 +2029,27 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6">
         <v>540</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="G10" s="6">
         <v>159</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="1" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="J10" s="1">
         <v>26</v>
@@ -2005,27 +2061,27 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="C11" s="6">
         <v>10</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="G11" s="6">
         <v>133</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="1" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="J11" s="1">
         <v>26</v>
@@ -2037,27 +2093,27 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6">
         <v>741</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="1" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="G12" s="6">
         <v>4</v>
       </c>
       <c r="H12" s="8"/>
       <c r="I12" s="1" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="J12" s="1">
         <v>24</v>
@@ -2069,27 +2125,27 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C13" s="6">
         <v>591</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="G13" s="6">
         <v>359</v>
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="1" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="J13" s="1">
         <v>22</v>
@@ -2101,27 +2157,27 @@
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C14" s="6">
         <v>40</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="1" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="G14" s="6">
         <v>26</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="1" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="J14" s="1">
         <v>18</v>
@@ -2133,27 +2189,27 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="C15" s="6">
         <v>31</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G15" s="6">
         <v>55</v>
       </c>
       <c r="H15" s="8"/>
       <c r="I15" s="1" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="J15" s="1">
         <v>16</v>
@@ -2165,27 +2221,27 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C16" s="6">
         <v>2479</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G16" s="6">
         <v>77</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="1" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="J16" s="1">
         <v>16</v>
@@ -2197,62 +2253,62 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C17" s="6">
         <v>41</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G17" s="6">
         <v>275</v>
       </c>
       <c r="H17" s="8"/>
       <c r="I17" s="7" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="C18" s="6">
         <v>98</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="H18" s="8"/>
       <c r="I18" s="13" t="s">
-        <v>132</v>
+        <v>91</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="K18" s="13">
         <v>610</v>
@@ -2261,27 +2317,27 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C19" s="6">
         <v>173</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="13" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="J19" s="10">
         <v>122</v>
@@ -2293,27 +2349,27 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="C20" s="6">
         <v>31</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G20" s="6">
         <v>6</v>
       </c>
       <c r="H20" s="8"/>
       <c r="I20" s="13" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="J20" s="10">
         <v>113</v>
@@ -2325,10 +2381,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="C21" s="6">
         <v>582</v>
@@ -2345,7 +2401,7 @@
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="13" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="J21" s="10">
         <v>103</v>
@@ -2357,27 +2413,27 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="C22" s="6">
         <v>365</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G22" s="6">
         <v>3</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="13" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="J22" s="10">
         <v>83</v>
@@ -2389,17 +2445,17 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>112</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
       <c r="C23" s="6">
         <v>6</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F23" s="2">
         <v>984</v>
@@ -2409,7 +2465,7 @@
       </c>
       <c r="H23" s="8"/>
       <c r="I23" s="6" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="J23" s="2">
         <v>81</v>
@@ -2421,17 +2477,17 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="C24" s="6">
         <v>109</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F24" s="2">
         <v>980</v>
@@ -2441,7 +2497,7 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="11" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="J24" s="10">
         <v>60</v>
@@ -2453,17 +2509,17 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="C25" s="6">
         <v>93</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="1" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="F25" s="2">
         <v>952</v>
@@ -2473,7 +2529,7 @@
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="11" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="J25" s="10">
         <v>50</v>
@@ -2485,17 +2541,17 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C26" s="6">
         <v>16</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="F26" s="2">
         <v>937</v>
@@ -2505,7 +2561,7 @@
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="J26" s="2">
         <v>47</v>
@@ -2517,10 +2573,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="C27" s="6">
         <v>23</v>
@@ -2531,7 +2587,7 @@
       <c r="G27" s="9"/>
       <c r="H27" s="8"/>
       <c r="I27" s="6" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="J27" s="2">
         <v>35</v>
@@ -2543,10 +2599,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C28" s="6">
         <v>3467</v>
@@ -2557,7 +2613,7 @@
       <c r="G28" s="9"/>
       <c r="H28" s="8"/>
       <c r="I28" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="J28" s="2">
         <v>31</v>
@@ -2568,10 +2624,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="C29" s="6">
         <v>12</v>
@@ -2582,7 +2638,7 @@
       <c r="G29" s="9"/>
       <c r="H29" s="8"/>
       <c r="I29" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="J29" s="2">
         <v>21</v>
@@ -2593,10 +2649,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="C30" s="6">
         <v>290</v>
@@ -2607,7 +2663,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="8"/>
       <c r="I30" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J30" s="2">
         <v>15</v>
@@ -2618,10 +2674,10 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="C31" s="6">
         <v>29</v>
@@ -2632,7 +2688,7 @@
       <c r="G31" s="9"/>
       <c r="H31" s="8"/>
       <c r="I31" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="J31" s="2">
         <v>14</v>
@@ -2643,10 +2699,10 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="C32" s="6">
         <v>269</v>
@@ -2659,10 +2715,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="C33" s="6">
         <v>4</v>
@@ -2678,10 +2734,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="C34" s="6">
         <v>6</v>
@@ -2721,61 +2777,61 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="7" t="s">
         <v>151</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6">
         <v>19</v>
       </c>
       <c r="D2" s="8"/>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="G2" s="6">
         <v>376</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K2" s="6">
         <v>1103</v>
@@ -2783,30 +2839,30 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C3" s="6">
         <v>1049</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="G3" s="6">
         <v>676</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="K3" s="6">
         <v>741</v>
@@ -2814,30 +2870,30 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C4" s="6">
         <v>676</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G4" s="6">
         <v>41</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="1" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="K4" s="6">
         <v>407</v>
@@ -2845,30 +2901,30 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6">
         <v>536</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="G5" s="6">
         <v>16</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="1" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="K5" s="6">
         <v>93</v>
@@ -2876,30 +2932,30 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="C6" s="6">
         <v>31</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="G6" s="6">
         <v>12</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="1" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="K6" s="6">
         <v>23</v>
@@ -2907,20 +2963,20 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C7" s="6">
         <v>41</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="G7" s="6">
         <v>404</v>
@@ -2930,38 +2986,38 @@
         <v>152</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C8" s="6">
         <v>16</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="G8" s="6">
         <v>4</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="K8" s="6">
         <v>540</v>
@@ -2969,30 +3025,30 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="C9" s="6">
         <v>12</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="G9" s="6">
         <v>6</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="1" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="K9" s="6">
         <v>591</v>
@@ -3000,30 +3056,30 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6">
         <v>23</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="G10" s="6">
         <v>55</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="1" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K10" s="6">
         <v>292</v>
@@ -3031,30 +3087,30 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C11" s="6">
         <v>404</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G11" s="6">
         <v>77</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K11" s="6">
         <v>275</v>
@@ -3062,17 +3118,17 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="C12" s="6">
         <v>4</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F12" s="2">
         <v>984</v>
@@ -3085,25 +3141,25 @@
         <v>153</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>131</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="C13" s="6">
         <v>6</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="6" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="F13" s="2">
         <v>113</v>
@@ -3113,10 +3169,10 @@
       </c>
       <c r="H13" s="8"/>
       <c r="I13" s="1" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="K13" s="6">
         <v>290</v>
@@ -3124,17 +3180,17 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C14" s="6">
         <v>55</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="6" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="F14" s="2">
         <v>103</v>
@@ -3144,10 +3200,10 @@
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="K14" s="6">
         <v>133</v>
@@ -3155,7 +3211,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="B15" s="2">
         <v>122</v>
@@ -3165,7 +3221,7 @@
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="1" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1">
         <v>89</v>
@@ -3180,7 +3236,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="B16" s="2">
         <v>113</v>
@@ -3190,7 +3246,7 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="6" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="F16" s="2">
         <v>83</v>
@@ -3205,7 +3261,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="B17" s="2">
         <v>103</v>
@@ -3221,7 +3277,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B18" s="2">
         <v>60</v>
@@ -3237,7 +3293,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B19" s="2">
         <v>50</v>
@@ -3253,7 +3309,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B20" s="2">
         <v>47</v>
@@ -3264,7 +3320,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1">
         <v>45</v>
@@ -3275,7 +3331,7 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="B22" s="1">
         <v>28</v>
@@ -3286,7 +3342,7 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1">
         <v>26</v>
@@ -3297,7 +3353,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B24" s="2">
         <v>21</v>
@@ -3308,7 +3364,7 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="B25" s="1">
         <v>16</v>
@@ -3341,200 +3397,200 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="51" t="s">
-        <v>191</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="53"/>
+      <c r="B2" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
+      <c r="F2" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="K2" s="52"/>
-      <c r="L2" s="53"/>
+      <c r="J2" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" s="57"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" s="38"/>
-      <c r="F3" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="K3" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>196</v>
+      <c r="B3" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" s="33"/>
+      <c r="F3" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="I3" s="33"/>
+      <c r="J3" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="40">
+      <c r="B4" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="35">
         <v>0.61</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="36">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="40">
+      <c r="F4" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="35">
         <v>0.43</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="36">
         <v>0.80800000000000005</v>
       </c>
-      <c r="J4" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="40">
+      <c r="J4" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="35">
         <v>0.59</v>
       </c>
-      <c r="L4" s="41">
+      <c r="L4" s="36">
         <v>0.82</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="40">
+      <c r="B5" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="35">
         <v>0.59</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="36">
         <v>0.77500000000000002</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5" s="40">
+      <c r="F5" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" s="35">
         <v>0.42</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="36">
         <v>0.79500000000000004</v>
       </c>
-      <c r="J5" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="K5" s="40">
+      <c r="J5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" s="35">
         <v>0.52</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="36">
         <v>0.82299999999999995</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="40">
+      <c r="B6" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="35">
         <v>0.51</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="36">
         <v>0.7</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="35">
         <v>0.43</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="36">
         <v>0.81499999999999995</v>
       </c>
-      <c r="J6" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="40">
+      <c r="J6" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="35">
         <v>0.5</v>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="36">
         <v>0.79800000000000004</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="40">
+      <c r="B7" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="35">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="36">
         <v>0.75</v>
       </c>
-      <c r="F7" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50"/>
-      <c r="J7" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="K7" s="40">
+      <c r="F7" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
+      <c r="J7" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="K7" s="35">
         <v>0.39</v>
       </c>
-      <c r="L7" s="41">
+      <c r="L7" s="36">
         <v>0.84</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="40">
+      <c r="B8" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="35">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="36">
         <v>0.7</v>
       </c>
-      <c r="J8" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="50"/>
+      <c r="J8" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="40">
+      <c r="B9" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="35">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="36">
         <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="48" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50"/>
+      <c r="B10" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3546,6 +3602,42 @@
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="J8:L8"/>
   </mergeCells>
+  <conditionalFormatting sqref="C4:D9">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:H6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:L7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3565,51 +3657,51 @@
   <sheetData>
     <row r="1" spans="2:5" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>161</v>
+      <c r="B2" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="B3" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="E3" s="26"/>
+      <c r="B3" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="2:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="26"/>
+      <c r="B4" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="2:5" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="26"/>
+      <c r="B5" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="E5" s="22"/>
     </row>
     <row r="6" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3629,29 +3721,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="C1" s="21" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="24" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>180</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>193</v>
       </c>
       <c r="C3" s="15">
         <v>1</v>
@@ -3659,32 +3751,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C4" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>182</v>
+      <c r="A5" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C5" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>185</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -3692,10 +3784,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C7" s="15">
         <v>1</v>
@@ -3703,50 +3795,50 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C8" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>188</v>
+      <c r="A9" s="22" t="s">
+        <v>185</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C9" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
-        <v>189</v>
+      <c r="A10" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C10" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
+      <c r="A11" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C12" s="15">
         <v>1</v>
@@ -3754,32 +3846,32 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C13" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>182</v>
+      <c r="A14" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C14" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>185</v>
       </c>
       <c r="C15" s="15">
         <v>1</v>
@@ -3787,10 +3879,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>187</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>194</v>
       </c>
       <c r="C16" s="15">
         <v>1</v>
@@ -3798,50 +3890,50 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C17" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>191</v>
+      <c r="A18" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C18" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>189</v>
+      <c r="A19" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C19" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
+      <c r="A20" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C21" s="15">
         <v>1</v>
@@ -3849,32 +3941,32 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C22" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>182</v>
+      <c r="A23" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C23" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B24" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>185</v>
       </c>
       <c r="C24" s="15">
         <v>1</v>
@@ -3882,10 +3974,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C25" s="15">
         <v>1</v>
@@ -3893,32 +3985,32 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C26" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>191</v>
+      <c r="A27" s="22" t="s">
+        <v>154</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C27" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>188</v>
+      <c r="A28" s="22" t="s">
+        <v>185</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C28" s="15">
         <v>1</v>
@@ -3941,31 +4033,31 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62" t="s">
-        <v>181</v>
-      </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62" t="s">
-        <v>192</v>
-      </c>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
+      <c r="A1" s="60" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4004,542 +4096,542 @@
   <sheetData>
     <row r="1" spans="2:14" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="F2" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="G2" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>162</v>
+      <c r="H2" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="28">
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="28">
+        <v>0.49</v>
+      </c>
+      <c r="G3" s="64" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="28">
+        <v>0.01</v>
+      </c>
+      <c r="I3" s="64" t="s">
+        <v>198</v>
+      </c>
+      <c r="J3" s="28">
+        <v>0.59</v>
+      </c>
+      <c r="K3" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="L3" s="28">
+        <v>0.49</v>
+      </c>
+      <c r="M3" s="64" t="s">
+        <v>200</v>
+      </c>
+      <c r="N3" s="28">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="E4" s="64"/>
+      <c r="F4" s="28">
+        <v>0.27</v>
+      </c>
+      <c r="G4" s="64"/>
+      <c r="H4" s="28">
+        <v>0.15</v>
+      </c>
+      <c r="I4" s="64"/>
+      <c r="J4" s="28">
+        <v>0.18</v>
+      </c>
+      <c r="K4" s="64"/>
+      <c r="L4" s="28">
+        <v>0.3</v>
+      </c>
+      <c r="M4" s="64"/>
+      <c r="N4" s="28">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="28">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="64"/>
+      <c r="F5" s="28">
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="64"/>
+      <c r="H5" s="28">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="64"/>
+      <c r="J5" s="28">
+        <v>0.21</v>
+      </c>
+      <c r="K5" s="64"/>
+      <c r="L5" s="28">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M5" s="64"/>
+      <c r="N5" s="28">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="64"/>
+      <c r="D6" s="28">
+        <v>0.16</v>
+      </c>
+      <c r="E6" s="64"/>
+      <c r="F6" s="28">
+        <v>0.63</v>
+      </c>
+      <c r="G6" s="64"/>
+      <c r="H6" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="64"/>
+      <c r="J6" s="28">
+        <v>0.64</v>
+      </c>
+      <c r="K6" s="64"/>
+      <c r="L6" s="28">
+        <v>0.49</v>
+      </c>
+      <c r="M6" s="64"/>
+      <c r="N6" s="28">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="28">
+        <v>0.63</v>
+      </c>
+      <c r="E7" s="64"/>
+      <c r="F7" s="28">
         <v>0</v>
       </c>
-      <c r="C3" s="58" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="32">
+      <c r="G7" s="64"/>
+      <c r="H7" s="28">
+        <v>0</v>
+      </c>
+      <c r="I7" s="64"/>
+      <c r="J7" s="28">
+        <v>0</v>
+      </c>
+      <c r="K7" s="64"/>
+      <c r="L7" s="28">
+        <v>0</v>
+      </c>
+      <c r="M7" s="64"/>
+      <c r="N7" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="64"/>
+      <c r="D8" s="28">
+        <v>0.61</v>
+      </c>
+      <c r="E8" s="64"/>
+      <c r="F8" s="28">
+        <v>0.01</v>
+      </c>
+      <c r="G8" s="64"/>
+      <c r="H8" s="28">
+        <v>0.18</v>
+      </c>
+      <c r="I8" s="64"/>
+      <c r="J8" s="28">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="64"/>
+      <c r="L8" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="64"/>
+      <c r="N8" s="28">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="64"/>
+      <c r="D9" s="28">
+        <v>0.52</v>
+      </c>
+      <c r="E9" s="64"/>
+      <c r="F9" s="28">
+        <v>0.19</v>
+      </c>
+      <c r="G9" s="64"/>
+      <c r="H9" s="28">
+        <v>0.18</v>
+      </c>
+      <c r="I9" s="64"/>
+      <c r="J9" s="28">
+        <v>0.12</v>
+      </c>
+      <c r="K9" s="64"/>
+      <c r="L9" s="28">
         <v>0.22</v>
       </c>
-      <c r="E3" s="58" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="32">
+      <c r="M9" s="64"/>
+      <c r="N9" s="28">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="64"/>
+      <c r="D10" s="28">
+        <v>0.51</v>
+      </c>
+      <c r="E10" s="64"/>
+      <c r="F10" s="28">
+        <v>0</v>
+      </c>
+      <c r="G10" s="64"/>
+      <c r="H10" s="28">
+        <v>0</v>
+      </c>
+      <c r="I10" s="64"/>
+      <c r="J10" s="28">
+        <v>0</v>
+      </c>
+      <c r="K10" s="64"/>
+      <c r="L10" s="28">
+        <v>0</v>
+      </c>
+      <c r="M10" s="64"/>
+      <c r="N10" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="28">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E11" s="64"/>
+      <c r="F11" s="28">
+        <v>0</v>
+      </c>
+      <c r="G11" s="64"/>
+      <c r="H11" s="28">
+        <v>0</v>
+      </c>
+      <c r="I11" s="64"/>
+      <c r="J11" s="28">
+        <v>0</v>
+      </c>
+      <c r="K11" s="64"/>
+      <c r="L11" s="28">
+        <v>0</v>
+      </c>
+      <c r="M11" s="64"/>
+      <c r="N11" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="64"/>
+      <c r="D12" s="28">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E12" s="64"/>
+      <c r="F12" s="28">
+        <v>0.19</v>
+      </c>
+      <c r="G12" s="64"/>
+      <c r="H12" s="28">
+        <v>0.18</v>
+      </c>
+      <c r="I12" s="64"/>
+      <c r="J12" s="28">
+        <v>0.12</v>
+      </c>
+      <c r="K12" s="64"/>
+      <c r="L12" s="28">
+        <v>0.23</v>
+      </c>
+      <c r="M12" s="64"/>
+      <c r="N12" s="28">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="29"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="28"/>
+    </row>
+    <row r="14" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="28">
         <v>0.49</v>
       </c>
-      <c r="G3" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="H3" s="32">
+      <c r="E14" s="63" t="s">
+        <v>202</v>
+      </c>
+      <c r="F14" s="28">
+        <v>0.49</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>203</v>
+      </c>
+      <c r="J14" s="41">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="66"/>
+      <c r="D15" s="28">
+        <v>0.62</v>
+      </c>
+      <c r="E15" s="62"/>
+      <c r="F15" s="28">
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="62"/>
+      <c r="J15" s="28">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="66"/>
+      <c r="D16" s="28">
+        <v>0.04</v>
+      </c>
+      <c r="E16" s="62"/>
+      <c r="F16" s="28">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I16" s="62"/>
+      <c r="J16" s="28">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="66"/>
+      <c r="D17" s="28">
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="62"/>
+      <c r="F17" s="28">
+        <v>0.19</v>
+      </c>
+      <c r="I17" s="62"/>
+      <c r="J17" s="28">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="66"/>
+      <c r="D18" s="28">
+        <v>0.71</v>
+      </c>
+      <c r="E18" s="62"/>
+      <c r="F18" s="28">
+        <v>0</v>
+      </c>
+      <c r="I18" s="62"/>
+      <c r="J18" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="66"/>
+      <c r="D19" s="28">
+        <v>0.65</v>
+      </c>
+      <c r="E19" s="62"/>
+      <c r="F19" s="28">
+        <v>0</v>
+      </c>
+      <c r="I19" s="62"/>
+      <c r="J19" s="28">
         <v>0.01</v>
       </c>
-      <c r="I3" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="J3" s="32">
-        <v>0.59</v>
-      </c>
-      <c r="K3" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="L3" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="M3" s="58" t="s">
-        <v>175</v>
-      </c>
-      <c r="N3" s="32">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="32">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="32">
-        <v>0.27</v>
-      </c>
-      <c r="G4" s="58"/>
-      <c r="H4" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="K4" s="58"/>
-      <c r="L4" s="32">
-        <v>0.3</v>
-      </c>
-      <c r="M4" s="58"/>
-      <c r="N4" s="32">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="32">
-        <v>0.09</v>
-      </c>
-      <c r="E5" s="58"/>
-      <c r="F5" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="G5" s="58"/>
-      <c r="H5" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="I5" s="58"/>
-      <c r="J5" s="32">
+    </row>
+    <row r="20" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="66"/>
+      <c r="D20" s="28">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E20" s="62"/>
+      <c r="F20" s="28">
+        <v>0</v>
+      </c>
+      <c r="I20" s="62"/>
+      <c r="J20" s="28">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="66"/>
+      <c r="D21" s="28">
+        <v>0.65</v>
+      </c>
+      <c r="E21" s="62"/>
+      <c r="F21" s="28">
+        <v>0.02</v>
+      </c>
+      <c r="I21" s="62"/>
+      <c r="J21" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="28">
         <v>0.21</v>
       </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="32">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M5" s="58"/>
-      <c r="N5" s="32">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="32">
-        <v>0.16</v>
-      </c>
-      <c r="E6" s="58"/>
-      <c r="F6" s="32">
-        <v>0.63</v>
-      </c>
-      <c r="G6" s="58"/>
-      <c r="H6" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="I6" s="58"/>
-      <c r="J6" s="32">
-        <v>0.64</v>
-      </c>
-      <c r="K6" s="58"/>
-      <c r="L6" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="M6" s="58"/>
-      <c r="N6" s="32">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="32">
-        <v>0.63</v>
-      </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="32">
+      <c r="E22" s="62"/>
+      <c r="F22" s="28">
         <v>0</v>
       </c>
-      <c r="G7" s="58"/>
-      <c r="H7" s="32">
+      <c r="I22" s="62"/>
+      <c r="J22" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="58"/>
-      <c r="J7" s="32">
-        <v>0</v>
-      </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="32">
-        <v>0</v>
-      </c>
-      <c r="M7" s="58"/>
-      <c r="N7" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="32">
-        <v>0.61</v>
-      </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="32">
+    </row>
+    <row r="23" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="67"/>
+      <c r="D23" s="28">
+        <v>0.42</v>
+      </c>
+      <c r="E23" s="62"/>
+      <c r="F23" s="28">
         <v>0.01</v>
       </c>
-      <c r="G8" s="58"/>
-      <c r="H8" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="K8" s="58"/>
-      <c r="L8" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="32">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="32">
-        <v>0.52</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="G9" s="58"/>
-      <c r="H9" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="I9" s="58"/>
-      <c r="J9" s="32">
-        <v>0.12</v>
-      </c>
-      <c r="K9" s="58"/>
-      <c r="L9" s="32">
-        <v>0.22</v>
-      </c>
-      <c r="M9" s="58"/>
-      <c r="N9" s="32">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="32">
-        <v>0.51</v>
-      </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="32">
-        <v>0</v>
-      </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="32">
-        <v>0</v>
-      </c>
-      <c r="I10" s="58"/>
-      <c r="J10" s="32">
-        <v>0</v>
-      </c>
-      <c r="K10" s="58"/>
-      <c r="L10" s="32">
-        <v>0</v>
-      </c>
-      <c r="M10" s="58"/>
-      <c r="N10" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="32">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="32">
-        <v>0</v>
-      </c>
-      <c r="G11" s="58"/>
-      <c r="H11" s="32">
-        <v>0</v>
-      </c>
-      <c r="I11" s="58"/>
-      <c r="J11" s="32">
-        <v>0</v>
-      </c>
-      <c r="K11" s="58"/>
-      <c r="L11" s="32">
-        <v>0</v>
-      </c>
-      <c r="M11" s="58"/>
-      <c r="N11" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="32">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="G12" s="58"/>
-      <c r="H12" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="I12" s="58"/>
-      <c r="J12" s="32">
-        <v>0.12</v>
-      </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="32">
-        <v>0.23</v>
-      </c>
-      <c r="M12" s="58"/>
-      <c r="N12" s="32">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="33"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="32"/>
-    </row>
-    <row r="14" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="D14" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="F14" s="32">
-        <v>0.49</v>
-      </c>
-      <c r="I14" s="55" t="s">
-        <v>202</v>
-      </c>
-      <c r="J14" s="46">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="60"/>
-      <c r="D15" s="32">
-        <v>0.62</v>
-      </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="32">
-        <v>0.2</v>
-      </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="32">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="32">
-        <v>0.04</v>
-      </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="32">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="32">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="32">
-        <v>0.18</v>
-      </c>
-      <c r="E17" s="56"/>
-      <c r="F17" s="32">
-        <v>0.19</v>
-      </c>
-      <c r="I17" s="56"/>
-      <c r="J17" s="32">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="32">
-        <v>0.71</v>
-      </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="I18" s="56"/>
-      <c r="J18" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="32">
-        <v>0.65</v>
-      </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="32">
-        <v>0</v>
-      </c>
-      <c r="I19" s="56"/>
-      <c r="J19" s="32">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="32">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="32">
-        <v>0</v>
-      </c>
-      <c r="I20" s="56"/>
-      <c r="J20" s="32">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="32">
-        <v>0.65</v>
-      </c>
-      <c r="E21" s="56"/>
-      <c r="F21" s="32">
-        <v>0.02</v>
-      </c>
-      <c r="I21" s="56"/>
-      <c r="J21" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="32">
-        <v>0.21</v>
-      </c>
-      <c r="E22" s="56"/>
-      <c r="F22" s="32">
-        <v>0</v>
-      </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="61"/>
-      <c r="D23" s="32">
-        <v>0.42</v>
-      </c>
-      <c r="E23" s="56"/>
-      <c r="F23" s="32">
-        <v>0.01</v>
-      </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="32">
+      <c r="I23" s="62"/>
+      <c r="J23" s="28">
         <v>0.12</v>
       </c>
     </row>
     <row r="24" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="42" t="s">
         <v>204</v>
       </c>
       <c r="C25" s="15">
@@ -4579,6 +4671,66 @@
     <mergeCell ref="K3:K12"/>
     <mergeCell ref="C14:C23"/>
   </mergeCells>
+  <conditionalFormatting sqref="D3:D23">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F23">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L12 N3:N12">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1"/>
     <hyperlink ref="C3" r:id="rId2"/>
@@ -4605,83 +4757,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="21" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
-        <v>166</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="66" t="s">
-        <v>173</v>
+      <c r="A5" s="51" t="s">
+        <v>199</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="22" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
+      <c r="A7" s="50"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="66" t="s">
-        <v>167</v>
+      <c r="A8" s="51" t="s">
+        <v>195</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
+      <c r="A9" s="50"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
+      <c r="A10" s="50"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
+      <c r="A11" s="50"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
+      <c r="A12" s="50"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
+      <c r="A13" s="50"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
+      <c r="A14" s="50"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4690,7 +4842,118 @@
     <hyperlink ref="A4" r:id="rId3"/>
     <hyperlink ref="A5" r:id="rId4"/>
     <hyperlink ref="A8" r:id="rId5"/>
+    <hyperlink ref="A6" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="52" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="69">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="C2" s="69">
+        <v>0.31900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="52" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="69">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C3" s="69">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="69">
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="C4" s="69">
+        <v>0.13500000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="69">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="C5" s="69">
+        <v>0.20699999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="69">
+        <v>0</v>
+      </c>
+      <c r="C6" s="69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" tabRatio="619" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="220">
   <si>
     <t>ЗАПРОС «СПОРТИВНАЯ ОДЕЖДА»</t>
   </si>
@@ -698,6 +698,9 @@
   </si>
   <si>
     <t>piter.sportse.ru</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1188,54 +1191,54 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -3397,23 +3400,23 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="58" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="58" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="58"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="60"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="30" t="s">
@@ -3543,11 +3546,11 @@
       <c r="D7" s="36">
         <v>0.75</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="57"/>
       <c r="J7" s="34" t="s">
         <v>5</v>
       </c>
@@ -3568,11 +3571,11 @@
       <c r="D8" s="36">
         <v>0.7</v>
       </c>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="55" t="s">
         <v>161</v>
       </c>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="57"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
@@ -3586,11 +3589,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="57"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3735,8 +3738,8 @@
       <c r="A2" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -3830,8 +3833,8 @@
       <c r="A11" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
@@ -3925,8 +3928,8 @@
       <c r="A20" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
@@ -4033,31 +4036,31 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="62" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60" t="s">
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4140,37 +4143,37 @@
       <c r="B3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="66" t="s">
         <v>195</v>
       </c>
       <c r="D3" s="28">
         <v>0.22</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="66" t="s">
         <v>196</v>
       </c>
       <c r="F3" s="28">
         <v>0.49</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="66" t="s">
         <v>197</v>
       </c>
       <c r="H3" s="28">
         <v>0.01</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="66" t="s">
         <v>198</v>
       </c>
       <c r="J3" s="28">
         <v>0.59</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="66" t="s">
         <v>199</v>
       </c>
       <c r="L3" s="28">
         <v>0.49</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="66" t="s">
         <v>200</v>
       </c>
       <c r="N3" s="28">
@@ -4181,27 +4184,27 @@
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="64"/>
+      <c r="C4" s="66"/>
       <c r="D4" s="28">
         <v>0.25</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="66"/>
       <c r="F4" s="28">
         <v>0.27</v>
       </c>
-      <c r="G4" s="64"/>
+      <c r="G4" s="66"/>
       <c r="H4" s="28">
         <v>0.15</v>
       </c>
-      <c r="I4" s="64"/>
+      <c r="I4" s="66"/>
       <c r="J4" s="28">
         <v>0.18</v>
       </c>
-      <c r="K4" s="64"/>
+      <c r="K4" s="66"/>
       <c r="L4" s="28">
         <v>0.3</v>
       </c>
-      <c r="M4" s="64"/>
+      <c r="M4" s="66"/>
       <c r="N4" s="28">
         <v>0.26</v>
       </c>
@@ -4210,27 +4213,27 @@
       <c r="B5" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="64"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="28">
         <v>0.09</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="66"/>
       <c r="F5" s="28">
         <v>0.19</v>
       </c>
-      <c r="G5" s="64"/>
+      <c r="G5" s="66"/>
       <c r="H5" s="28">
         <v>0.15</v>
       </c>
-      <c r="I5" s="64"/>
+      <c r="I5" s="66"/>
       <c r="J5" s="28">
         <v>0.21</v>
       </c>
-      <c r="K5" s="64"/>
+      <c r="K5" s="66"/>
       <c r="L5" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="64"/>
+      <c r="M5" s="66"/>
       <c r="N5" s="28">
         <v>0.26</v>
       </c>
@@ -4239,27 +4242,27 @@
       <c r="B6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="64"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="28">
         <v>0.16</v>
       </c>
-      <c r="E6" s="64"/>
+      <c r="E6" s="66"/>
       <c r="F6" s="28">
         <v>0.63</v>
       </c>
-      <c r="G6" s="64"/>
+      <c r="G6" s="66"/>
       <c r="H6" s="28">
         <v>0.5</v>
       </c>
-      <c r="I6" s="64"/>
+      <c r="I6" s="66"/>
       <c r="J6" s="28">
         <v>0.64</v>
       </c>
-      <c r="K6" s="64"/>
+      <c r="K6" s="66"/>
       <c r="L6" s="28">
         <v>0.49</v>
       </c>
-      <c r="M6" s="64"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="28">
         <v>0.2</v>
       </c>
@@ -4268,27 +4271,27 @@
       <c r="B7" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="64"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="28">
         <v>0.63</v>
       </c>
-      <c r="E7" s="64"/>
+      <c r="E7" s="66"/>
       <c r="F7" s="28">
         <v>0</v>
       </c>
-      <c r="G7" s="64"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="64"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="28">
         <v>0</v>
       </c>
-      <c r="K7" s="64"/>
+      <c r="K7" s="66"/>
       <c r="L7" s="28">
         <v>0</v>
       </c>
-      <c r="M7" s="64"/>
+      <c r="M7" s="66"/>
       <c r="N7" s="28">
         <v>0</v>
       </c>
@@ -4297,27 +4300,27 @@
       <c r="B8" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="64"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="28">
         <v>0.61</v>
       </c>
-      <c r="E8" s="64"/>
+      <c r="E8" s="66"/>
       <c r="F8" s="28">
         <v>0.01</v>
       </c>
-      <c r="G8" s="64"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="28">
         <v>0.18</v>
       </c>
-      <c r="I8" s="64"/>
+      <c r="I8" s="66"/>
       <c r="J8" s="28">
         <v>0.01</v>
       </c>
-      <c r="K8" s="64"/>
+      <c r="K8" s="66"/>
       <c r="L8" s="28">
         <v>0.2</v>
       </c>
-      <c r="M8" s="64"/>
+      <c r="M8" s="66"/>
       <c r="N8" s="28">
         <v>0.17</v>
       </c>
@@ -4326,27 +4329,27 @@
       <c r="B9" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="28">
         <v>0.52</v>
       </c>
-      <c r="E9" s="64"/>
+      <c r="E9" s="66"/>
       <c r="F9" s="28">
         <v>0.19</v>
       </c>
-      <c r="G9" s="64"/>
+      <c r="G9" s="66"/>
       <c r="H9" s="28">
         <v>0.18</v>
       </c>
-      <c r="I9" s="64"/>
+      <c r="I9" s="66"/>
       <c r="J9" s="28">
         <v>0.12</v>
       </c>
-      <c r="K9" s="64"/>
+      <c r="K9" s="66"/>
       <c r="L9" s="28">
         <v>0.22</v>
       </c>
-      <c r="M9" s="64"/>
+      <c r="M9" s="66"/>
       <c r="N9" s="28">
         <v>0.18</v>
       </c>
@@ -4355,27 +4358,27 @@
       <c r="B10" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="64"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="28">
         <v>0.51</v>
       </c>
-      <c r="E10" s="64"/>
+      <c r="E10" s="66"/>
       <c r="F10" s="28">
         <v>0</v>
       </c>
-      <c r="G10" s="64"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="28">
         <v>0</v>
       </c>
-      <c r="I10" s="64"/>
+      <c r="I10" s="66"/>
       <c r="J10" s="28">
         <v>0</v>
       </c>
-      <c r="K10" s="64"/>
+      <c r="K10" s="66"/>
       <c r="L10" s="28">
         <v>0</v>
       </c>
-      <c r="M10" s="64"/>
+      <c r="M10" s="66"/>
       <c r="N10" s="28">
         <v>0</v>
       </c>
@@ -4384,27 +4387,27 @@
       <c r="B11" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="64"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="28">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E11" s="64"/>
+      <c r="E11" s="66"/>
       <c r="F11" s="28">
         <v>0</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="66"/>
       <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="64"/>
+      <c r="I11" s="66"/>
       <c r="J11" s="28">
         <v>0</v>
       </c>
-      <c r="K11" s="64"/>
+      <c r="K11" s="66"/>
       <c r="L11" s="28">
         <v>0</v>
       </c>
-      <c r="M11" s="64"/>
+      <c r="M11" s="66"/>
       <c r="N11" s="28">
         <v>0</v>
       </c>
@@ -4413,27 +4416,27 @@
       <c r="B12" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="28">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E12" s="64"/>
+      <c r="E12" s="66"/>
       <c r="F12" s="28">
         <v>0.19</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="66"/>
       <c r="H12" s="28">
         <v>0.18</v>
       </c>
-      <c r="I12" s="64"/>
+      <c r="I12" s="66"/>
       <c r="J12" s="28">
         <v>0.12</v>
       </c>
-      <c r="K12" s="64"/>
+      <c r="K12" s="66"/>
       <c r="L12" s="28">
         <v>0.23</v>
       </c>
-      <c r="M12" s="64"/>
+      <c r="M12" s="66"/>
       <c r="N12" s="28">
         <v>0.18</v>
       </c>
@@ -4457,19 +4460,19 @@
       <c r="B14" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="67" t="s">
         <v>201</v>
       </c>
       <c r="D14" s="28">
         <v>0.49</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="65" t="s">
         <v>202</v>
       </c>
       <c r="F14" s="28">
         <v>0.49</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="63" t="s">
         <v>203</v>
       </c>
       <c r="J14" s="41">
@@ -4480,15 +4483,15 @@
       <c r="B15" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="66"/>
+      <c r="C15" s="68"/>
       <c r="D15" s="28">
         <v>0.62</v>
       </c>
-      <c r="E15" s="62"/>
+      <c r="E15" s="64"/>
       <c r="F15" s="28">
         <v>0.2</v>
       </c>
-      <c r="I15" s="62"/>
+      <c r="I15" s="64"/>
       <c r="J15" s="28">
         <v>0.18</v>
       </c>
@@ -4497,15 +4500,15 @@
       <c r="B16" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="28">
         <v>0.04</v>
       </c>
-      <c r="E16" s="62"/>
+      <c r="E16" s="64"/>
       <c r="F16" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I16" s="62"/>
+      <c r="I16" s="64"/>
       <c r="J16" s="28">
         <v>0.21</v>
       </c>
@@ -4514,15 +4517,15 @@
       <c r="B17" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="66"/>
+      <c r="C17" s="68"/>
       <c r="D17" s="28">
         <v>0.18</v>
       </c>
-      <c r="E17" s="62"/>
+      <c r="E17" s="64"/>
       <c r="F17" s="28">
         <v>0.19</v>
       </c>
-      <c r="I17" s="62"/>
+      <c r="I17" s="64"/>
       <c r="J17" s="28">
         <v>0.64</v>
       </c>
@@ -4531,15 +4534,15 @@
       <c r="B18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="66"/>
+      <c r="C18" s="68"/>
       <c r="D18" s="28">
         <v>0.71</v>
       </c>
-      <c r="E18" s="62"/>
+      <c r="E18" s="64"/>
       <c r="F18" s="28">
         <v>0</v>
       </c>
-      <c r="I18" s="62"/>
+      <c r="I18" s="64"/>
       <c r="J18" s="28">
         <v>0</v>
       </c>
@@ -4548,15 +4551,15 @@
       <c r="B19" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="66"/>
+      <c r="C19" s="68"/>
       <c r="D19" s="28">
         <v>0.65</v>
       </c>
-      <c r="E19" s="62"/>
+      <c r="E19" s="64"/>
       <c r="F19" s="28">
         <v>0</v>
       </c>
-      <c r="I19" s="62"/>
+      <c r="I19" s="64"/>
       <c r="J19" s="28">
         <v>0.01</v>
       </c>
@@ -4565,15 +4568,15 @@
       <c r="B20" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="66"/>
+      <c r="C20" s="68"/>
       <c r="D20" s="28">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E20" s="62"/>
+      <c r="E20" s="64"/>
       <c r="F20" s="28">
         <v>0</v>
       </c>
-      <c r="I20" s="62"/>
+      <c r="I20" s="64"/>
       <c r="J20" s="28">
         <v>0.12</v>
       </c>
@@ -4582,15 +4585,15 @@
       <c r="B21" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="68"/>
       <c r="D21" s="28">
         <v>0.65</v>
       </c>
-      <c r="E21" s="62"/>
+      <c r="E21" s="64"/>
       <c r="F21" s="28">
         <v>0.02</v>
       </c>
-      <c r="I21" s="62"/>
+      <c r="I21" s="64"/>
       <c r="J21" s="28">
         <v>0</v>
       </c>
@@ -4599,15 +4602,15 @@
       <c r="B22" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="66"/>
+      <c r="C22" s="68"/>
       <c r="D22" s="28">
         <v>0.21</v>
       </c>
-      <c r="E22" s="62"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="28">
         <v>0</v>
       </c>
-      <c r="I22" s="62"/>
+      <c r="I22" s="64"/>
       <c r="J22" s="28">
         <v>0</v>
       </c>
@@ -4616,15 +4619,15 @@
       <c r="B23" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="28">
         <v>0.42</v>
       </c>
-      <c r="E23" s="62"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="28">
         <v>0.01</v>
       </c>
-      <c r="I23" s="62"/>
+      <c r="I23" s="64"/>
       <c r="J23" s="28">
         <v>0.12</v>
       </c>
@@ -4850,15 +4853,17 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>205</v>
       </c>
@@ -4868,69 +4873,105 @@
       <c r="C1" s="21" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="52" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="69">
+      <c r="B2" s="54">
         <v>0.47699999999999998</v>
       </c>
-      <c r="C2" s="69">
+      <c r="C2" s="54">
         <v>0.31900000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E2" s="15">
+        <v>2</v>
+      </c>
+      <c r="F2" s="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="69">
+      <c r="B3" s="54">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C3" s="69">
+      <c r="C3" s="54">
         <v>0.26</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" s="15">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="69">
+      <c r="B4" s="54">
         <v>0.29899999999999999</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="54">
         <v>0.13500000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E4" s="15">
+        <v>4</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="54">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="54">
         <v>0.20699999999999999</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E5" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="69">
+      <c r="B6" s="54">
         <v>0</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="54">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
+      <c r="E6" s="15">
+        <v>29</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4942,7 +4983,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C6">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4953,6 +4994,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2:F6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" tabRatio="619" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" tabRatio="526" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="227">
   <si>
     <t>ЗАПРОС «СПОРТИВНАЯ ОДЕЖДА»</t>
   </si>
@@ -697,10 +697,31 @@
     <t>spb.rendez-vous.ru</t>
   </si>
   <si>
-    <t>piter.sportse.ru</t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>МЕСТО ПО ЗАПРОСУ</t>
+  </si>
+  <si>
+    <t>КОЛ-ВО ССЫЛОК</t>
+  </si>
+  <si>
+    <t>% ИКС 200-500</t>
+  </si>
+  <si>
+    <t>% ИКС 100-200</t>
+  </si>
+  <si>
+    <t>% ИКС 50-100</t>
+  </si>
+  <si>
+    <t>% ИКС 20-50</t>
+  </si>
+  <si>
+    <t>% ИКС 0-20</t>
+  </si>
+  <si>
+    <t>ИКС</t>
   </si>
 </sst>
 </file>
@@ -818,7 +839,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1028,6 +1049,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1039,7 +1075,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1188,34 +1224,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1239,6 +1271,28 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -3400,23 +3454,23 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="60"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="58" t="s">
+      <c r="J2" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="60"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="58"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="30" t="s">
@@ -3546,11 +3600,11 @@
       <c r="D7" s="36">
         <v>0.75</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="53" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="57"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55"/>
       <c r="J7" s="34" t="s">
         <v>5</v>
       </c>
@@ -3571,11 +3625,11 @@
       <c r="D8" s="36">
         <v>0.7</v>
       </c>
-      <c r="J8" s="55" t="s">
+      <c r="J8" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="K8" s="56"/>
-      <c r="L8" s="57"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
@@ -3589,11 +3643,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="57"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="55"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3738,8 +3792,8 @@
       <c r="A2" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -3833,8 +3887,8 @@
       <c r="A11" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
@@ -3928,8 +3982,8 @@
       <c r="A20" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
@@ -4036,31 +4090,31 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="60" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62" t="s">
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62" t="s">
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4143,37 +4197,37 @@
       <c r="B3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="66" t="s">
+      <c r="C3" s="64" t="s">
         <v>195</v>
       </c>
       <c r="D3" s="28">
         <v>0.22</v>
       </c>
-      <c r="E3" s="66" t="s">
+      <c r="E3" s="64" t="s">
         <v>196</v>
       </c>
       <c r="F3" s="28">
         <v>0.49</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="G3" s="64" t="s">
         <v>197</v>
       </c>
       <c r="H3" s="28">
         <v>0.01</v>
       </c>
-      <c r="I3" s="66" t="s">
+      <c r="I3" s="64" t="s">
         <v>198</v>
       </c>
       <c r="J3" s="28">
         <v>0.59</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="K3" s="64" t="s">
         <v>199</v>
       </c>
       <c r="L3" s="28">
         <v>0.49</v>
       </c>
-      <c r="M3" s="66" t="s">
+      <c r="M3" s="64" t="s">
         <v>200</v>
       </c>
       <c r="N3" s="28">
@@ -4184,27 +4238,27 @@
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="66"/>
+      <c r="C4" s="64"/>
       <c r="D4" s="28">
         <v>0.25</v>
       </c>
-      <c r="E4" s="66"/>
+      <c r="E4" s="64"/>
       <c r="F4" s="28">
         <v>0.27</v>
       </c>
-      <c r="G4" s="66"/>
+      <c r="G4" s="64"/>
       <c r="H4" s="28">
         <v>0.15</v>
       </c>
-      <c r="I4" s="66"/>
+      <c r="I4" s="64"/>
       <c r="J4" s="28">
         <v>0.18</v>
       </c>
-      <c r="K4" s="66"/>
+      <c r="K4" s="64"/>
       <c r="L4" s="28">
         <v>0.3</v>
       </c>
-      <c r="M4" s="66"/>
+      <c r="M4" s="64"/>
       <c r="N4" s="28">
         <v>0.26</v>
       </c>
@@ -4213,27 +4267,27 @@
       <c r="B5" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="66"/>
+      <c r="C5" s="64"/>
       <c r="D5" s="28">
         <v>0.09</v>
       </c>
-      <c r="E5" s="66"/>
+      <c r="E5" s="64"/>
       <c r="F5" s="28">
         <v>0.19</v>
       </c>
-      <c r="G5" s="66"/>
+      <c r="G5" s="64"/>
       <c r="H5" s="28">
         <v>0.15</v>
       </c>
-      <c r="I5" s="66"/>
+      <c r="I5" s="64"/>
       <c r="J5" s="28">
         <v>0.21</v>
       </c>
-      <c r="K5" s="66"/>
+      <c r="K5" s="64"/>
       <c r="L5" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="66"/>
+      <c r="M5" s="64"/>
       <c r="N5" s="28">
         <v>0.26</v>
       </c>
@@ -4242,27 +4296,27 @@
       <c r="B6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="66"/>
+      <c r="C6" s="64"/>
       <c r="D6" s="28">
         <v>0.16</v>
       </c>
-      <c r="E6" s="66"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="28">
         <v>0.63</v>
       </c>
-      <c r="G6" s="66"/>
+      <c r="G6" s="64"/>
       <c r="H6" s="28">
         <v>0.5</v>
       </c>
-      <c r="I6" s="66"/>
+      <c r="I6" s="64"/>
       <c r="J6" s="28">
         <v>0.64</v>
       </c>
-      <c r="K6" s="66"/>
+      <c r="K6" s="64"/>
       <c r="L6" s="28">
         <v>0.49</v>
       </c>
-      <c r="M6" s="66"/>
+      <c r="M6" s="64"/>
       <c r="N6" s="28">
         <v>0.2</v>
       </c>
@@ -4271,27 +4325,27 @@
       <c r="B7" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="66"/>
+      <c r="C7" s="64"/>
       <c r="D7" s="28">
         <v>0.63</v>
       </c>
-      <c r="E7" s="66"/>
+      <c r="E7" s="64"/>
       <c r="F7" s="28">
         <v>0</v>
       </c>
-      <c r="G7" s="66"/>
+      <c r="G7" s="64"/>
       <c r="H7" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="66"/>
+      <c r="I7" s="64"/>
       <c r="J7" s="28">
         <v>0</v>
       </c>
-      <c r="K7" s="66"/>
+      <c r="K7" s="64"/>
       <c r="L7" s="28">
         <v>0</v>
       </c>
-      <c r="M7" s="66"/>
+      <c r="M7" s="64"/>
       <c r="N7" s="28">
         <v>0</v>
       </c>
@@ -4300,27 +4354,27 @@
       <c r="B8" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="66"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="28">
         <v>0.61</v>
       </c>
-      <c r="E8" s="66"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="28">
         <v>0.01</v>
       </c>
-      <c r="G8" s="66"/>
+      <c r="G8" s="64"/>
       <c r="H8" s="28">
         <v>0.18</v>
       </c>
-      <c r="I8" s="66"/>
+      <c r="I8" s="64"/>
       <c r="J8" s="28">
         <v>0.01</v>
       </c>
-      <c r="K8" s="66"/>
+      <c r="K8" s="64"/>
       <c r="L8" s="28">
         <v>0.2</v>
       </c>
-      <c r="M8" s="66"/>
+      <c r="M8" s="64"/>
       <c r="N8" s="28">
         <v>0.17</v>
       </c>
@@ -4329,27 +4383,27 @@
       <c r="B9" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="66"/>
+      <c r="C9" s="64"/>
       <c r="D9" s="28">
         <v>0.52</v>
       </c>
-      <c r="E9" s="66"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="28">
         <v>0.19</v>
       </c>
-      <c r="G9" s="66"/>
+      <c r="G9" s="64"/>
       <c r="H9" s="28">
         <v>0.18</v>
       </c>
-      <c r="I9" s="66"/>
+      <c r="I9" s="64"/>
       <c r="J9" s="28">
         <v>0.12</v>
       </c>
-      <c r="K9" s="66"/>
+      <c r="K9" s="64"/>
       <c r="L9" s="28">
         <v>0.22</v>
       </c>
-      <c r="M9" s="66"/>
+      <c r="M9" s="64"/>
       <c r="N9" s="28">
         <v>0.18</v>
       </c>
@@ -4358,27 +4412,27 @@
       <c r="B10" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="66"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="28">
         <v>0.51</v>
       </c>
-      <c r="E10" s="66"/>
+      <c r="E10" s="64"/>
       <c r="F10" s="28">
         <v>0</v>
       </c>
-      <c r="G10" s="66"/>
+      <c r="G10" s="64"/>
       <c r="H10" s="28">
         <v>0</v>
       </c>
-      <c r="I10" s="66"/>
+      <c r="I10" s="64"/>
       <c r="J10" s="28">
         <v>0</v>
       </c>
-      <c r="K10" s="66"/>
+      <c r="K10" s="64"/>
       <c r="L10" s="28">
         <v>0</v>
       </c>
-      <c r="M10" s="66"/>
+      <c r="M10" s="64"/>
       <c r="N10" s="28">
         <v>0</v>
       </c>
@@ -4387,27 +4441,27 @@
       <c r="B11" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="66"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="28">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E11" s="66"/>
+      <c r="E11" s="64"/>
       <c r="F11" s="28">
         <v>0</v>
       </c>
-      <c r="G11" s="66"/>
+      <c r="G11" s="64"/>
       <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="66"/>
+      <c r="I11" s="64"/>
       <c r="J11" s="28">
         <v>0</v>
       </c>
-      <c r="K11" s="66"/>
+      <c r="K11" s="64"/>
       <c r="L11" s="28">
         <v>0</v>
       </c>
-      <c r="M11" s="66"/>
+      <c r="M11" s="64"/>
       <c r="N11" s="28">
         <v>0</v>
       </c>
@@ -4416,27 +4470,27 @@
       <c r="B12" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="66"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="28">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E12" s="66"/>
+      <c r="E12" s="64"/>
       <c r="F12" s="28">
         <v>0.19</v>
       </c>
-      <c r="G12" s="66"/>
+      <c r="G12" s="64"/>
       <c r="H12" s="28">
         <v>0.18</v>
       </c>
-      <c r="I12" s="66"/>
+      <c r="I12" s="64"/>
       <c r="J12" s="28">
         <v>0.12</v>
       </c>
-      <c r="K12" s="66"/>
+      <c r="K12" s="64"/>
       <c r="L12" s="28">
         <v>0.23</v>
       </c>
-      <c r="M12" s="66"/>
+      <c r="M12" s="64"/>
       <c r="N12" s="28">
         <v>0.18</v>
       </c>
@@ -4460,19 +4514,19 @@
       <c r="B14" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="65" t="s">
         <v>201</v>
       </c>
       <c r="D14" s="28">
         <v>0.49</v>
       </c>
-      <c r="E14" s="65" t="s">
+      <c r="E14" s="63" t="s">
         <v>202</v>
       </c>
       <c r="F14" s="28">
         <v>0.49</v>
       </c>
-      <c r="I14" s="63" t="s">
+      <c r="I14" s="61" t="s">
         <v>203</v>
       </c>
       <c r="J14" s="41">
@@ -4483,15 +4537,15 @@
       <c r="B15" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="68"/>
+      <c r="C15" s="66"/>
       <c r="D15" s="28">
         <v>0.62</v>
       </c>
-      <c r="E15" s="64"/>
+      <c r="E15" s="62"/>
       <c r="F15" s="28">
         <v>0.2</v>
       </c>
-      <c r="I15" s="64"/>
+      <c r="I15" s="62"/>
       <c r="J15" s="28">
         <v>0.18</v>
       </c>
@@ -4500,15 +4554,15 @@
       <c r="B16" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="68"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="28">
         <v>0.04</v>
       </c>
-      <c r="E16" s="64"/>
+      <c r="E16" s="62"/>
       <c r="F16" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I16" s="64"/>
+      <c r="I16" s="62"/>
       <c r="J16" s="28">
         <v>0.21</v>
       </c>
@@ -4517,15 +4571,15 @@
       <c r="B17" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="68"/>
+      <c r="C17" s="66"/>
       <c r="D17" s="28">
         <v>0.18</v>
       </c>
-      <c r="E17" s="64"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="28">
         <v>0.19</v>
       </c>
-      <c r="I17" s="64"/>
+      <c r="I17" s="62"/>
       <c r="J17" s="28">
         <v>0.64</v>
       </c>
@@ -4534,15 +4588,15 @@
       <c r="B18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="68"/>
+      <c r="C18" s="66"/>
       <c r="D18" s="28">
         <v>0.71</v>
       </c>
-      <c r="E18" s="64"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="28">
         <v>0</v>
       </c>
-      <c r="I18" s="64"/>
+      <c r="I18" s="62"/>
       <c r="J18" s="28">
         <v>0</v>
       </c>
@@ -4551,15 +4605,15 @@
       <c r="B19" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="68"/>
+      <c r="C19" s="66"/>
       <c r="D19" s="28">
         <v>0.65</v>
       </c>
-      <c r="E19" s="64"/>
+      <c r="E19" s="62"/>
       <c r="F19" s="28">
         <v>0</v>
       </c>
-      <c r="I19" s="64"/>
+      <c r="I19" s="62"/>
       <c r="J19" s="28">
         <v>0.01</v>
       </c>
@@ -4568,15 +4622,15 @@
       <c r="B20" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="68"/>
+      <c r="C20" s="66"/>
       <c r="D20" s="28">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E20" s="64"/>
+      <c r="E20" s="62"/>
       <c r="F20" s="28">
         <v>0</v>
       </c>
-      <c r="I20" s="64"/>
+      <c r="I20" s="62"/>
       <c r="J20" s="28">
         <v>0.12</v>
       </c>
@@ -4585,15 +4639,15 @@
       <c r="B21" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="68"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="28">
         <v>0.65</v>
       </c>
-      <c r="E21" s="64"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="28">
         <v>0.02</v>
       </c>
-      <c r="I21" s="64"/>
+      <c r="I21" s="62"/>
       <c r="J21" s="28">
         <v>0</v>
       </c>
@@ -4602,15 +4656,15 @@
       <c r="B22" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="68"/>
+      <c r="C22" s="66"/>
       <c r="D22" s="28">
         <v>0.21</v>
       </c>
-      <c r="E22" s="64"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="28">
         <v>0</v>
       </c>
-      <c r="I22" s="64"/>
+      <c r="I22" s="62"/>
       <c r="J22" s="28">
         <v>0</v>
       </c>
@@ -4619,15 +4673,15 @@
       <c r="B23" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="69"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="28">
         <v>0.42</v>
       </c>
-      <c r="E23" s="64"/>
+      <c r="E23" s="62"/>
       <c r="F23" s="28">
         <v>0.01</v>
       </c>
-      <c r="I23" s="64"/>
+      <c r="I23" s="62"/>
       <c r="J23" s="28">
         <v>0.12</v>
       </c>
@@ -4853,125 +4907,237 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="8" width="14" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="10" width="12.85546875" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="69"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="70" t="s">
+        <v>219</v>
+      </c>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="72" t="s">
         <v>205</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B2" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="72" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D2" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="72" t="s">
         <v>214</v>
       </c>
-      <c r="E1" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="F1" s="21" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="G2" s="72" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="72" t="s">
+        <v>223</v>
+      </c>
+      <c r="J2" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="72" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="54">
+      <c r="B3" s="74">
+        <v>7823</v>
+      </c>
+      <c r="C3" s="75">
         <v>0.47699999999999998</v>
       </c>
-      <c r="C2" s="54">
+      <c r="D3" s="74">
+        <v>2</v>
+      </c>
+      <c r="E3" s="74">
+        <v>3</v>
+      </c>
+      <c r="F3" s="75">
         <v>0.31900000000000001</v>
       </c>
-      <c r="E2" s="15">
-        <v>2</v>
-      </c>
-      <c r="F2" s="15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="G3" s="75">
+        <v>0.10299999999999999</v>
+      </c>
+      <c r="H3" s="75">
+        <v>0.125</v>
+      </c>
+      <c r="I3" s="75">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J3" s="75">
+        <v>5.5E-2</v>
+      </c>
+      <c r="K3" s="75">
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="73" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="54">
+      <c r="B4" s="74">
+        <v>2984</v>
+      </c>
+      <c r="C4" s="75">
         <v>0.55000000000000004</v>
       </c>
-      <c r="C3" s="54">
+      <c r="D4" s="74">
+        <v>11</v>
+      </c>
+      <c r="E4" s="74">
+        <v>7</v>
+      </c>
+      <c r="F4" s="75">
         <v>0.26</v>
       </c>
-      <c r="E3" s="15">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="G4" s="75">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="H4" s="75">
+        <v>0.123</v>
+      </c>
+      <c r="I4" s="75">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="J4" s="75">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="K4" s="75">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B5" s="74">
+        <v>1555</v>
+      </c>
+      <c r="C5" s="75">
         <v>0.29899999999999999</v>
       </c>
-      <c r="C4" s="54">
+      <c r="D5" s="74">
+        <v>4</v>
+      </c>
+      <c r="E5" s="74">
+        <v>1</v>
+      </c>
+      <c r="F5" s="75">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E4" s="15">
-        <v>4</v>
-      </c>
-      <c r="F4" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="G5" s="75">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="H5" s="75">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="I5" s="75">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="J5" s="75">
+        <v>0.05</v>
+      </c>
+      <c r="K5" s="75">
+        <v>0.70099999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="54">
+      <c r="B6" s="74">
+        <v>144</v>
+      </c>
+      <c r="C6" s="75">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="C5" s="54">
+      <c r="D6" s="74" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" s="74">
+        <v>5</v>
+      </c>
+      <c r="F6" s="75">
         <v>0.20699999999999999</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" s="54">
+      <c r="G6" s="75">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="H6" s="75">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="I6" s="75">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="J6" s="75">
         <v>0</v>
       </c>
-      <c r="C6" s="54">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>29</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="K6" s="75">
+        <v>0.77200000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="H7" s="68"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B6">
+  <mergeCells count="2">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3:C6 B7">
     <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6 C7">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4982,7 +5148,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C6">
+  <conditionalFormatting sqref="E7:F7 D3:E6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -4994,8 +5172,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:F6">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="J3:K6">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5006,6 +5184,18 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G3:I6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/абибас.xlsx
+++ b/абибас.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" tabRatio="526" firstSheet="6" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" tabRatio="802" firstSheet="7" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Запросы" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,9 @@
     <sheet name="Конкуренты" sheetId="4" r:id="rId7"/>
     <sheet name="Интерактив" sheetId="9" r:id="rId8"/>
     <sheet name="Ссылки сайтов" sheetId="10" r:id="rId9"/>
+    <sheet name="Доноры" sheetId="11" r:id="rId10"/>
+    <sheet name="Анкор-лист" sheetId="12" r:id="rId11"/>
+    <sheet name="скорость загрузки" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="394">
   <si>
     <t>ЗАПРОС «СПОРТИВНАЯ ОДЕЖДА»</t>
   </si>
@@ -722,13 +725,515 @@
   </si>
   <si>
     <t>ИКС</t>
+  </si>
+  <si>
+    <t>ДИЗАЙН</t>
+  </si>
+  <si>
+    <t>ТРАФИК</t>
+  </si>
+  <si>
+    <t>ТЕМАТИКА</t>
+  </si>
+  <si>
+    <t>РЕГИОН</t>
+  </si>
+  <si>
+    <t>ТРАСТ</t>
+  </si>
+  <si>
+    <t>ВХОД. ССЫЛКИ</t>
+  </si>
+  <si>
+    <t>ИСХ. ССЫЛКИ</t>
+  </si>
+  <si>
+    <t>ЦЕНА</t>
+  </si>
+  <si>
+    <t>tv-wwe.ru</t>
+  </si>
+  <si>
+    <t>4/100</t>
+  </si>
+  <si>
+    <t>Спорт, СМИ</t>
+  </si>
+  <si>
+    <t>81,18 тыс.</t>
+  </si>
+  <si>
+    <t>современный</t>
+  </si>
+  <si>
+    <t>Россия</t>
+  </si>
+  <si>
+    <t>Россия, Хакасия</t>
+  </si>
+  <si>
+    <t>50/100</t>
+  </si>
+  <si>
+    <t>167,2 тыс</t>
+  </si>
+  <si>
+    <t>gazeta19.ru</t>
+  </si>
+  <si>
+    <t>zen.yandex.ru/filinfit69</t>
+  </si>
+  <si>
+    <t>65,05 тыс.</t>
+  </si>
+  <si>
+    <t>Спорт, здоровье и медицина, развлечения и хобби</t>
+  </si>
+  <si>
+    <t>100/100</t>
+  </si>
+  <si>
+    <t>imperiya.by</t>
+  </si>
+  <si>
+    <t>убогий</t>
+  </si>
+  <si>
+    <t>615 тыс.</t>
+  </si>
+  <si>
+    <t>9/100</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Спорт, СМИ, бизнес</t>
+  </si>
+  <si>
+    <t>Спорт, развлечения и хобби, мода и красота</t>
+  </si>
+  <si>
+    <t>milanac.ru</t>
+  </si>
+  <si>
+    <t>немного устаревший</t>
+  </si>
+  <si>
+    <t>7/100</t>
+  </si>
+  <si>
+    <t>125,1 тыс</t>
+  </si>
+  <si>
+    <t>Россия (?)</t>
+  </si>
+  <si>
+    <t>Спорт</t>
+  </si>
+  <si>
+    <t>sport-51.ru</t>
+  </si>
+  <si>
+    <t>35,08 тыс.</t>
+  </si>
+  <si>
+    <t>Россия, Мурманская обл.</t>
+  </si>
+  <si>
+    <t>10/100</t>
+  </si>
+  <si>
+    <t>устаревший</t>
+  </si>
+  <si>
+    <t>Спорт, СМИ, туризм</t>
+  </si>
+  <si>
+    <t>miryogi.com</t>
+  </si>
+  <si>
+    <t>терпимый</t>
+  </si>
+  <si>
+    <t>44,4 тыс</t>
+  </si>
+  <si>
+    <t>8/100</t>
+  </si>
+  <si>
+    <t>Спорт, здоровье и медицина, психология</t>
+  </si>
+  <si>
+    <t>auto.vercity.ru</t>
+  </si>
+  <si>
+    <t>неплохой</t>
+  </si>
+  <si>
+    <t>Авто и мото, СМИ, спорт</t>
+  </si>
+  <si>
+    <t>127 тыс.</t>
+  </si>
+  <si>
+    <t>12/100</t>
+  </si>
+  <si>
+    <t>snowbd.ru</t>
+  </si>
+  <si>
+    <t>устревеший</t>
+  </si>
+  <si>
+    <t>3,18 тыс.</t>
+  </si>
+  <si>
+    <t>55/100</t>
+  </si>
+  <si>
+    <t>14/100</t>
+  </si>
+  <si>
+    <t>sport.rin.ru</t>
+  </si>
+  <si>
+    <t>3,7 млн</t>
+  </si>
+  <si>
+    <t>59,16 тыс.</t>
+  </si>
+  <si>
+    <t>manutd.one</t>
+  </si>
+  <si>
+    <t>myliverpool.ru</t>
+  </si>
+  <si>
+    <t>165,1 тыс.</t>
+  </si>
+  <si>
+    <t>48/100</t>
+  </si>
+  <si>
+    <t>ВОЗРАСТ</t>
+  </si>
+  <si>
+    <t>6 лет</t>
+  </si>
+  <si>
+    <t>12 лет</t>
+  </si>
+  <si>
+    <t>12 лет, 6 мес.</t>
+  </si>
+  <si>
+    <t>6 лет, 10 месяцев</t>
+  </si>
+  <si>
+    <t>5 лет, 10 месяцев</t>
+  </si>
+  <si>
+    <t>13 лет, 8 месяцев</t>
+  </si>
+  <si>
+    <t>7 лет, 11 месяцев</t>
+  </si>
+  <si>
+    <t>3 года, 9 месяцев</t>
+  </si>
+  <si>
+    <t>8 лет, 10 месяцев</t>
+  </si>
+  <si>
+    <t>12 лет, 10 месяцев</t>
+  </si>
+  <si>
+    <t>Россия, Московская обл.</t>
+  </si>
+  <si>
+    <t>21 год, 10 месяцев</t>
+  </si>
+  <si>
+    <t>bestbodyblog.com</t>
+  </si>
+  <si>
+    <t>55,54 тыс.</t>
+  </si>
+  <si>
+    <t>17/100</t>
+  </si>
+  <si>
+    <t>4 года, 9 месяцев</t>
+  </si>
+  <si>
+    <t>motogp-news.ru</t>
+  </si>
+  <si>
+    <t>10 лет, 3 месяца</t>
+  </si>
+  <si>
+    <t>270,1 тыс.</t>
+  </si>
+  <si>
+    <t>2/100</t>
+  </si>
+  <si>
+    <t>167 тыс.</t>
+  </si>
+  <si>
+    <t>sport-nation.net</t>
+  </si>
+  <si>
+    <t>3 года, 10 месяцев</t>
+  </si>
+  <si>
+    <t>24/100</t>
+  </si>
+  <si>
+    <t>2,75 тыс</t>
+  </si>
+  <si>
+    <t>12 лет, 4 месяца</t>
+  </si>
+  <si>
+    <t>Спорт, развлечения и хобби</t>
+  </si>
+  <si>
+    <t>rus-boys.ru</t>
+  </si>
+  <si>
+    <t>pulse19.ru</t>
+  </si>
+  <si>
+    <t>15/100</t>
+  </si>
+  <si>
+    <t>121,4 тыс.</t>
+  </si>
+  <si>
+    <t>3 года, 1 месяц</t>
+  </si>
+  <si>
+    <t>football-esthete.ru</t>
+  </si>
+  <si>
+    <t>Россия, Костромская обл.</t>
+  </si>
+  <si>
+    <t>46,05 тыс.</t>
+  </si>
+  <si>
+    <t>2 года, 8 месяцев</t>
+  </si>
+  <si>
+    <t>45,92 тыс.</t>
+  </si>
+  <si>
+    <t>bet-ring.ru</t>
+  </si>
+  <si>
+    <t>57/100</t>
+  </si>
+  <si>
+    <t>СМИ, спорт</t>
+  </si>
+  <si>
+    <t>13 лет, 6 месяцев</t>
+  </si>
+  <si>
+    <t>damki.net</t>
+  </si>
+  <si>
+    <t>шашки</t>
+  </si>
+  <si>
+    <t>антиквариат</t>
+  </si>
+  <si>
+    <t>13 лет</t>
+  </si>
+  <si>
+    <t>KANT.RU</t>
+  </si>
+  <si>
+    <t>Безанкорные</t>
+  </si>
+  <si>
+    <t>Строго безанкорные</t>
+  </si>
+  <si>
+    <t>Фирменные</t>
+  </si>
+  <si>
+    <t>Анкорные</t>
+  </si>
+  <si>
+    <t>Прямые</t>
+  </si>
+  <si>
+    <t>Разбавленные</t>
+  </si>
+  <si>
+    <t>TRAEKTORIA.RU</t>
+  </si>
+  <si>
+    <t>PLANETA-SPORT.RU</t>
+  </si>
+  <si>
+    <t>SPB.RENDEZ-VOUS.RU</t>
+  </si>
+  <si>
+    <t>ССЫЛКА</t>
+  </si>
+  <si>
+    <t>Спорт, авто и мото, СМИ</t>
+  </si>
+  <si>
+    <t>ТЕКСТ ССЫЛКИ</t>
+  </si>
+  <si>
+    <t>Abibas</t>
+  </si>
+  <si>
+    <t>сайте</t>
+  </si>
+  <si>
+    <t>https://georgekazanba.github.io/index1.html</t>
+  </si>
+  <si>
+    <t>сайт Abibas</t>
+  </si>
+  <si>
+    <t>сайте Abibas</t>
+  </si>
+  <si>
+    <t>Абибас</t>
+  </si>
+  <si>
+    <t>здесь (одежда)</t>
+  </si>
+  <si>
+    <t>здесь (обувь)</t>
+  </si>
+  <si>
+    <t>ТИП</t>
+  </si>
+  <si>
+    <t>фирменная</t>
+  </si>
+  <si>
+    <t>безанкорная</t>
+  </si>
+  <si>
+    <t>прямая</t>
+  </si>
+  <si>
+    <t>разбавленная</t>
+  </si>
+  <si>
+    <t>линейкой одежды</t>
+  </si>
+  <si>
+    <t>КОМПЬЮТЕР</t>
+  </si>
+  <si>
+    <t>МОБ. УСТРОЙСТВА</t>
+  </si>
+  <si>
+    <t>GEORGEKAZANBA.GITHUB.IO</t>
+  </si>
+  <si>
+    <t>Производительность</t>
+  </si>
+  <si>
+    <t>1st Contentful Paint</t>
+  </si>
+  <si>
+    <t>Speed Index</t>
+  </si>
+  <si>
+    <t>Largest Contentful Paint</t>
+  </si>
+  <si>
+    <t>Time To Interactive</t>
+  </si>
+  <si>
+    <t>Total Blocking Time</t>
+  </si>
+  <si>
+    <t>Cumulative Layout Shift</t>
+  </si>
+  <si>
+    <t>2 сек</t>
+  </si>
+  <si>
+    <t>9,7 сек</t>
+  </si>
+  <si>
+    <t>3,7 сек</t>
+  </si>
+  <si>
+    <t>38,7 сек</t>
+  </si>
+  <si>
+    <t>9190 мс</t>
+  </si>
+  <si>
+    <t>1370 мс</t>
+  </si>
+  <si>
+    <t>7,2 сек</t>
+  </si>
+  <si>
+    <t>1,1 сек</t>
+  </si>
+  <si>
+    <t>1,4 сек</t>
+  </si>
+  <si>
+    <t>0,5 сек</t>
+  </si>
+  <si>
+    <t>3 сек</t>
+  </si>
+  <si>
+    <t>5 сек</t>
+  </si>
+  <si>
+    <t>2,3 сек</t>
+  </si>
+  <si>
+    <t>3,6 сек</t>
+  </si>
+  <si>
+    <t>3,2 сек</t>
+  </si>
+  <si>
+    <t>1,5 сек</t>
+  </si>
+  <si>
+    <t>2,1 сек</t>
+  </si>
+  <si>
+    <t>1,3 сек</t>
+  </si>
+  <si>
+    <t>2,2 сек</t>
+  </si>
+  <si>
+    <t>5,4 сек</t>
+  </si>
+  <si>
+    <t>4,1 сек</t>
+  </si>
+  <si>
+    <t>1,8 сек</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
@@ -805,7 +1310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -835,6 +1340,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -1065,7 +1582,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1074,8 +1591,10 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1227,6 +1746,71 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="9" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="9" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="8" borderId="0" xfId="9" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="8" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="7" borderId="0" xfId="8" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="9" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1272,30 +1856,44 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="10">
+    <cellStyle name="20% — акцент1" xfId="8" builtinId="30"/>
+    <cellStyle name="20% — акцент2" xfId="9" builtinId="34"/>
     <cellStyle name="40% — акцент2" xfId="7" builtinId="35"/>
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
     <cellStyle name="Нейтральный" xfId="3" builtinId="28"/>
@@ -1309,6 +1907,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFB3FFB7"/>
+      <color rgb="FFFF6B43"/>
+      <color rgb="FF85FF8B"/>
+      <color rgb="FFFF4715"/>
       <color rgb="FFACE6DC"/>
       <color rgb="FFD3F1D7"/>
       <color rgb="FFBFEBC4"/>
@@ -1457,6 +2059,174 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1419225" y="1771650"/>
+          <a:ext cx="4124325" cy="1295400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1200"/>
+            <a:t>Для наилучшей выдачи сайта в поисковых системах рекомендуется иметь как можно больше внешних ссылок на ваш</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1200" baseline="0"/>
+            <a:t> сайт и ИКС более 100, а также как можно меньше безанкорных ссылок и ИКС менее 100. Однако, не всегда всё работает по таким правилам и сайт с посредственными характеристиками имеет шанс выйти первым.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>380999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>309561</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>250031</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10048874" y="3809999"/>
+          <a:ext cx="6096000" cy="1964532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600"/>
+            <a:t>Выбор данных сайтов обуславливается хорошим трафиком у</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" baseline="0"/>
+            <a:t> большинства сайтов </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600"/>
+            <a:t>и</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600"/>
+            <a:t>неплохими от случая к случаю ИКС и трастом. Однако, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Collaborator</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ru-RU" sz="1600" baseline="0"/>
+            <a:t> не имеет более узкой фильтрации сайтов по тематике, из-за чего единственная подходящая тема "Спорт" была забита сайтами, которыми к спорту отношение имеют, но конкретики, а именно одежды, не было. Также из спорного стоит отметить цены. На некоторых из них они завышены.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2814,6 +3584,1419 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="68" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="67">
+        <v>730</v>
+      </c>
+      <c r="I2" s="67">
+        <v>300</v>
+      </c>
+      <c r="J2" s="67">
+        <v>38</v>
+      </c>
+      <c r="K2" s="70">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="G3" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="H3" s="67">
+        <v>1060</v>
+      </c>
+      <c r="I3" s="67">
+        <v>5443</v>
+      </c>
+      <c r="J3" s="67">
+        <v>5413</v>
+      </c>
+      <c r="K3" s="70">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>246</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="64" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="64">
+        <v>0</v>
+      </c>
+      <c r="I4" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="J4" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="K4" s="66">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" s="15">
+        <v>340</v>
+      </c>
+      <c r="I5" s="15">
+        <v>3706</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="K5" s="59">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="D6" s="67" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="68" t="s">
+        <v>300</v>
+      </c>
+      <c r="G6" s="67" t="s">
+        <v>257</v>
+      </c>
+      <c r="H6" s="67">
+        <v>1010</v>
+      </c>
+      <c r="I6" s="67">
+        <v>440</v>
+      </c>
+      <c r="J6" s="67">
+        <v>4291</v>
+      </c>
+      <c r="K6" s="70">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="67" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="68" t="s">
+        <v>263</v>
+      </c>
+      <c r="G7" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="H7" s="67">
+        <v>480</v>
+      </c>
+      <c r="I7" s="67">
+        <v>1113</v>
+      </c>
+      <c r="J7" s="67">
+        <v>275</v>
+      </c>
+      <c r="K7" s="70">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="64" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" s="64" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="E8" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>270</v>
+      </c>
+      <c r="H8" s="64">
+        <v>420</v>
+      </c>
+      <c r="I8" s="64">
+        <v>118</v>
+      </c>
+      <c r="J8" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="K8" s="66">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="67" t="s">
+        <v>272</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>273</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="67" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="67">
+        <v>840</v>
+      </c>
+      <c r="I9" s="67">
+        <v>1299</v>
+      </c>
+      <c r="J9" s="67">
+        <v>962</v>
+      </c>
+      <c r="K9" s="70">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="67" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" s="67" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" s="67" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" s="67">
+        <v>50</v>
+      </c>
+      <c r="I10" s="67">
+        <v>3596</v>
+      </c>
+      <c r="J10" s="67">
+        <v>2160</v>
+      </c>
+      <c r="K10" s="70">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="67" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="67" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>283</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F11" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G11" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11" s="67">
+        <v>1750</v>
+      </c>
+      <c r="I11" s="67">
+        <v>4027</v>
+      </c>
+      <c r="J11" s="67">
+        <v>1</v>
+      </c>
+      <c r="K11" s="70">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="67" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G12" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="H12" s="67">
+        <v>730</v>
+      </c>
+      <c r="I12" s="67">
+        <v>294</v>
+      </c>
+      <c r="J12" s="67">
+        <v>414</v>
+      </c>
+      <c r="K12" s="70">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="67" t="s">
+        <v>286</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>295</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G13" s="67" t="s">
+        <v>288</v>
+      </c>
+      <c r="H13" s="67">
+        <v>430</v>
+      </c>
+      <c r="I13" s="67">
+        <v>769</v>
+      </c>
+      <c r="J13" s="67">
+        <v>1174</v>
+      </c>
+      <c r="K13" s="70">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="64" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="64" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>304</v>
+      </c>
+      <c r="H14" s="64">
+        <v>360</v>
+      </c>
+      <c r="I14" s="64">
+        <v>340</v>
+      </c>
+      <c r="J14" s="64">
+        <v>1</v>
+      </c>
+      <c r="K14" s="66">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="67" t="s">
+        <v>306</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>307</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>268</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>346</v>
+      </c>
+      <c r="F15" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G15" s="67" t="s">
+        <v>281</v>
+      </c>
+      <c r="H15" s="67">
+        <v>1160</v>
+      </c>
+      <c r="I15" s="67">
+        <v>6993</v>
+      </c>
+      <c r="J15" s="67">
+        <v>2074</v>
+      </c>
+      <c r="K15" s="70">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="64" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="64" t="s">
+        <v>310</v>
+      </c>
+      <c r="E16" s="64" t="s">
+        <v>260</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" s="64" t="s">
+        <v>309</v>
+      </c>
+      <c r="H16" s="64">
+        <v>700</v>
+      </c>
+      <c r="I16" s="64">
+        <v>4958</v>
+      </c>
+      <c r="J16" s="64">
+        <v>1487</v>
+      </c>
+      <c r="K16" s="66">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="64" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="64" t="s">
+        <v>314</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>316</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="H17" s="64">
+        <v>150</v>
+      </c>
+      <c r="I17" s="64">
+        <v>271</v>
+      </c>
+      <c r="J17" s="64">
+        <v>1081</v>
+      </c>
+      <c r="K17" s="66">
+        <v>1709.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="67" t="s">
+        <v>318</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>321</v>
+      </c>
+      <c r="C18" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>320</v>
+      </c>
+      <c r="E18" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="H18" s="67">
+        <v>900</v>
+      </c>
+      <c r="I18" s="67">
+        <v>1691</v>
+      </c>
+      <c r="J18" s="67">
+        <v>4242</v>
+      </c>
+      <c r="K18" s="70">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="67" t="s">
+        <v>322</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="67" t="s">
+        <v>324</v>
+      </c>
+      <c r="E19" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="F19" s="68" t="s">
+        <v>323</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="H19" s="67">
+        <v>220</v>
+      </c>
+      <c r="I19" s="67">
+        <v>99</v>
+      </c>
+      <c r="J19" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="K19" s="70">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="67" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>330</v>
+      </c>
+      <c r="C20" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="67" t="s">
+        <v>326</v>
+      </c>
+      <c r="E20" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="F20" s="68" t="s">
+        <v>240</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>328</v>
+      </c>
+      <c r="H20" s="67">
+        <v>550</v>
+      </c>
+      <c r="I20" s="67">
+        <v>1676</v>
+      </c>
+      <c r="J20" s="67">
+        <v>847</v>
+      </c>
+      <c r="K20" s="70">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="D21" s="15">
+        <v>888</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="H21" s="15">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
+        <v>10432</v>
+      </c>
+      <c r="J21" s="15">
+        <v>204</v>
+      </c>
+      <c r="K21" s="59">
+        <v>999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="G1" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="H1" s="60" t="s">
+        <v>347</v>
+      </c>
+      <c r="I1" s="60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="97"/>
+      <c r="G2" s="71" t="s">
+        <v>357</v>
+      </c>
+      <c r="H2" s="72" t="s">
+        <v>348</v>
+      </c>
+      <c r="I2" s="72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="96"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="G3" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="H3" s="74" t="s">
+        <v>351</v>
+      </c>
+      <c r="I3" s="74" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="93">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="B4" s="93">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="G4" s="73" t="s">
+        <v>357</v>
+      </c>
+      <c r="H4" s="74" t="s">
+        <v>352</v>
+      </c>
+      <c r="I4" s="74" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="93"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="G5" s="71" t="s">
+        <v>357</v>
+      </c>
+      <c r="H5" s="72" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" s="72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="G6" s="71" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="I6" s="72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="94" t="s">
+        <v>342</v>
+      </c>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="G7" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="H7" s="74" t="s">
+        <v>354</v>
+      </c>
+      <c r="I7" s="73" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D8" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="E8" s="97"/>
+      <c r="G8" s="73" t="s">
+        <v>358</v>
+      </c>
+      <c r="H8" s="74" t="s">
+        <v>355</v>
+      </c>
+      <c r="I8" s="74" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="96"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>360</v>
+      </c>
+      <c r="H9" s="72" t="s">
+        <v>361</v>
+      </c>
+      <c r="I9" s="71" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="93">
+        <v>0.03</v>
+      </c>
+      <c r="B10" s="93">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="G10" s="71" t="s">
+        <v>360</v>
+      </c>
+      <c r="H10" s="72" t="s">
+        <v>349</v>
+      </c>
+      <c r="I10" s="72" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="93"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="G11" s="73" t="s">
+        <v>359</v>
+      </c>
+      <c r="H11" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="74" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="94" t="s">
+        <v>343</v>
+      </c>
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="G13" s="63"/>
+    </row>
+    <row r="14" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="B14" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="E14" s="97"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="96"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="93">
+        <v>2.4E-2</v>
+      </c>
+      <c r="B16" s="93">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="93"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="94" t="s">
+        <v>344</v>
+      </c>
+      <c r="B19" s="94"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="95" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="95" t="s">
+        <v>336</v>
+      </c>
+      <c r="C20" s="95" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="97"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="96"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="93">
+        <v>0</v>
+      </c>
+      <c r="B22" s="93">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="93"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="100"/>
+      <c r="B1" s="99" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99" t="s">
+        <v>342</v>
+      </c>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99" t="s">
+        <v>343</v>
+      </c>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99" t="s">
+        <v>344</v>
+      </c>
+      <c r="K1" s="99"/>
+    </row>
+    <row r="2" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="101"/>
+      <c r="B2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="F2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="G2" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="H2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="I2" s="62" t="s">
+        <v>362</v>
+      </c>
+      <c r="J2" s="62" t="s">
+        <v>363</v>
+      </c>
+      <c r="K2" s="62" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="98" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="102">
+        <v>0.39</v>
+      </c>
+      <c r="C3" s="102">
+        <v>0.59</v>
+      </c>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+    </row>
+    <row r="4" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="98" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>390</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>393</v>
+      </c>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+    </row>
+    <row r="5" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="98" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+    </row>
+    <row r="6" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="98" t="s">
+        <v>368</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>388</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>391</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>392</v>
+      </c>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+    </row>
+    <row r="7" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="98" t="s">
+        <v>369</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="98" t="s">
+        <v>370</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>377</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+    </row>
+    <row r="9" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="98" t="s">
+        <v>371</v>
+      </c>
+      <c r="B9" s="29">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C9" s="29">
+        <v>0.01</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0.13</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0.01</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0.01</v>
+      </c>
+      <c r="H9" s="29">
+        <v>0.21</v>
+      </c>
+      <c r="I9" s="29">
+        <v>0.24</v>
+      </c>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K25"/>
@@ -3454,23 +5637,23 @@
   <sheetData>
     <row r="1" spans="2:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="58"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
       <c r="E2" s="15"/>
-      <c r="F2" s="56" t="s">
+      <c r="F2" s="79" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="81"/>
       <c r="I2" s="15"/>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="58"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="81"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="30" t="s">
@@ -3600,11 +5783,11 @@
       <c r="D7" s="36">
         <v>0.75</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="G7" s="54"/>
-      <c r="H7" s="55"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="78"/>
       <c r="J7" s="34" t="s">
         <v>5</v>
       </c>
@@ -3625,11 +5808,11 @@
       <c r="D8" s="36">
         <v>0.7</v>
       </c>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="76" t="s">
         <v>161</v>
       </c>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
+      <c r="K8" s="77"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="34" t="s">
@@ -3643,11 +5826,11 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="78"/>
     </row>
     <row r="11" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
@@ -3792,8 +5975,8 @@
       <c r="A2" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
@@ -3887,8 +6070,8 @@
       <c r="A11" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
@@ -3982,8 +6165,8 @@
       <c r="A20" s="46" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
@@ -4090,31 +6273,31 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83" t="s">
         <v>155</v>
       </c>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60" t="s">
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83" t="s">
         <v>156</v>
       </c>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4197,37 +6380,37 @@
       <c r="B3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="87" t="s">
         <v>195</v>
       </c>
       <c r="D3" s="28">
         <v>0.22</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="87" t="s">
         <v>196</v>
       </c>
       <c r="F3" s="28">
         <v>0.49</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="87" t="s">
         <v>197</v>
       </c>
       <c r="H3" s="28">
         <v>0.01</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="87" t="s">
         <v>198</v>
       </c>
       <c r="J3" s="28">
         <v>0.59</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="87" t="s">
         <v>199</v>
       </c>
       <c r="L3" s="28">
         <v>0.49</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="87" t="s">
         <v>200</v>
       </c>
       <c r="N3" s="28">
@@ -4238,27 +6421,27 @@
       <c r="B4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="64"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="28">
         <v>0.25</v>
       </c>
-      <c r="E4" s="64"/>
+      <c r="E4" s="87"/>
       <c r="F4" s="28">
         <v>0.27</v>
       </c>
-      <c r="G4" s="64"/>
+      <c r="G4" s="87"/>
       <c r="H4" s="28">
         <v>0.15</v>
       </c>
-      <c r="I4" s="64"/>
+      <c r="I4" s="87"/>
       <c r="J4" s="28">
         <v>0.18</v>
       </c>
-      <c r="K4" s="64"/>
+      <c r="K4" s="87"/>
       <c r="L4" s="28">
         <v>0.3</v>
       </c>
-      <c r="M4" s="64"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="28">
         <v>0.26</v>
       </c>
@@ -4267,27 +6450,27 @@
       <c r="B5" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="64"/>
+      <c r="C5" s="87"/>
       <c r="D5" s="28">
         <v>0.09</v>
       </c>
-      <c r="E5" s="64"/>
+      <c r="E5" s="87"/>
       <c r="F5" s="28">
         <v>0.19</v>
       </c>
-      <c r="G5" s="64"/>
+      <c r="G5" s="87"/>
       <c r="H5" s="28">
         <v>0.15</v>
       </c>
-      <c r="I5" s="64"/>
+      <c r="I5" s="87"/>
       <c r="J5" s="28">
         <v>0.21</v>
       </c>
-      <c r="K5" s="64"/>
+      <c r="K5" s="87"/>
       <c r="L5" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M5" s="64"/>
+      <c r="M5" s="87"/>
       <c r="N5" s="28">
         <v>0.26</v>
       </c>
@@ -4296,27 +6479,27 @@
       <c r="B6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="64"/>
+      <c r="C6" s="87"/>
       <c r="D6" s="28">
         <v>0.16</v>
       </c>
-      <c r="E6" s="64"/>
+      <c r="E6" s="87"/>
       <c r="F6" s="28">
         <v>0.63</v>
       </c>
-      <c r="G6" s="64"/>
+      <c r="G6" s="87"/>
       <c r="H6" s="28">
         <v>0.5</v>
       </c>
-      <c r="I6" s="64"/>
+      <c r="I6" s="87"/>
       <c r="J6" s="28">
         <v>0.64</v>
       </c>
-      <c r="K6" s="64"/>
+      <c r="K6" s="87"/>
       <c r="L6" s="28">
         <v>0.49</v>
       </c>
-      <c r="M6" s="64"/>
+      <c r="M6" s="87"/>
       <c r="N6" s="28">
         <v>0.2</v>
       </c>
@@ -4325,27 +6508,27 @@
       <c r="B7" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="64"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="28">
         <v>0.63</v>
       </c>
-      <c r="E7" s="64"/>
+      <c r="E7" s="87"/>
       <c r="F7" s="28">
         <v>0</v>
       </c>
-      <c r="G7" s="64"/>
+      <c r="G7" s="87"/>
       <c r="H7" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="64"/>
+      <c r="I7" s="87"/>
       <c r="J7" s="28">
         <v>0</v>
       </c>
-      <c r="K7" s="64"/>
+      <c r="K7" s="87"/>
       <c r="L7" s="28">
         <v>0</v>
       </c>
-      <c r="M7" s="64"/>
+      <c r="M7" s="87"/>
       <c r="N7" s="28">
         <v>0</v>
       </c>
@@ -4354,27 +6537,27 @@
       <c r="B8" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="64"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="28">
         <v>0.61</v>
       </c>
-      <c r="E8" s="64"/>
+      <c r="E8" s="87"/>
       <c r="F8" s="28">
         <v>0.01</v>
       </c>
-      <c r="G8" s="64"/>
+      <c r="G8" s="87"/>
       <c r="H8" s="28">
         <v>0.18</v>
       </c>
-      <c r="I8" s="64"/>
+      <c r="I8" s="87"/>
       <c r="J8" s="28">
         <v>0.01</v>
       </c>
-      <c r="K8" s="64"/>
+      <c r="K8" s="87"/>
       <c r="L8" s="28">
         <v>0.2</v>
       </c>
-      <c r="M8" s="64"/>
+      <c r="M8" s="87"/>
       <c r="N8" s="28">
         <v>0.17</v>
       </c>
@@ -4383,27 +6566,27 @@
       <c r="B9" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="87"/>
       <c r="D9" s="28">
         <v>0.52</v>
       </c>
-      <c r="E9" s="64"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="28">
         <v>0.19</v>
       </c>
-      <c r="G9" s="64"/>
+      <c r="G9" s="87"/>
       <c r="H9" s="28">
         <v>0.18</v>
       </c>
-      <c r="I9" s="64"/>
+      <c r="I9" s="87"/>
       <c r="J9" s="28">
         <v>0.12</v>
       </c>
-      <c r="K9" s="64"/>
+      <c r="K9" s="87"/>
       <c r="L9" s="28">
         <v>0.22</v>
       </c>
-      <c r="M9" s="64"/>
+      <c r="M9" s="87"/>
       <c r="N9" s="28">
         <v>0.18</v>
       </c>
@@ -4412,27 +6595,27 @@
       <c r="B10" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="64"/>
+      <c r="C10" s="87"/>
       <c r="D10" s="28">
         <v>0.51</v>
       </c>
-      <c r="E10" s="64"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="28">
         <v>0</v>
       </c>
-      <c r="G10" s="64"/>
+      <c r="G10" s="87"/>
       <c r="H10" s="28">
         <v>0</v>
       </c>
-      <c r="I10" s="64"/>
+      <c r="I10" s="87"/>
       <c r="J10" s="28">
         <v>0</v>
       </c>
-      <c r="K10" s="64"/>
+      <c r="K10" s="87"/>
       <c r="L10" s="28">
         <v>0</v>
       </c>
-      <c r="M10" s="64"/>
+      <c r="M10" s="87"/>
       <c r="N10" s="28">
         <v>0</v>
       </c>
@@ -4441,27 +6624,27 @@
       <c r="B11" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="64"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="28">
         <v>0.56999999999999995</v>
       </c>
-      <c r="E11" s="64"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="28">
         <v>0</v>
       </c>
-      <c r="G11" s="64"/>
+      <c r="G11" s="87"/>
       <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="64"/>
+      <c r="I11" s="87"/>
       <c r="J11" s="28">
         <v>0</v>
       </c>
-      <c r="K11" s="64"/>
+      <c r="K11" s="87"/>
       <c r="L11" s="28">
         <v>0</v>
       </c>
-      <c r="M11" s="64"/>
+      <c r="M11" s="87"/>
       <c r="N11" s="28">
         <v>0</v>
       </c>
@@ -4470,27 +6653,27 @@
       <c r="B12" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="28">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E12" s="64"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="28">
         <v>0.19</v>
       </c>
-      <c r="G12" s="64"/>
+      <c r="G12" s="87"/>
       <c r="H12" s="28">
         <v>0.18</v>
       </c>
-      <c r="I12" s="64"/>
+      <c r="I12" s="87"/>
       <c r="J12" s="28">
         <v>0.12</v>
       </c>
-      <c r="K12" s="64"/>
+      <c r="K12" s="87"/>
       <c r="L12" s="28">
         <v>0.23</v>
       </c>
-      <c r="M12" s="64"/>
+      <c r="M12" s="87"/>
       <c r="N12" s="28">
         <v>0.18</v>
       </c>
@@ -4514,19 +6697,19 @@
       <c r="B14" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="88" t="s">
         <v>201</v>
       </c>
       <c r="D14" s="28">
         <v>0.49</v>
       </c>
-      <c r="E14" s="63" t="s">
+      <c r="E14" s="86" t="s">
         <v>202</v>
       </c>
       <c r="F14" s="28">
         <v>0.49</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="84" t="s">
         <v>203</v>
       </c>
       <c r="J14" s="41">
@@ -4537,15 +6720,15 @@
       <c r="B15" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="66"/>
+      <c r="C15" s="89"/>
       <c r="D15" s="28">
         <v>0.62</v>
       </c>
-      <c r="E15" s="62"/>
+      <c r="E15" s="85"/>
       <c r="F15" s="28">
         <v>0.2</v>
       </c>
-      <c r="I15" s="62"/>
+      <c r="I15" s="85"/>
       <c r="J15" s="28">
         <v>0.18</v>
       </c>
@@ -4554,15 +6737,15 @@
       <c r="B16" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="89"/>
       <c r="D16" s="28">
         <v>0.04</v>
       </c>
-      <c r="E16" s="62"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="28">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I16" s="62"/>
+      <c r="I16" s="85"/>
       <c r="J16" s="28">
         <v>0.21</v>
       </c>
@@ -4571,15 +6754,15 @@
       <c r="B17" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="66"/>
+      <c r="C17" s="89"/>
       <c r="D17" s="28">
         <v>0.18</v>
       </c>
-      <c r="E17" s="62"/>
+      <c r="E17" s="85"/>
       <c r="F17" s="28">
         <v>0.19</v>
       </c>
-      <c r="I17" s="62"/>
+      <c r="I17" s="85"/>
       <c r="J17" s="28">
         <v>0.64</v>
       </c>
@@ -4588,15 +6771,15 @@
       <c r="B18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="66"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="28">
         <v>0.71</v>
       </c>
-      <c r="E18" s="62"/>
+      <c r="E18" s="85"/>
       <c r="F18" s="28">
         <v>0</v>
       </c>
-      <c r="I18" s="62"/>
+      <c r="I18" s="85"/>
       <c r="J18" s="28">
         <v>0</v>
       </c>
@@ -4605,15 +6788,15 @@
       <c r="B19" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="66"/>
+      <c r="C19" s="89"/>
       <c r="D19" s="28">
         <v>0.65</v>
       </c>
-      <c r="E19" s="62"/>
+      <c r="E19" s="85"/>
       <c r="F19" s="28">
         <v>0</v>
       </c>
-      <c r="I19" s="62"/>
+      <c r="I19" s="85"/>
       <c r="J19" s="28">
         <v>0.01</v>
       </c>
@@ -4622,15 +6805,15 @@
       <c r="B20" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="66"/>
+      <c r="C20" s="89"/>
       <c r="D20" s="28">
         <v>0.55000000000000004</v>
       </c>
-      <c r="E20" s="62"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="28">
         <v>0</v>
       </c>
-      <c r="I20" s="62"/>
+      <c r="I20" s="85"/>
       <c r="J20" s="28">
         <v>0.12</v>
       </c>
@@ -4639,15 +6822,15 @@
       <c r="B21" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="28">
         <v>0.65</v>
       </c>
-      <c r="E21" s="62"/>
+      <c r="E21" s="85"/>
       <c r="F21" s="28">
         <v>0.02</v>
       </c>
-      <c r="I21" s="62"/>
+      <c r="I21" s="85"/>
       <c r="J21" s="28">
         <v>0</v>
       </c>
@@ -4656,15 +6839,15 @@
       <c r="B22" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="66"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="28">
         <v>0.21</v>
       </c>
-      <c r="E22" s="62"/>
+      <c r="E22" s="85"/>
       <c r="F22" s="28">
         <v>0</v>
       </c>
-      <c r="I22" s="62"/>
+      <c r="I22" s="85"/>
       <c r="J22" s="28">
         <v>0</v>
       </c>
@@ -4673,15 +6856,15 @@
       <c r="B23" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="28">
         <v>0.42</v>
       </c>
-      <c r="E23" s="62"/>
+      <c r="E23" s="85"/>
       <c r="F23" s="28">
         <v>0.01</v>
       </c>
-      <c r="I23" s="62"/>
+      <c r="I23" s="85"/>
       <c r="J23" s="28">
         <v>0.12</v>
       </c>
@@ -4921,194 +7104,194 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="70" t="s">
+      <c r="A1" s="54"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71" t="s">
+      <c r="E1" s="91"/>
+      <c r="F1" s="92" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="55" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="55" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="55" t="s">
         <v>186</v>
       </c>
-      <c r="E2" s="72" t="s">
+      <c r="E2" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="55" t="s">
         <v>214</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="55" t="s">
         <v>221</v>
       </c>
-      <c r="H2" s="72" t="s">
+      <c r="H2" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="55" t="s">
         <v>223</v>
       </c>
-      <c r="J2" s="72" t="s">
+      <c r="J2" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="K2" s="72" t="s">
+      <c r="K2" s="55" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="57">
         <v>7823</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="58">
         <v>0.47699999999999998</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D3" s="57">
         <v>2</v>
       </c>
-      <c r="E3" s="74">
+      <c r="E3" s="57">
         <v>3</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="58">
         <v>0.31900000000000001</v>
       </c>
-      <c r="G3" s="75">
+      <c r="G3" s="58">
         <v>0.10299999999999999</v>
       </c>
-      <c r="H3" s="75">
+      <c r="H3" s="58">
         <v>0.125</v>
       </c>
-      <c r="I3" s="75">
+      <c r="I3" s="58">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J3" s="75">
+      <c r="J3" s="58">
         <v>5.5E-2</v>
       </c>
-      <c r="K3" s="75">
+      <c r="K3" s="58">
         <v>0.372</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="B4" s="74">
+      <c r="B4" s="57">
         <v>2984</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="58">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="57">
         <v>11</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="57">
         <v>7</v>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="58">
         <v>0.26</v>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="58">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="58">
         <v>0.123</v>
       </c>
-      <c r="I4" s="75">
+      <c r="I4" s="58">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J4" s="75">
+      <c r="J4" s="58">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="K4" s="75">
+      <c r="K4" s="58">
         <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="56" t="s">
         <v>216</v>
       </c>
-      <c r="B5" s="74">
+      <c r="B5" s="57">
         <v>1555</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="58">
         <v>0.29899999999999999</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="57">
         <v>4</v>
       </c>
-      <c r="E5" s="74">
+      <c r="E5" s="57">
         <v>1</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="58">
         <v>0.13500000000000001</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="58">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="58">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="I5" s="75">
+      <c r="I5" s="58">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="58">
         <v>0.05</v>
       </c>
-      <c r="K5" s="75">
+      <c r="K5" s="58">
         <v>0.70099999999999996</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="57">
         <v>144</v>
       </c>
-      <c r="C6" s="75">
+      <c r="C6" s="58">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="E6" s="74">
+      <c r="E6" s="57">
         <v>5</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="58">
         <v>0.20699999999999999</v>
       </c>
-      <c r="G6" s="75">
+      <c r="G6" s="58">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="58">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I6" s="75">
+      <c r="I6" s="58">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J6" s="75">
+      <c r="J6" s="58">
         <v>0</v>
       </c>
-      <c r="K6" s="75">
+      <c r="K6" s="58">
         <v>0.77200000000000002</v>
       </c>
     </row>
@@ -5117,7 +7300,7 @@
       <c r="C7" s="52"/>
       <c r="E7" s="15"/>
       <c r="F7" s="15"/>
-      <c r="H7" s="68"/>
+      <c r="H7" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5125,6 +7308,54 @@
     <mergeCell ref="F1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:C6 B7">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6 C7">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:F7 D3:E6">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B6">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:K6">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -5136,31 +7367,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6 C7">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:F7 D3:E6">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B6">
+  <conditionalFormatting sqref="G3:I6">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -5172,8 +7379,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K6">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="I3:I6">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5184,19 +7391,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:I6">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>